--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -838,7 +838,7 @@
         <v>42</v>
       </c>
       <c r="F25" t="n">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="G25" t="n">
         <v>0.0</v>
@@ -3984,7 +3984,7 @@
         <v>40</v>
       </c>
       <c r="F146" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="G146" t="n">
         <v>0.0</v>
@@ -4010,7 +4010,7 @@
         <v>41</v>
       </c>
       <c r="F147" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G147" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -240,7 +240,7 @@
         <v>39</v>
       </c>
       <c r="F2" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="G2" t="n">
         <v>5.0</v>
@@ -1436,7 +1436,7 @@
         <v>42</v>
       </c>
       <c r="F48" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G48" t="n">
         <v>1.0</v>
@@ -1780,7 +1780,7 @@
         <v>0.0</v>
       </c>
       <c r="H61" t="n">
-        <v>36.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="62">
@@ -2606,7 +2606,7 @@
         <v>39</v>
       </c>
       <c r="F93" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G93" t="n">
         <v>0.0</v>
@@ -3256,7 +3256,7 @@
         <v>41</v>
       </c>
       <c r="F118" t="n">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
       <c r="G118" t="n">
         <v>14.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1228,7 +1228,7 @@
         <v>42</v>
       </c>
       <c r="F40" t="n">
-        <v>133.0</v>
+        <v>132.0</v>
       </c>
       <c r="G40" t="n">
         <v>1.0</v>
@@ -3282,10 +3282,10 @@
         <v>42</v>
       </c>
       <c r="F119" t="n">
-        <v>532.0</v>
+        <v>533.0</v>
       </c>
       <c r="G119" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="H119" t="n">
         <v>1.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3282,7 +3282,7 @@
         <v>42</v>
       </c>
       <c r="F119" t="n">
-        <v>533.0</v>
+        <v>532.0</v>
       </c>
       <c r="G119" t="n">
         <v>8.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="46">
   <si>
     <t>Area</t>
   </si>
@@ -630,7 +630,7 @@
         <v>41</v>
       </c>
       <c r="F17" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="G17" t="n">
         <v>1.0</v>
@@ -708,7 +708,7 @@
         <v>42</v>
       </c>
       <c r="F20" t="n">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="G20" t="n">
         <v>0.0</v>
@@ -1202,7 +1202,7 @@
         <v>41</v>
       </c>
       <c r="F39" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G39" t="n">
         <v>1.0</v>
@@ -1228,7 +1228,7 @@
         <v>42</v>
       </c>
       <c r="F40" t="n">
-        <v>132.0</v>
+        <v>131.0</v>
       </c>
       <c r="G40" t="n">
         <v>1.0</v>
@@ -1592,7 +1592,7 @@
         <v>41</v>
       </c>
       <c r="F54" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="G54" t="n">
         <v>0.0</v>
@@ -3695,10 +3695,10 @@
         <v>35</v>
       </c>
       <c r="E135" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G135" t="n">
         <v>1.0</v>
@@ -3721,13 +3721,13 @@
         <v>35</v>
       </c>
       <c r="E136" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F136" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H136" t="n">
         <v>0.0</v>
@@ -3747,10 +3747,10 @@
         <v>35</v>
       </c>
       <c r="E137" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F137" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G137" t="n">
         <v>0.0</v>
@@ -3764,7 +3764,7 @@
         <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C138" t="s">
         <v>16</v>
@@ -3773,13 +3773,13 @@
         <v>35</v>
       </c>
       <c r="E138" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F138" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3799,13 +3799,13 @@
         <v>35</v>
       </c>
       <c r="E139" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F139" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G139" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3825,13 +3825,13 @@
         <v>35</v>
       </c>
       <c r="E140" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F140" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G140" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H140" t="n">
         <v>0.0</v>
@@ -3851,7 +3851,7 @@
         <v>35</v>
       </c>
       <c r="E141" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F141" t="n">
         <v>2.0</v>
@@ -3868,7 +3868,7 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C142" t="s">
         <v>16</v>
@@ -3876,11 +3876,11 @@
       <c r="D142" t="s">
         <v>35</v>
       </c>
-      <c r="E142" t="s">
-        <v>40</v>
+      <c r="E142" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F142" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G142" t="n">
         <v>0.0</v>
@@ -3894,7 +3894,7 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C143" t="s">
         <v>16</v>
@@ -3903,10 +3903,10 @@
         <v>35</v>
       </c>
       <c r="E143" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F143" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G143" t="n">
         <v>0.0</v>
@@ -3928,11 +3928,11 @@
       <c r="D144" t="s">
         <v>35</v>
       </c>
-      <c r="E144" t="e">
-        <v>#N/A</v>
+      <c r="E144" t="s">
+        <v>40</v>
       </c>
       <c r="F144" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G144" t="n">
         <v>0.0</v>
@@ -3955,10 +3955,10 @@
         <v>35</v>
       </c>
       <c r="E145" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F145" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G145" t="n">
         <v>0.0</v>
@@ -3981,10 +3981,10 @@
         <v>35</v>
       </c>
       <c r="E146" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F146" t="n">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="G146" t="n">
         <v>0.0</v>
@@ -3998,22 +3998,22 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C147" t="s">
         <v>16</v>
       </c>
       <c r="D147" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E147" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F147" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4024,22 +4024,22 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C148" t="s">
         <v>16</v>
       </c>
       <c r="D148" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E148" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F148" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4059,13 +4059,13 @@
         <v>36</v>
       </c>
       <c r="E149" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F149" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G149" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4085,13 +4085,13 @@
         <v>36</v>
       </c>
       <c r="E150" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F150" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G150" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>
@@ -4111,13 +4111,13 @@
         <v>36</v>
       </c>
       <c r="E151" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F151" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G151" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4137,10 +4137,10 @@
         <v>36</v>
       </c>
       <c r="E152" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F152" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G152" t="n">
         <v>0.0</v>
@@ -4154,19 +4154,19 @@
         <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C153" t="s">
         <v>16</v>
       </c>
       <c r="D153" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E153" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F153" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G153" t="n">
         <v>0.0</v>
@@ -4180,22 +4180,22 @@
         <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C154" t="s">
         <v>16</v>
       </c>
       <c r="D154" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E154" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F154" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G154" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H154" t="n">
         <v>0.0</v>
@@ -4206,19 +4206,19 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C155" t="s">
         <v>16</v>
       </c>
       <c r="D155" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E155" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F155" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G155" t="n">
         <v>0.0</v>
@@ -4232,7 +4232,7 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C156" t="s">
         <v>16</v>
@@ -4241,13 +4241,13 @@
         <v>38</v>
       </c>
       <c r="E156" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F156" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G156" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H156" t="n">
         <v>0.0</v>
@@ -4258,7 +4258,7 @@
         <v>8</v>
       </c>
       <c r="B157" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C157" t="s">
         <v>16</v>
@@ -4267,13 +4267,13 @@
         <v>38</v>
       </c>
       <c r="E157" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F157" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G157" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H157" t="n">
         <v>0.0</v>
@@ -4284,7 +4284,7 @@
         <v>8</v>
       </c>
       <c r="B158" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C158" t="s">
         <v>16</v>
@@ -4293,13 +4293,13 @@
         <v>38</v>
       </c>
       <c r="E158" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F158" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G158" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G158" t="n">
-        <v>0.0</v>
       </c>
       <c r="H158" t="n">
         <v>0.0</v>
@@ -4319,13 +4319,13 @@
         <v>38</v>
       </c>
       <c r="E159" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F159" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G159" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H159" t="n">
         <v>0.0</v>
@@ -4345,13 +4345,13 @@
         <v>38</v>
       </c>
       <c r="E160" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F160" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G160" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H160" t="n">
         <v>0.0</v>
@@ -4371,10 +4371,10 @@
         <v>38</v>
       </c>
       <c r="E161" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F161" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G161" t="n">
         <v>1.0</v>
@@ -4397,67 +4397,15 @@
         <v>38</v>
       </c>
       <c r="E162" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F162" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="G162" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H162" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>8</v>
-      </c>
-      <c r="B163" t="s">
-        <v>9</v>
-      </c>
-      <c r="C163" t="s">
-        <v>16</v>
-      </c>
-      <c r="D163" t="s">
-        <v>38</v>
-      </c>
-      <c r="E163" t="s">
-        <v>42</v>
-      </c>
-      <c r="F163" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="G163" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H163" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>8</v>
-      </c>
-      <c r="B164" t="s">
-        <v>9</v>
-      </c>
-      <c r="C164" t="s">
-        <v>16</v>
-      </c>
-      <c r="D164" t="s">
-        <v>38</v>
-      </c>
-      <c r="E164" t="s">
-        <v>43</v>
-      </c>
-      <c r="F164" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G164" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H164" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1774,13 +1774,13 @@
         <v>42</v>
       </c>
       <c r="F61" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
       </c>
       <c r="H61" t="n">
-        <v>35.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="62">

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="46">
   <si>
     <t>Area</t>
   </si>
@@ -3903,10 +3903,10 @@
         <v>35</v>
       </c>
       <c r="E143" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F143" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G143" t="n">
         <v>0.0</v>
@@ -3929,7 +3929,7 @@
         <v>35</v>
       </c>
       <c r="E144" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F144" t="n">
         <v>10.0</v>
@@ -3955,10 +3955,10 @@
         <v>35</v>
       </c>
       <c r="E145" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F145" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G145" t="n">
         <v>0.0</v>
@@ -3972,22 +3972,22 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C146" t="s">
         <v>16</v>
       </c>
       <c r="D146" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E146" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F146" t="n">
         <v>4.0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4007,13 +4007,13 @@
         <v>36</v>
       </c>
       <c r="E147" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F147" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G147" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4033,13 +4033,13 @@
         <v>36</v>
       </c>
       <c r="E148" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F148" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G148" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4059,13 +4059,13 @@
         <v>36</v>
       </c>
       <c r="E149" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F149" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G149" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4085,10 +4085,10 @@
         <v>36</v>
       </c>
       <c r="E150" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F150" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G150" t="n">
         <v>0.0</v>
@@ -4111,10 +4111,10 @@
         <v>36</v>
       </c>
       <c r="E151" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F151" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G151" t="n">
         <v>0.0</v>
@@ -4128,19 +4128,19 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C152" t="s">
         <v>16</v>
       </c>
       <c r="D152" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E152" t="s">
         <v>42</v>
       </c>
       <c r="F152" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G152" t="n">
         <v>0.0</v>
@@ -4154,22 +4154,22 @@
         <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C153" t="s">
         <v>16</v>
       </c>
       <c r="D153" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E153" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F153" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H153" t="n">
         <v>0.0</v>
@@ -4189,13 +4189,13 @@
         <v>38</v>
       </c>
       <c r="E154" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F154" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G154" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H154" t="n">
         <v>0.0</v>
@@ -4206,7 +4206,7 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C155" t="s">
         <v>16</v>
@@ -4232,7 +4232,7 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C156" t="s">
         <v>16</v>
@@ -4241,13 +4241,13 @@
         <v>38</v>
       </c>
       <c r="E156" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F156" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H156" t="n">
         <v>0.0</v>
@@ -4267,13 +4267,13 @@
         <v>38</v>
       </c>
       <c r="E157" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F157" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G157" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H157" t="n">
         <v>0.0</v>
@@ -4293,13 +4293,13 @@
         <v>38</v>
       </c>
       <c r="E158" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F158" t="n">
         <v>1.0</v>
       </c>
       <c r="G158" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H158" t="n">
         <v>0.0</v>
@@ -4319,13 +4319,13 @@
         <v>38</v>
       </c>
       <c r="E159" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F159" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G159" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H159" t="n">
         <v>0.0</v>
@@ -4345,13 +4345,13 @@
         <v>38</v>
       </c>
       <c r="E160" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F160" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="G160" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H160" t="n">
         <v>0.0</v>
@@ -4371,41 +4371,15 @@
         <v>38</v>
       </c>
       <c r="E161" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F161" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="G161" t="n">
         <v>1.0</v>
       </c>
       <c r="H161" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>8</v>
-      </c>
-      <c r="B162" t="s">
-        <v>9</v>
-      </c>
-      <c r="C162" t="s">
-        <v>16</v>
-      </c>
-      <c r="D162" t="s">
-        <v>38</v>
-      </c>
-      <c r="E162" t="s">
-        <v>43</v>
-      </c>
-      <c r="F162" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G162" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H162" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -240,7 +240,7 @@
         <v>39</v>
       </c>
       <c r="F2" t="n">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="G2" t="n">
         <v>5.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="46">
   <si>
     <t>Area</t>
   </si>
@@ -1592,7 +1592,7 @@
         <v>41</v>
       </c>
       <c r="F54" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G54" t="n">
         <v>0.0</v>
@@ -1774,13 +1774,13 @@
         <v>42</v>
       </c>
       <c r="F61" t="n">
-        <v>172.0</v>
+        <v>173.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
       </c>
       <c r="H61" t="n">
-        <v>34.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="62">
@@ -2082,11 +2082,11 @@
       <c r="D73" t="s">
         <v>27</v>
       </c>
-      <c r="E73" t="e">
-        <v>#N/A</v>
+      <c r="E73" t="s">
+        <v>39</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G73" t="n">
         <v>1.0</v>
@@ -2109,10 +2109,10 @@
         <v>27</v>
       </c>
       <c r="E74" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F74" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2135,10 +2135,10 @@
         <v>27</v>
       </c>
       <c r="E75" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F75" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G75" t="n">
         <v>0.0</v>
@@ -2152,7 +2152,7 @@
         <v>8</v>
       </c>
       <c r="B76" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -2161,10 +2161,10 @@
         <v>27</v>
       </c>
       <c r="E76" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F76" t="n">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2187,10 +2187,10 @@
         <v>27</v>
       </c>
       <c r="E77" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F77" t="n">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -2213,10 +2213,10 @@
         <v>27</v>
       </c>
       <c r="E78" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F78" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G78" t="n">
         <v>0.0</v>
@@ -2239,10 +2239,10 @@
         <v>27</v>
       </c>
       <c r="E79" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F79" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2256,19 +2256,19 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C80" t="s">
         <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>27</v>
-      </c>
-      <c r="E80" t="s">
-        <v>42</v>
+        <v>28</v>
+      </c>
+      <c r="E80" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F80" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G80" t="n">
         <v>0.0</v>
@@ -2290,11 +2290,11 @@
       <c r="D81" t="s">
         <v>28</v>
       </c>
-      <c r="E81" t="e">
-        <v>#N/A</v>
+      <c r="E81" t="s">
+        <v>39</v>
       </c>
       <c r="F81" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2317,10 +2317,10 @@
         <v>28</v>
       </c>
       <c r="E82" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F82" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2334,7 +2334,7 @@
         <v>8</v>
       </c>
       <c r="B83" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C83" t="s">
         <v>14</v>
@@ -2343,13 +2343,13 @@
         <v>28</v>
       </c>
       <c r="E83" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F83" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H83" t="n">
         <v>0.0</v>
@@ -2369,10 +2369,10 @@
         <v>28</v>
       </c>
       <c r="E84" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="G84" t="n">
         <v>1.0</v>
@@ -2395,13 +2395,13 @@
         <v>28</v>
       </c>
       <c r="E85" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F85" t="n">
-        <v>8.0</v>
+        <v>28.0</v>
       </c>
       <c r="G85" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H85" t="n">
         <v>0.0</v>
@@ -2421,13 +2421,13 @@
         <v>28</v>
       </c>
       <c r="E86" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F86" t="n">
-        <v>28.0</v>
+        <v>0.0</v>
       </c>
       <c r="G86" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H86" t="n">
         <v>0.0</v>
@@ -2447,13 +2447,13 @@
         <v>28</v>
       </c>
       <c r="E87" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F87" t="n">
-        <v>0.0</v>
+        <v>33.0</v>
       </c>
       <c r="G87" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H87" t="n">
         <v>0.0</v>
@@ -2464,19 +2464,19 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E88" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F88" t="n">
-        <v>33.0</v>
+        <v>1.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2499,7 +2499,7 @@
         <v>29</v>
       </c>
       <c r="E89" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F89" t="n">
         <v>1.0</v>
@@ -2516,7 +2516,7 @@
         <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
@@ -2525,13 +2525,13 @@
         <v>29</v>
       </c>
       <c r="E90" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F90" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H90" t="n">
         <v>0.0</v>
@@ -2551,16 +2551,16 @@
         <v>29</v>
       </c>
       <c r="E91" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="G91" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="92">
@@ -2577,16 +2577,16 @@
         <v>29</v>
       </c>
       <c r="E92" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F92" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="G92" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H92" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="93">
@@ -2603,16 +2603,16 @@
         <v>29</v>
       </c>
       <c r="E93" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F93" t="n">
-        <v>5.0</v>
+        <v>43.0</v>
       </c>
       <c r="G93" t="n">
         <v>0.0</v>
       </c>
       <c r="H93" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="94">
@@ -2629,16 +2629,16 @@
         <v>29</v>
       </c>
       <c r="E94" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F94" t="n">
-        <v>43.0</v>
+        <v>12.0</v>
       </c>
       <c r="G94" t="n">
         <v>0.0</v>
       </c>
       <c r="H94" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="95">
@@ -2646,25 +2646,25 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C95" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D95" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E95" t="s">
         <v>41</v>
       </c>
       <c r="F95" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
       </c>
       <c r="H95" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="96">
@@ -2681,7 +2681,7 @@
         <v>30</v>
       </c>
       <c r="E96" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F96" t="n">
         <v>1.0</v>
@@ -2698,7 +2698,7 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C97" t="s">
         <v>15</v>
@@ -2707,13 +2707,13 @@
         <v>30</v>
       </c>
       <c r="E97" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F97" t="n">
-        <v>1.0</v>
+        <v>34.0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -2733,13 +2733,13 @@
         <v>30</v>
       </c>
       <c r="E98" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F98" t="n">
-        <v>34.0</v>
+        <v>8.0</v>
       </c>
       <c r="G98" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H98" t="n">
         <v>0.0</v>
@@ -2759,13 +2759,13 @@
         <v>30</v>
       </c>
       <c r="E99" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F99" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="G99" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H99" t="n">
         <v>0.0</v>
@@ -2776,7 +2776,7 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C100" t="s">
         <v>15</v>
@@ -2785,10 +2785,10 @@
         <v>30</v>
       </c>
       <c r="E100" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F100" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
@@ -2802,22 +2802,22 @@
         <v>8</v>
       </c>
       <c r="B101" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C101" t="s">
         <v>15</v>
       </c>
       <c r="D101" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E101" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F101" t="n">
         <v>1.0</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -2837,13 +2837,13 @@
         <v>31</v>
       </c>
       <c r="E102" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F102" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G102" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2863,13 +2863,13 @@
         <v>31</v>
       </c>
       <c r="E103" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F103" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G103" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H103" t="n">
         <v>0.0</v>
@@ -2880,7 +2880,7 @@
         <v>8</v>
       </c>
       <c r="B104" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C104" t="s">
         <v>15</v>
@@ -2889,10 +2889,10 @@
         <v>31</v>
       </c>
       <c r="E104" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F104" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -2915,16 +2915,16 @@
         <v>31</v>
       </c>
       <c r="E105" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F105" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="106">
@@ -2941,16 +2941,16 @@
         <v>31</v>
       </c>
       <c r="E106" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F106" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G106" t="n">
         <v>0.0</v>
       </c>
       <c r="H106" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="107">
@@ -2958,7 +2958,7 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C107" t="s">
         <v>15</v>
@@ -2966,14 +2966,14 @@
       <c r="D107" t="s">
         <v>31</v>
       </c>
-      <c r="E107" t="s">
-        <v>42</v>
+      <c r="E107" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F107" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H107" t="n">
         <v>0.0</v>
@@ -2992,14 +2992,14 @@
       <c r="D108" t="s">
         <v>31</v>
       </c>
-      <c r="E108" t="e">
-        <v>#N/A</v>
+      <c r="E108" t="s">
+        <v>39</v>
       </c>
       <c r="F108" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G108" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H108" t="n">
         <v>0.0</v>
@@ -3019,13 +3019,13 @@
         <v>31</v>
       </c>
       <c r="E109" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F109" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="G109" t="n">
         <v>4.0</v>
-      </c>
-      <c r="G109" t="n">
-        <v>2.0</v>
       </c>
       <c r="H109" t="n">
         <v>0.0</v>
@@ -3045,13 +3045,13 @@
         <v>31</v>
       </c>
       <c r="E110" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F110" t="n">
-        <v>6.0</v>
+        <v>17.0</v>
       </c>
       <c r="G110" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="H110" t="n">
         <v>0.0</v>
@@ -3062,22 +3062,22 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C111" t="s">
         <v>15</v>
       </c>
       <c r="D111" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E111" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F111" t="n">
-        <v>17.0</v>
+        <v>2.0</v>
       </c>
       <c r="G111" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3097,13 +3097,13 @@
         <v>32</v>
       </c>
       <c r="E112" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F112" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G112" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G112" t="n">
-        <v>1.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3123,13 +3123,13 @@
         <v>32</v>
       </c>
       <c r="E113" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F113" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G113" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H113" t="n">
         <v>0.0</v>
@@ -3140,7 +3140,7 @@
         <v>8</v>
       </c>
       <c r="B114" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C114" t="s">
         <v>15</v>
@@ -3149,13 +3149,13 @@
         <v>32</v>
       </c>
       <c r="E114" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F114" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3174,8 +3174,8 @@
       <c r="D115" t="s">
         <v>32</v>
       </c>
-      <c r="E115" t="s">
-        <v>44</v>
+      <c r="E115" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F115" t="n">
         <v>0.0</v>
@@ -3184,7 +3184,7 @@
         <v>1.0</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="116">
@@ -3200,17 +3200,17 @@
       <c r="D116" t="s">
         <v>32</v>
       </c>
-      <c r="E116" t="e">
-        <v>#N/A</v>
+      <c r="E116" t="s">
+        <v>39</v>
       </c>
       <c r="F116" t="n">
-        <v>0.0</v>
+        <v>90.0</v>
       </c>
       <c r="G116" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="H116" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="117">
@@ -3227,13 +3227,13 @@
         <v>32</v>
       </c>
       <c r="E117" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F117" t="n">
-        <v>90.0</v>
+        <v>28.0</v>
       </c>
       <c r="G117" t="n">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3253,16 +3253,16 @@
         <v>32</v>
       </c>
       <c r="E118" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F118" t="n">
-        <v>28.0</v>
+        <v>532.0</v>
       </c>
       <c r="G118" t="n">
-        <v>14.0</v>
+        <v>8.0</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="119">
@@ -3279,16 +3279,16 @@
         <v>32</v>
       </c>
       <c r="E119" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F119" t="n">
-        <v>532.0</v>
+        <v>0.0</v>
       </c>
       <c r="G119" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="H119" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="120">
@@ -3296,22 +3296,22 @@
         <v>8</v>
       </c>
       <c r="B120" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C120" t="s">
         <v>15</v>
       </c>
       <c r="D120" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E120" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F120" t="n">
         <v>0.0</v>
       </c>
       <c r="G120" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H120" t="n">
         <v>0.0</v>
@@ -3331,13 +3331,13 @@
         <v>33</v>
       </c>
       <c r="E121" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G121" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H121" t="n">
         <v>0.0</v>
@@ -3348,7 +3348,7 @@
         <v>8</v>
       </c>
       <c r="B122" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C122" t="s">
         <v>15</v>
@@ -3356,14 +3356,14 @@
       <c r="D122" t="s">
         <v>33</v>
       </c>
-      <c r="E122" t="s">
-        <v>42</v>
+      <c r="E122" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F122" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3382,14 +3382,14 @@
       <c r="D123" t="s">
         <v>33</v>
       </c>
-      <c r="E123" t="e">
-        <v>#N/A</v>
+      <c r="E123" t="s">
+        <v>41</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G123" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>
@@ -3400,7 +3400,7 @@
         <v>8</v>
       </c>
       <c r="B124" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C124" t="s">
         <v>15</v>
@@ -3409,13 +3409,13 @@
         <v>33</v>
       </c>
       <c r="E124" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F124" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>
@@ -3435,13 +3435,13 @@
         <v>33</v>
       </c>
       <c r="E125" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G125" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3461,10 +3461,10 @@
         <v>33</v>
       </c>
       <c r="E126" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F126" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="G126" t="n">
         <v>2.0</v>
@@ -3486,14 +3486,14 @@
       <c r="D127" t="s">
         <v>33</v>
       </c>
-      <c r="E127" t="s">
-        <v>42</v>
+      <c r="E127" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F127" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
       <c r="G127" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H127" t="n">
         <v>0.0</v>
@@ -3504,19 +3504,19 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C128" t="s">
         <v>15</v>
       </c>
       <c r="D128" t="s">
-        <v>33</v>
-      </c>
-      <c r="E128" t="e">
-        <v>#N/A</v>
+        <v>34</v>
+      </c>
+      <c r="E128" t="s">
+        <v>41</v>
       </c>
       <c r="F128" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G128" t="n">
         <v>0.0</v>
@@ -3530,7 +3530,7 @@
         <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C129" t="s">
         <v>15</v>
@@ -3542,7 +3542,7 @@
         <v>41</v>
       </c>
       <c r="F129" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G129" t="n">
         <v>0.0</v>
@@ -3556,7 +3556,7 @@
         <v>8</v>
       </c>
       <c r="B130" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C130" t="s">
         <v>15</v>
@@ -3565,10 +3565,10 @@
         <v>34</v>
       </c>
       <c r="E130" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F130" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G130" t="n">
         <v>0.0</v>
@@ -3591,16 +3591,16 @@
         <v>34</v>
       </c>
       <c r="E131" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F131" t="n">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
       <c r="G131" t="n">
         <v>0.0</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="132">
@@ -3617,16 +3617,16 @@
         <v>34</v>
       </c>
       <c r="E132" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F132" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="G132" t="n">
         <v>0.0</v>
       </c>
       <c r="H132" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="133">
@@ -3634,22 +3634,22 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C133" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D133" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E133" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F133" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H133" t="n">
         <v>0.0</v>
@@ -3669,10 +3669,10 @@
         <v>35</v>
       </c>
       <c r="E134" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G134" t="n">
         <v>1.0</v>
@@ -3695,10 +3695,10 @@
         <v>35</v>
       </c>
       <c r="E135" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F135" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="G135" t="n">
         <v>1.0</v>
@@ -3721,13 +3721,13 @@
         <v>35</v>
       </c>
       <c r="E136" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F136" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G136" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H136" t="n">
         <v>0.0</v>
@@ -3738,7 +3738,7 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C137" t="s">
         <v>16</v>
@@ -3747,13 +3747,13 @@
         <v>35</v>
       </c>
       <c r="E137" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F137" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3773,13 +3773,13 @@
         <v>35</v>
       </c>
       <c r="E138" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F138" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G138" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3799,13 +3799,13 @@
         <v>35</v>
       </c>
       <c r="E139" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F139" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G139" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3825,7 +3825,7 @@
         <v>35</v>
       </c>
       <c r="E140" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F140" t="n">
         <v>2.0</v>
@@ -3842,7 +3842,7 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C141" t="s">
         <v>16</v>
@@ -3850,11 +3850,11 @@
       <c r="D141" t="s">
         <v>35</v>
       </c>
-      <c r="E141" t="s">
-        <v>42</v>
+      <c r="E141" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F141" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G141" t="n">
         <v>0.0</v>
@@ -3876,11 +3876,11 @@
       <c r="D142" t="s">
         <v>35</v>
       </c>
-      <c r="E142" t="e">
-        <v>#N/A</v>
+      <c r="E142" t="s">
+        <v>40</v>
       </c>
       <c r="F142" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G142" t="n">
         <v>0.0</v>
@@ -3903,7 +3903,7 @@
         <v>35</v>
       </c>
       <c r="E143" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F143" t="n">
         <v>10.0</v>
@@ -3929,10 +3929,10 @@
         <v>35</v>
       </c>
       <c r="E144" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F144" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G144" t="n">
         <v>0.0</v>
@@ -3946,22 +3946,22 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C145" t="s">
         <v>16</v>
       </c>
       <c r="D145" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E145" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F145" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H145" t="n">
         <v>0.0</v>
@@ -3981,13 +3981,13 @@
         <v>36</v>
       </c>
       <c r="E146" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F146" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G146" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4007,13 +4007,13 @@
         <v>36</v>
       </c>
       <c r="E147" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F147" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G147" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4033,13 +4033,13 @@
         <v>36</v>
       </c>
       <c r="E148" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F148" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G148" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4059,10 +4059,10 @@
         <v>36</v>
       </c>
       <c r="E149" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F149" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G149" t="n">
         <v>0.0</v>
@@ -4085,10 +4085,10 @@
         <v>36</v>
       </c>
       <c r="E150" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F150" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G150" t="n">
         <v>0.0</v>
@@ -4102,19 +4102,19 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C151" t="s">
         <v>16</v>
       </c>
       <c r="D151" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E151" t="s">
         <v>42</v>
       </c>
       <c r="F151" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G151" t="n">
         <v>0.0</v>
@@ -4128,22 +4128,22 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C152" t="s">
         <v>16</v>
       </c>
       <c r="D152" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E152" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F152" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G152" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4163,13 +4163,13 @@
         <v>38</v>
       </c>
       <c r="E153" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F153" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G153" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H153" t="n">
         <v>0.0</v>
@@ -4180,7 +4180,7 @@
         <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C154" t="s">
         <v>16</v>
@@ -4206,7 +4206,7 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C155" t="s">
         <v>16</v>
@@ -4215,13 +4215,13 @@
         <v>38</v>
       </c>
       <c r="E155" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F155" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H155" t="n">
         <v>0.0</v>
@@ -4241,13 +4241,13 @@
         <v>38</v>
       </c>
       <c r="E156" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F156" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G156" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H156" t="n">
         <v>0.0</v>
@@ -4267,13 +4267,13 @@
         <v>38</v>
       </c>
       <c r="E157" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F157" t="n">
         <v>1.0</v>
       </c>
       <c r="G157" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H157" t="n">
         <v>0.0</v>
@@ -4293,13 +4293,13 @@
         <v>38</v>
       </c>
       <c r="E158" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F158" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G158" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H158" t="n">
         <v>0.0</v>
@@ -4319,13 +4319,13 @@
         <v>38</v>
       </c>
       <c r="E159" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F159" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="G159" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H159" t="n">
         <v>0.0</v>
@@ -4345,41 +4345,15 @@
         <v>38</v>
       </c>
       <c r="E160" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F160" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="G160" t="n">
         <v>1.0</v>
       </c>
       <c r="H160" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>8</v>
-      </c>
-      <c r="B161" t="s">
-        <v>9</v>
-      </c>
-      <c r="C161" t="s">
-        <v>16</v>
-      </c>
-      <c r="D161" t="s">
-        <v>38</v>
-      </c>
-      <c r="E161" t="s">
-        <v>43</v>
-      </c>
-      <c r="F161" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G161" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H161" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -604,7 +604,7 @@
         <v>39</v>
       </c>
       <c r="F16" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="G16" t="n">
         <v>1.0</v>
@@ -3256,7 +3256,7 @@
         <v>42</v>
       </c>
       <c r="F118" t="n">
-        <v>532.0</v>
+        <v>531.0</v>
       </c>
       <c r="G118" t="n">
         <v>8.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1176,7 +1176,7 @@
         <v>39</v>
       </c>
       <c r="F38" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G38" t="n">
         <v>4.0</v>
@@ -1228,7 +1228,7 @@
         <v>42</v>
       </c>
       <c r="F40" t="n">
-        <v>131.0</v>
+        <v>130.0</v>
       </c>
       <c r="G40" t="n">
         <v>1.0</v>
@@ -2840,7 +2840,7 @@
         <v>41</v>
       </c>
       <c r="F102" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G102" t="n">
         <v>2.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="46">
   <si>
     <t>Area</t>
   </si>
@@ -367,10 +367,10 @@
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F7" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G7" t="n">
         <v>0.0</v>
@@ -393,10 +393,10 @@
         <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F8" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G8" t="n">
         <v>0.0</v>
@@ -410,7 +410,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
@@ -419,13 +419,13 @@
         <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H9" t="n">
         <v>0.0</v>
@@ -436,7 +436,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
@@ -448,10 +448,10 @@
         <v>39</v>
       </c>
       <c r="F10" t="n">
-        <v>28.0</v>
+        <v>0.0</v>
       </c>
       <c r="G10" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H10" t="n">
         <v>0.0</v>
@@ -462,7 +462,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -471,13 +471,13 @@
         <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H11" t="n">
         <v>0.0</v>
@@ -488,7 +488,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
@@ -497,10 +497,10 @@
         <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F12" t="n">
-        <v>35.0</v>
+        <v>2.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -523,13 +523,13 @@
         <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F13" t="n">
-        <v>79.0</v>
+        <v>26.0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H13" t="n">
         <v>0.0</v>
@@ -540,22 +540,22 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F14" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H14" t="n">
         <v>0.0</v>
@@ -566,19 +566,19 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F15" t="n">
-        <v>13.0</v>
+        <v>32.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -592,22 +592,22 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F16" t="n">
-        <v>7.0</v>
+        <v>68.0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H16" t="n">
         <v>0.0</v>
@@ -618,7 +618,7 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
@@ -627,13 +627,13 @@
         <v>19</v>
       </c>
       <c r="E17" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F17" t="n">
-        <v>11.0</v>
+        <v>2.0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H17" t="n">
         <v>0.0</v>
@@ -644,7 +644,7 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="s">
         <v>12</v>
@@ -653,10 +653,10 @@
         <v>19</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="G18" t="n">
         <v>0.0</v>
@@ -678,14 +678,14 @@
       <c r="D19" t="s">
         <v>19</v>
       </c>
-      <c r="E19" t="e">
-        <v>#N/A</v>
+      <c r="E19" t="s">
+        <v>39</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H19" t="n">
         <v>0.0</v>
@@ -705,13 +705,13 @@
         <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F20" t="n">
-        <v>19.0</v>
+        <v>11.0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H20" t="n">
         <v>0.0</v>
@@ -722,7 +722,7 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
@@ -731,7 +731,7 @@
         <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F21" t="n">
         <v>1.0</v>
@@ -748,7 +748,7 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
@@ -756,11 +756,11 @@
       <c r="D22" t="s">
         <v>19</v>
       </c>
-      <c r="E22" t="s">
-        <v>42</v>
+      <c r="E22" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F22" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -774,22 +774,22 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0</v>
+        <v>23.0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H23" t="n">
         <v>0.0</v>
@@ -809,13 +809,13 @@
         <v>20</v>
       </c>
       <c r="E24" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F24" t="n">
-        <v>13.0</v>
+        <v>3.0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H24" t="n">
         <v>0.0</v>
@@ -835,10 +835,10 @@
         <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F25" t="n">
-        <v>19.0</v>
+        <v>12.0</v>
       </c>
       <c r="G25" t="n">
         <v>0.0</v>
@@ -852,7 +852,7 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
@@ -861,13 +861,13 @@
         <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F26" t="n">
-        <v>1.0</v>
+        <v>20.0</v>
       </c>
       <c r="G26" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H26" t="n">
         <v>0.0</v>
@@ -887,13 +887,13 @@
         <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F27" t="n">
-        <v>21.0</v>
+        <v>1.0</v>
       </c>
       <c r="G27" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H27" t="n">
         <v>0.0</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0</v>
+        <v>23.0</v>
       </c>
       <c r="G28" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H28" t="n">
         <v>0.0</v>
@@ -939,13 +939,13 @@
         <v>20</v>
       </c>
       <c r="E29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F29" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H29" t="n">
         <v>0.0</v>
@@ -956,7 +956,7 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
@@ -965,10 +965,10 @@
         <v>20</v>
       </c>
       <c r="E30" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F30" t="n">
-        <v>4.0</v>
+        <v>15.0</v>
       </c>
       <c r="G30" t="n">
         <v>0.0</v>
@@ -991,7 +991,7 @@
         <v>20</v>
       </c>
       <c r="E31" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F31" t="n">
         <v>3.0</v>
@@ -1017,10 +1017,10 @@
         <v>20</v>
       </c>
       <c r="E32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F32" t="n">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -1034,22 +1034,22 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="G33" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H33" t="n">
         <v>0.0</v>
@@ -1069,13 +1069,13 @@
         <v>21</v>
       </c>
       <c r="E34" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F34" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H34" t="n">
         <v>0.0</v>
@@ -1098,10 +1098,10 @@
         <v>42</v>
       </c>
       <c r="F35" t="n">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H35" t="n">
         <v>0.0</v>
@@ -1112,7 +1112,7 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C36" t="s">
         <v>12</v>
@@ -1121,10 +1121,10 @@
         <v>21</v>
       </c>
       <c r="E36" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F36" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G36" t="n">
         <v>1.0</v>
@@ -1138,7 +1138,7 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C37" t="s">
         <v>12</v>
@@ -1147,13 +1147,13 @@
         <v>21</v>
       </c>
       <c r="E37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G37" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H37" t="n">
         <v>0.0</v>
@@ -1164,7 +1164,7 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
@@ -1176,10 +1176,10 @@
         <v>39</v>
       </c>
       <c r="F38" t="n">
-        <v>15.0</v>
+        <v>2.0</v>
       </c>
       <c r="G38" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H38" t="n">
         <v>0.0</v>
@@ -1190,7 +1190,7 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C39" t="s">
         <v>12</v>
@@ -1199,10 +1199,10 @@
         <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F39" t="n">
-        <v>23.0</v>
+        <v>2.0</v>
       </c>
       <c r="G39" t="n">
         <v>1.0</v>
@@ -1216,7 +1216,7 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C40" t="s">
         <v>12</v>
@@ -1225,13 +1225,13 @@
         <v>21</v>
       </c>
       <c r="E40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F40" t="n">
-        <v>130.0</v>
+        <v>1.0</v>
       </c>
       <c r="G40" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H40" t="n">
         <v>0.0</v>
@@ -1251,10 +1251,10 @@
         <v>21</v>
       </c>
       <c r="E41" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="G41" t="n">
         <v>1.0</v>
@@ -1268,22 +1268,22 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E42" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F42" t="n">
-        <v>4.0</v>
+        <v>18.0</v>
       </c>
       <c r="G42" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H42" t="n">
         <v>0.0</v>
@@ -1294,22 +1294,22 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D43" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E43" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F43" t="n">
-        <v>23.0</v>
+        <v>119.0</v>
       </c>
       <c r="G43" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H43" t="n">
         <v>0.0</v>
@@ -1329,13 +1329,13 @@
         <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H44" t="n">
         <v>0.0</v>
@@ -1355,13 +1355,13 @@
         <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F45" t="n">
-        <v>1.0</v>
+        <v>23.0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H45" t="n">
         <v>0.0</v>
@@ -1378,10 +1378,10 @@
         <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E46" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F46" t="n">
         <v>0.0</v>
@@ -1404,19 +1404,19 @@
         <v>13</v>
       </c>
       <c r="D47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E47" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F47" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G47" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H47" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="48">
@@ -1433,7 +1433,7 @@
         <v>23</v>
       </c>
       <c r="E48" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F48" t="n">
         <v>0.0</v>
@@ -1459,16 +1459,16 @@
         <v>23</v>
       </c>
       <c r="E49" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G49" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="50">
@@ -1485,13 +1485,13 @@
         <v>23</v>
       </c>
       <c r="E50" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F50" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -1502,22 +1502,22 @@
         <v>8</v>
       </c>
       <c r="B51" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C51" t="s">
         <v>13</v>
       </c>
       <c r="D51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E51" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F51" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G51" t="n">
         <v>3.0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.0</v>
       </c>
       <c r="H51" t="n">
         <v>0.0</v>
@@ -1534,16 +1534,16 @@
         <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E52" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G52" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H52" t="n">
         <v>0.0</v>
@@ -1554,7 +1554,7 @@
         <v>8</v>
       </c>
       <c r="B53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C53" t="s">
         <v>13</v>
@@ -1563,7 +1563,7 @@
         <v>24</v>
       </c>
       <c r="E53" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F53" t="n">
         <v>3.0</v>
@@ -1589,13 +1589,13 @@
         <v>24</v>
       </c>
       <c r="E54" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F54" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H54" t="n">
         <v>0.0</v>
@@ -1606,7 +1606,7 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C55" t="s">
         <v>13</v>
@@ -1615,13 +1615,13 @@
         <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G55" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H55" t="n">
         <v>0.0</v>
@@ -1632,7 +1632,7 @@
         <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C56" t="s">
         <v>13</v>
@@ -1641,10 +1641,10 @@
         <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F56" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1667,13 +1667,13 @@
         <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F57" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H57" t="n">
         <v>0.0</v>
@@ -1693,10 +1693,10 @@
         <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F58" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
@@ -1713,22 +1713,22 @@
         <v>9</v>
       </c>
       <c r="C59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F59" t="n">
-        <v>39.0</v>
+        <v>9.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
       </c>
       <c r="H59" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="60">
@@ -1739,22 +1739,22 @@
         <v>9</v>
       </c>
       <c r="C60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F60" t="n">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
       </c>
       <c r="H60" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="61">
@@ -1771,16 +1771,16 @@
         <v>25</v>
       </c>
       <c r="E61" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F61" t="n">
-        <v>173.0</v>
+        <v>39.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
       </c>
       <c r="H61" t="n">
-        <v>33.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="62">
@@ -1788,25 +1788,25 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E62" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F62" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="63">
@@ -1814,25 +1814,25 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C63" t="s">
         <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E63" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F63" t="n">
-        <v>2.0</v>
+        <v>173.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="64">
@@ -1849,10 +1849,10 @@
         <v>26</v>
       </c>
       <c r="E64" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F64" t="n">
-        <v>38.0</v>
+        <v>1.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1866,7 +1866,7 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
@@ -1875,10 +1875,10 @@
         <v>26</v>
       </c>
       <c r="E65" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F65" t="n">
-        <v>19.0</v>
+        <v>2.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1901,10 +1901,10 @@
         <v>26</v>
       </c>
       <c r="E66" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F66" t="n">
-        <v>1.0</v>
+        <v>35.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1927,10 +1927,10 @@
         <v>26</v>
       </c>
       <c r="E67" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F67" t="n">
-        <v>30.0</v>
+        <v>3.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1944,22 +1944,22 @@
         <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C68" t="s">
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>27</v>
-      </c>
-      <c r="E68" t="e">
-        <v>#N/A</v>
+        <v>26</v>
+      </c>
+      <c r="E68" t="s">
+        <v>42</v>
       </c>
       <c r="F68" t="n">
-        <v>0.0</v>
+        <v>66.0</v>
       </c>
       <c r="G68" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H68" t="n">
         <v>0.0</v>
@@ -1970,7 +1970,7 @@
         <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
@@ -1978,11 +1978,11 @@
       <c r="D69" t="s">
         <v>27</v>
       </c>
-      <c r="E69" t="s">
-        <v>42</v>
+      <c r="E69" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F69" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G69" t="n">
         <v>1.0</v>
@@ -1996,7 +1996,7 @@
         <v>8</v>
       </c>
       <c r="B70" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
@@ -2008,10 +2008,10 @@
         <v>39</v>
       </c>
       <c r="F70" t="n">
-        <v>5.0</v>
+        <v>18.0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H70" t="n">
         <v>0.0</v>
@@ -2022,7 +2022,7 @@
         <v>8</v>
       </c>
       <c r="B71" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
@@ -2031,16 +2031,16 @@
         <v>27</v>
       </c>
       <c r="E71" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F71" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H71" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="72">
@@ -2048,7 +2048,7 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C72" t="s">
         <v>14</v>
@@ -2057,13 +2057,13 @@
         <v>27</v>
       </c>
       <c r="E72" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F72" t="n">
-        <v>4.0</v>
+        <v>17.0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H72" t="n">
         <v>0.0</v>
@@ -2074,7 +2074,7 @@
         <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C73" t="s">
         <v>14</v>
@@ -2083,16 +2083,16 @@
         <v>27</v>
       </c>
       <c r="E73" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F73" t="n">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
       <c r="G73" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="74">
@@ -2100,19 +2100,19 @@
         <v>8</v>
       </c>
       <c r="B74" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E74" t="s">
         <v>41</v>
       </c>
       <c r="F74" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2126,16 +2126,16 @@
         <v>8</v>
       </c>
       <c r="B75" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C75" t="s">
         <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>27</v>
-      </c>
-      <c r="E75" t="s">
-        <v>42</v>
+        <v>28</v>
+      </c>
+      <c r="E75" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F75" t="n">
         <v>1.0</v>
@@ -2152,19 +2152,19 @@
         <v>8</v>
       </c>
       <c r="B76" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E76" t="s">
         <v>39</v>
       </c>
       <c r="F76" t="n">
-        <v>11.0</v>
+        <v>2.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2178,19 +2178,19 @@
         <v>8</v>
       </c>
       <c r="B77" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C77" t="s">
         <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E77" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F77" t="n">
-        <v>3.0</v>
+        <v>18.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -2204,22 +2204,22 @@
         <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E78" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F78" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H78" t="n">
         <v>0.0</v>
@@ -2230,22 +2230,22 @@
         <v>8</v>
       </c>
       <c r="B79" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
       </c>
       <c r="D79" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E79" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F79" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H79" t="n">
         <v>0.0</v>
@@ -2256,7 +2256,7 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C80" t="s">
         <v>14</v>
@@ -2264,14 +2264,14 @@
       <c r="D80" t="s">
         <v>28</v>
       </c>
-      <c r="E80" t="e">
-        <v>#N/A</v>
+      <c r="E80" t="s">
+        <v>43</v>
       </c>
       <c r="F80" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H80" t="n">
         <v>0.0</v>
@@ -2282,7 +2282,7 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C81" t="s">
         <v>14</v>
@@ -2291,10 +2291,10 @@
         <v>28</v>
       </c>
       <c r="E81" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F81" t="n">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2308,7 +2308,7 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C82" t="s">
         <v>14</v>
@@ -2320,7 +2320,7 @@
         <v>42</v>
       </c>
       <c r="F82" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2334,7 +2334,7 @@
         <v>8</v>
       </c>
       <c r="B83" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C83" t="s">
         <v>14</v>
@@ -2343,10 +2343,10 @@
         <v>28</v>
       </c>
       <c r="E83" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="G83" t="n">
         <v>1.0</v>
@@ -2360,7 +2360,7 @@
         <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C84" t="s">
         <v>14</v>
@@ -2375,7 +2375,7 @@
         <v>8.0</v>
       </c>
       <c r="G84" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H84" t="n">
         <v>0.0</v>
@@ -2386,7 +2386,7 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C85" t="s">
         <v>14</v>
@@ -2395,13 +2395,13 @@
         <v>28</v>
       </c>
       <c r="E85" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F85" t="n">
-        <v>28.0</v>
+        <v>16.0</v>
       </c>
       <c r="G85" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H85" t="n">
         <v>0.0</v>
@@ -2412,16 +2412,16 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C86" t="s">
         <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E86" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F86" t="n">
         <v>0.0</v>
@@ -2438,25 +2438,25 @@
         <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E87" t="s">
         <v>42</v>
       </c>
       <c r="F87" t="n">
-        <v>33.0</v>
+        <v>9.0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="88">
@@ -2464,7 +2464,7 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
@@ -2473,16 +2473,16 @@
         <v>29</v>
       </c>
       <c r="E88" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F88" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="89">
@@ -2490,7 +2490,7 @@
         <v>8</v>
       </c>
       <c r="B89" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
@@ -2499,16 +2499,16 @@
         <v>29</v>
       </c>
       <c r="E89" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F89" t="n">
-        <v>1.0</v>
+        <v>44.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="90">
@@ -2525,16 +2525,16 @@
         <v>29</v>
       </c>
       <c r="E90" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="G90" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="91">
@@ -2542,25 +2542,25 @@
         <v>8</v>
       </c>
       <c r="B91" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C91" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D91" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E91" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F91" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
       <c r="G91" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H91" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="92">
@@ -2568,16 +2568,16 @@
         <v>8</v>
       </c>
       <c r="B92" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C92" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D92" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E92" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F92" t="n">
         <v>5.0</v>
@@ -2586,7 +2586,7 @@
         <v>0.0</v>
       </c>
       <c r="H92" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="93">
@@ -2594,25 +2594,25 @@
         <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C93" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D93" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E93" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F93" t="n">
-        <v>43.0</v>
+        <v>2.0</v>
       </c>
       <c r="G93" t="n">
         <v>0.0</v>
       </c>
       <c r="H93" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="94">
@@ -2620,25 +2620,25 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C94" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D94" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E94" t="s">
         <v>41</v>
       </c>
       <c r="F94" t="n">
-        <v>12.0</v>
+        <v>28.0</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H94" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="95">
@@ -2646,7 +2646,7 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C95" t="s">
         <v>15</v>
@@ -2655,13 +2655,13 @@
         <v>30</v>
       </c>
       <c r="E95" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F95" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H95" t="n">
         <v>0.0</v>
@@ -2672,7 +2672,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C96" t="s">
         <v>15</v>
@@ -2681,7 +2681,7 @@
         <v>30</v>
       </c>
       <c r="E96" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F96" t="n">
         <v>1.0</v>
@@ -2698,7 +2698,7 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C97" t="s">
         <v>15</v>
@@ -2710,10 +2710,10 @@
         <v>41</v>
       </c>
       <c r="F97" t="n">
-        <v>34.0</v>
+        <v>3.0</v>
       </c>
       <c r="G97" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -2724,7 +2724,7 @@
         <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C98" t="s">
         <v>15</v>
@@ -2736,10 +2736,10 @@
         <v>42</v>
       </c>
       <c r="F98" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="G98" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H98" t="n">
         <v>0.0</v>
@@ -2750,22 +2750,22 @@
         <v>8</v>
       </c>
       <c r="B99" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C99" t="s">
         <v>15</v>
       </c>
       <c r="D99" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E99" t="s">
         <v>39</v>
       </c>
       <c r="F99" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H99" t="n">
         <v>0.0</v>
@@ -2776,22 +2776,22 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C100" t="s">
         <v>15</v>
       </c>
       <c r="D100" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E100" t="s">
         <v>41</v>
       </c>
       <c r="F100" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2811,13 +2811,13 @@
         <v>31</v>
       </c>
       <c r="E101" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F101" t="n">
         <v>1.0</v>
       </c>
       <c r="G101" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -2828,7 +2828,7 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C102" t="s">
         <v>15</v>
@@ -2837,13 +2837,13 @@
         <v>31</v>
       </c>
       <c r="E102" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F102" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G102" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2854,7 +2854,7 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C103" t="s">
         <v>15</v>
@@ -2863,16 +2863,16 @@
         <v>31</v>
       </c>
       <c r="E103" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F103" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="104">
@@ -2889,7 +2889,7 @@
         <v>31</v>
       </c>
       <c r="E104" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F104" t="n">
         <v>1.0</v>
@@ -2906,7 +2906,7 @@
         <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C105" t="s">
         <v>15</v>
@@ -2914,17 +2914,17 @@
       <c r="D105" t="s">
         <v>31</v>
       </c>
-      <c r="E105" t="s">
-        <v>41</v>
+      <c r="E105" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F105" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H105" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="106">
@@ -2932,7 +2932,7 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C106" t="s">
         <v>15</v>
@@ -2941,13 +2941,13 @@
         <v>31</v>
       </c>
       <c r="E106" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F106" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H106" t="n">
         <v>0.0</v>
@@ -2966,14 +2966,14 @@
       <c r="D107" t="s">
         <v>31</v>
       </c>
-      <c r="E107" t="e">
-        <v>#N/A</v>
+      <c r="E107" t="s">
+        <v>41</v>
       </c>
       <c r="F107" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="G107" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H107" t="n">
         <v>0.0</v>
@@ -2993,10 +2993,10 @@
         <v>31</v>
       </c>
       <c r="E108" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F108" t="n">
-        <v>4.0</v>
+        <v>18.0</v>
       </c>
       <c r="G108" t="n">
         <v>2.0</v>
@@ -3010,22 +3010,22 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C109" t="s">
         <v>15</v>
       </c>
       <c r="D109" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E109" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F109" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G109" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H109" t="n">
         <v>0.0</v>
@@ -3036,19 +3036,19 @@
         <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C110" t="s">
         <v>15</v>
       </c>
       <c r="D110" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E110" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F110" t="n">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="G110" t="n">
         <v>2.0</v>
@@ -3071,13 +3071,13 @@
         <v>32</v>
       </c>
       <c r="E111" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F111" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G111" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3088,7 +3088,7 @@
         <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C112" t="s">
         <v>15</v>
@@ -3097,13 +3097,13 @@
         <v>32</v>
       </c>
       <c r="E112" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F112" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G112" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3114,7 +3114,7 @@
         <v>8</v>
       </c>
       <c r="B113" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C113" t="s">
         <v>15</v>
@@ -3122,17 +3122,17 @@
       <c r="D113" t="s">
         <v>32</v>
       </c>
-      <c r="E113" t="s">
-        <v>42</v>
+      <c r="E113" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F113" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H113" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="114">
@@ -3149,13 +3149,13 @@
         <v>32</v>
       </c>
       <c r="E114" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F114" t="n">
-        <v>0.0</v>
+        <v>90.0</v>
       </c>
       <c r="G114" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3174,17 +3174,17 @@
       <c r="D115" t="s">
         <v>32</v>
       </c>
-      <c r="E115" t="e">
-        <v>#N/A</v>
+      <c r="E115" t="s">
+        <v>41</v>
       </c>
       <c r="F115" t="n">
-        <v>0.0</v>
+        <v>28.0</v>
       </c>
       <c r="G115" t="n">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="H115" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="116">
@@ -3201,16 +3201,16 @@
         <v>32</v>
       </c>
       <c r="E116" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F116" t="n">
-        <v>90.0</v>
+        <v>531.0</v>
       </c>
       <c r="G116" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="117">
@@ -3227,13 +3227,13 @@
         <v>32</v>
       </c>
       <c r="E117" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F117" t="n">
-        <v>28.0</v>
+        <v>0.0</v>
       </c>
       <c r="G117" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3250,19 +3250,19 @@
         <v>15</v>
       </c>
       <c r="D118" t="s">
-        <v>32</v>
-      </c>
-      <c r="E118" t="s">
-        <v>42</v>
+        <v>33</v>
+      </c>
+      <c r="E118" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F118" t="n">
-        <v>531.0</v>
+        <v>1.0</v>
       </c>
       <c r="G118" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="H118" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="119">
@@ -3276,16 +3276,16 @@
         <v>15</v>
       </c>
       <c r="D119" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F119" t="n">
         <v>0.0</v>
       </c>
       <c r="G119" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H119" t="n">
         <v>0.0</v>
@@ -3296,7 +3296,7 @@
         <v>8</v>
       </c>
       <c r="B120" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C120" t="s">
         <v>15</v>
@@ -3308,10 +3308,10 @@
         <v>41</v>
       </c>
       <c r="F120" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="G120" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H120" t="n">
         <v>0.0</v>
@@ -3322,7 +3322,7 @@
         <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C121" t="s">
         <v>15</v>
@@ -3334,10 +3334,10 @@
         <v>42</v>
       </c>
       <c r="F121" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="G121" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G121" t="n">
-        <v>0.0</v>
       </c>
       <c r="H121" t="n">
         <v>0.0</v>
@@ -3348,22 +3348,22 @@
         <v>8</v>
       </c>
       <c r="B122" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C122" t="s">
         <v>15</v>
       </c>
       <c r="D122" t="s">
-        <v>33</v>
-      </c>
-      <c r="E122" t="e">
-        <v>#N/A</v>
+        <v>34</v>
+      </c>
+      <c r="E122" t="s">
+        <v>39</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="G122" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3374,25 +3374,25 @@
         <v>8</v>
       </c>
       <c r="B123" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C123" t="s">
         <v>15</v>
       </c>
       <c r="D123" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E123" t="s">
         <v>41</v>
       </c>
       <c r="F123" t="n">
-        <v>2.0</v>
+        <v>17.0</v>
       </c>
       <c r="G123" t="n">
         <v>0.0</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="124">
@@ -3406,16 +3406,16 @@
         <v>15</v>
       </c>
       <c r="D124" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E124" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="G124" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>
@@ -3426,22 +3426,22 @@
         <v>8</v>
       </c>
       <c r="B125" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C125" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D125" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E125" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F125" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G125" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3452,22 +3452,22 @@
         <v>8</v>
       </c>
       <c r="B126" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C126" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D126" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E126" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F126" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="G126" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>
@@ -3478,22 +3478,22 @@
         <v>8</v>
       </c>
       <c r="B127" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C127" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D127" t="s">
-        <v>33</v>
-      </c>
-      <c r="E127" t="e">
-        <v>#N/A</v>
+        <v>35</v>
+      </c>
+      <c r="E127" t="s">
+        <v>43</v>
       </c>
       <c r="F127" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H127" t="n">
         <v>0.0</v>
@@ -3507,16 +3507,16 @@
         <v>10</v>
       </c>
       <c r="C128" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D128" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E128" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F128" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G128" t="n">
         <v>0.0</v>
@@ -3533,19 +3533,19 @@
         <v>11</v>
       </c>
       <c r="C129" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D129" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E129" t="s">
         <v>41</v>
       </c>
       <c r="F129" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G129" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -3556,22 +3556,22 @@
         <v>8</v>
       </c>
       <c r="B130" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C130" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D130" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E130" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F130" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H130" t="n">
         <v>0.0</v>
@@ -3582,25 +3582,25 @@
         <v>8</v>
       </c>
       <c r="B131" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C131" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D131" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E131" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F131" t="n">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="G131" t="n">
         <v>0.0</v>
       </c>
       <c r="H131" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="132">
@@ -3608,19 +3608,19 @@
         <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C132" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D132" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E132" t="s">
         <v>42</v>
       </c>
       <c r="F132" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="G132" t="n">
         <v>0.0</v>
@@ -3634,7 +3634,7 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C133" t="s">
         <v>16</v>
@@ -3642,14 +3642,14 @@
       <c r="D133" t="s">
         <v>35</v>
       </c>
-      <c r="E133" t="s">
-        <v>39</v>
+      <c r="E133" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F133" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G133" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H133" t="n">
         <v>0.0</v>
@@ -3660,7 +3660,7 @@
         <v>8</v>
       </c>
       <c r="B134" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C134" t="s">
         <v>16</v>
@@ -3669,13 +3669,13 @@
         <v>35</v>
       </c>
       <c r="E134" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F134" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="G134" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H134" t="n">
         <v>0.0</v>
@@ -3686,7 +3686,7 @@
         <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C135" t="s">
         <v>16</v>
@@ -3695,13 +3695,13 @@
         <v>35</v>
       </c>
       <c r="E135" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="G135" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3712,7 +3712,7 @@
         <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C136" t="s">
         <v>16</v>
@@ -3724,7 +3724,7 @@
         <v>42</v>
       </c>
       <c r="F136" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G136" t="n">
         <v>0.0</v>
@@ -3744,16 +3744,16 @@
         <v>16</v>
       </c>
       <c r="D137" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F137" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G137" t="n">
         <v>3.0</v>
-      </c>
-      <c r="G137" t="n">
-        <v>4.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3770,16 +3770,16 @@
         <v>16</v>
       </c>
       <c r="D138" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E138" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F138" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G138" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3796,16 +3796,16 @@
         <v>16</v>
       </c>
       <c r="D139" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E139" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F139" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3822,13 +3822,13 @@
         <v>16</v>
       </c>
       <c r="D140" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E140" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F140" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G140" t="n">
         <v>0.0</v>
@@ -3842,19 +3842,19 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C141" t="s">
         <v>16</v>
       </c>
       <c r="D141" t="s">
-        <v>35</v>
-      </c>
-      <c r="E141" t="e">
-        <v>#N/A</v>
+        <v>36</v>
+      </c>
+      <c r="E141" t="s">
+        <v>40</v>
       </c>
       <c r="F141" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G141" t="n">
         <v>0.0</v>
@@ -3868,19 +3868,19 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C142" t="s">
         <v>16</v>
       </c>
       <c r="D142" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E142" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F142" t="n">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="G142" t="n">
         <v>0.0</v>
@@ -3900,13 +3900,13 @@
         <v>16</v>
       </c>
       <c r="D143" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E143" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F143" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G143" t="n">
         <v>0.0</v>
@@ -3920,22 +3920,22 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C144" t="s">
         <v>16</v>
       </c>
       <c r="D144" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E144" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F144" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3946,22 +3946,22 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C145" t="s">
         <v>16</v>
       </c>
       <c r="D145" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E145" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F145" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G145" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H145" t="n">
         <v>0.0</v>
@@ -3978,16 +3978,16 @@
         <v>16</v>
       </c>
       <c r="D146" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E146" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F146" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G146" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -3998,22 +3998,22 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C147" t="s">
         <v>16</v>
       </c>
       <c r="D147" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E147" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G147" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4024,13 +4024,13 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C148" t="s">
         <v>16</v>
       </c>
       <c r="D148" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E148" t="s">
         <v>44</v>
@@ -4039,7 +4039,7 @@
         <v>1.0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4050,22 +4050,22 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C149" t="s">
         <v>16</v>
       </c>
       <c r="D149" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E149" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F149" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4076,22 +4076,22 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C150" t="s">
         <v>16</v>
       </c>
       <c r="D150" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E150" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F150" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>
@@ -4108,16 +4108,16 @@
         <v>16</v>
       </c>
       <c r="D151" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E151" t="s">
         <v>42</v>
       </c>
       <c r="F151" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4128,7 +4128,7 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C152" t="s">
         <v>16</v>
@@ -4137,7 +4137,7 @@
         <v>38</v>
       </c>
       <c r="E152" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F152" t="n">
         <v>0.0</v>
@@ -4146,214 +4146,6 @@
         <v>1.0</v>
       </c>
       <c r="H152" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>8</v>
-      </c>
-      <c r="B153" t="s">
-        <v>10</v>
-      </c>
-      <c r="C153" t="s">
-        <v>16</v>
-      </c>
-      <c r="D153" t="s">
-        <v>38</v>
-      </c>
-      <c r="E153" t="s">
-        <v>40</v>
-      </c>
-      <c r="F153" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G153" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H153" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>8</v>
-      </c>
-      <c r="B154" t="s">
-        <v>11</v>
-      </c>
-      <c r="C154" t="s">
-        <v>16</v>
-      </c>
-      <c r="D154" t="s">
-        <v>38</v>
-      </c>
-      <c r="E154" t="s">
-        <v>40</v>
-      </c>
-      <c r="F154" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G154" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H154" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>8</v>
-      </c>
-      <c r="B155" t="s">
-        <v>9</v>
-      </c>
-      <c r="C155" t="s">
-        <v>16</v>
-      </c>
-      <c r="D155" t="s">
-        <v>38</v>
-      </c>
-      <c r="E155" t="s">
-        <v>45</v>
-      </c>
-      <c r="F155" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="G155" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="H155" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>8</v>
-      </c>
-      <c r="B156" t="s">
-        <v>9</v>
-      </c>
-      <c r="C156" t="s">
-        <v>16</v>
-      </c>
-      <c r="D156" t="s">
-        <v>38</v>
-      </c>
-      <c r="E156" t="s">
-        <v>44</v>
-      </c>
-      <c r="F156" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G156" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="H156" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>8</v>
-      </c>
-      <c r="B157" t="s">
-        <v>9</v>
-      </c>
-      <c r="C157" t="s">
-        <v>16</v>
-      </c>
-      <c r="D157" t="s">
-        <v>38</v>
-      </c>
-      <c r="E157" t="s">
-        <v>39</v>
-      </c>
-      <c r="F157" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G157" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H157" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>8</v>
-      </c>
-      <c r="B158" t="s">
-        <v>9</v>
-      </c>
-      <c r="C158" t="s">
-        <v>16</v>
-      </c>
-      <c r="D158" t="s">
-        <v>38</v>
-      </c>
-      <c r="E158" t="s">
-        <v>40</v>
-      </c>
-      <c r="F158" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="G158" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="H158" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>8</v>
-      </c>
-      <c r="B159" t="s">
-        <v>9</v>
-      </c>
-      <c r="C159" t="s">
-        <v>16</v>
-      </c>
-      <c r="D159" t="s">
-        <v>38</v>
-      </c>
-      <c r="E159" t="s">
-        <v>42</v>
-      </c>
-      <c r="F159" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="G159" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H159" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>8</v>
-      </c>
-      <c r="B160" t="s">
-        <v>9</v>
-      </c>
-      <c r="C160" t="s">
-        <v>16</v>
-      </c>
-      <c r="D160" t="s">
-        <v>38</v>
-      </c>
-      <c r="E160" t="s">
-        <v>43</v>
-      </c>
-      <c r="F160" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G160" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H160" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -604,7 +604,7 @@
         <v>42</v>
       </c>
       <c r="F16" t="n">
-        <v>68.0</v>
+        <v>67.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -1358,7 +1358,7 @@
         <v>41</v>
       </c>
       <c r="F45" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="G45" t="n">
         <v>3.0</v>
@@ -1826,13 +1826,13 @@
         <v>42</v>
       </c>
       <c r="F63" t="n">
-        <v>173.0</v>
+        <v>174.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
       </c>
       <c r="H63" t="n">
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="64">
@@ -3204,7 +3204,7 @@
         <v>42</v>
       </c>
       <c r="F116" t="n">
-        <v>531.0</v>
+        <v>530.0</v>
       </c>
       <c r="G116" t="n">
         <v>8.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -864,7 +864,7 @@
         <v>42</v>
       </c>
       <c r="F26" t="n">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="G26" t="n">
         <v>0.0</v>
@@ -1332,10 +1332,10 @@
         <v>45</v>
       </c>
       <c r="F44" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G44" t="n">
         <v>4.0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>2.0</v>
       </c>
       <c r="H44" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -864,7 +864,7 @@
         <v>42</v>
       </c>
       <c r="F26" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G26" t="n">
         <v>0.0</v>
@@ -3178,7 +3178,7 @@
         <v>41</v>
       </c>
       <c r="F115" t="n">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="G115" t="n">
         <v>14.0</v>
@@ -3204,7 +3204,7 @@
         <v>42</v>
       </c>
       <c r="F116" t="n">
-        <v>530.0</v>
+        <v>529.0</v>
       </c>
       <c r="G116" t="n">
         <v>8.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -968,7 +968,7 @@
         <v>42</v>
       </c>
       <c r="F30" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="G30" t="n">
         <v>0.0</v>
@@ -1774,7 +1774,7 @@
         <v>39</v>
       </c>
       <c r="F61" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1826,7 +1826,7 @@
         <v>42</v>
       </c>
       <c r="F63" t="n">
-        <v>172.0</v>
+        <v>171.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1956,7 +1956,7 @@
         <v>42</v>
       </c>
       <c r="F68" t="n">
-        <v>66.0</v>
+        <v>65.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2034,7 +2034,7 @@
         <v>41</v>
       </c>
       <c r="F71" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G71" t="n">
         <v>1.0</v>
@@ -2086,7 +2086,7 @@
         <v>40</v>
       </c>
       <c r="F73" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -2398,7 +2398,7 @@
         <v>42</v>
       </c>
       <c r="F85" t="n">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G85" t="n">
         <v>0.0</v>
@@ -3204,7 +3204,7 @@
         <v>42</v>
       </c>
       <c r="F116" t="n">
-        <v>529.0</v>
+        <v>528.0</v>
       </c>
       <c r="G116" t="n">
         <v>8.0</v>
@@ -3386,7 +3386,7 @@
         <v>41</v>
       </c>
       <c r="F123" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="G123" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -243,7 +243,7 @@
         <v>10.0</v>
       </c>
       <c r="G2" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="H2" t="n">
         <v>0.0</v>
@@ -838,7 +838,7 @@
         <v>41</v>
       </c>
       <c r="F25" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="G25" t="n">
         <v>0.0</v>
@@ -890,10 +890,10 @@
         <v>39</v>
       </c>
       <c r="F27" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G27" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H27" t="n">
         <v>0.0</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F28" t="n">
-        <v>23.0</v>
+        <v>0.0</v>
       </c>
       <c r="G28" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H28" t="n">
         <v>0.0</v>
@@ -939,13 +939,13 @@
         <v>20</v>
       </c>
       <c r="E29" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0</v>
+        <v>24.0</v>
       </c>
       <c r="G29" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H29" t="n">
         <v>0.0</v>
@@ -1826,13 +1826,13 @@
         <v>42</v>
       </c>
       <c r="F63" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
       </c>
       <c r="H63" t="n">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="64">
@@ -1956,7 +1956,7 @@
         <v>42</v>
       </c>
       <c r="F68" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2190,7 +2190,7 @@
         <v>42</v>
       </c>
       <c r="F77" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -2508,7 +2508,7 @@
         <v>0.0</v>
       </c>
       <c r="H89" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="90">
@@ -2996,7 +2996,7 @@
         <v>42</v>
       </c>
       <c r="F108" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G108" t="n">
         <v>2.0</v>
@@ -3204,7 +3204,7 @@
         <v>42</v>
       </c>
       <c r="F116" t="n">
-        <v>528.0</v>
+        <v>529.0</v>
       </c>
       <c r="G116" t="n">
         <v>8.0</v>
@@ -3334,7 +3334,7 @@
         <v>42</v>
       </c>
       <c r="F121" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="G121" t="n">
         <v>2.0</v>
@@ -3467,7 +3467,7 @@
         <v>6.0</v>
       </c>
       <c r="G126" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>
@@ -3642,14 +3642,14 @@
       <c r="D133" t="s">
         <v>35</v>
       </c>
-      <c r="E133" t="e">
-        <v>#N/A</v>
+      <c r="E133" t="s">
+        <v>41</v>
       </c>
       <c r="F133" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H133" t="n">
         <v>0.0</v>
@@ -3668,11 +3668,11 @@
       <c r="D134" t="s">
         <v>35</v>
       </c>
-      <c r="E134" t="s">
-        <v>40</v>
+      <c r="E134" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F134" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G134" t="n">
         <v>0.0</v>
@@ -3695,7 +3695,7 @@
         <v>35</v>
       </c>
       <c r="E135" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F135" t="n">
         <v>10.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1306,7 +1306,7 @@
         <v>42</v>
       </c>
       <c r="F43" t="n">
-        <v>119.0</v>
+        <v>118.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -2502,7 +2502,7 @@
         <v>40</v>
       </c>
       <c r="F89" t="n">
-        <v>44.0</v>
+        <v>43.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -292,7 +292,7 @@
         <v>41</v>
       </c>
       <c r="F4" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="G4" t="n">
         <v>3.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -942,7 +942,7 @@
         <v>41</v>
       </c>
       <c r="F29" t="n">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="G29" t="n">
         <v>0.0</v>
@@ -1306,7 +1306,7 @@
         <v>42</v>
       </c>
       <c r="F43" t="n">
-        <v>118.0</v>
+        <v>117.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3204,10 +3204,10 @@
         <v>42</v>
       </c>
       <c r="F116" t="n">
-        <v>529.0</v>
+        <v>530.0</v>
       </c>
       <c r="G116" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="H116" t="n">
         <v>1.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="47">
   <si>
     <t>Area</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t>II</t>
+  </si>
+  <si>
+    <t>III</t>
   </si>
   <si>
     <t>Emilia romagna</t>
@@ -231,13 +234,13 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
         <v>10.0</v>
@@ -257,13 +260,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F3" t="n">
         <v>18.0</v>
@@ -283,13 +286,13 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4" t="n">
         <v>9.0</v>
@@ -309,13 +312,13 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" t="n">
         <v>34.0</v>
@@ -335,13 +338,13 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F6" t="n">
         <v>1.0</v>
@@ -361,13 +364,13 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
         <v>2.0</v>
@@ -387,13 +390,13 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
         <v>6.0</v>
@@ -413,13 +416,13 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F9" t="n">
         <v>13.0</v>
@@ -439,13 +442,13 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
         <v>0.0</v>
@@ -465,13 +468,13 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F11" t="n">
         <v>1.0</v>
@@ -491,13 +494,13 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F12" t="n">
         <v>2.0</v>
@@ -517,13 +520,13 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="n">
         <v>26.0</v>
@@ -543,13 +546,13 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F14" t="n">
         <v>0.0</v>
@@ -569,13 +572,13 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="n">
         <v>32.0</v>
@@ -595,13 +598,13 @@
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="n">
         <v>67.0</v>
@@ -621,13 +624,13 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F17" t="n">
         <v>2.0</v>
@@ -647,16 +650,16 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F18" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="G18" t="n">
         <v>0.0</v>
@@ -673,13 +676,13 @@
         <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F19" t="n">
         <v>11.0</v>
@@ -699,13 +702,13 @@
         <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F20" t="n">
         <v>11.0</v>
@@ -725,13 +728,13 @@
         <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F21" t="n">
         <v>1.0</v>
@@ -751,10 +754,10 @@
         <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E22" t="e">
         <v>#N/A</v>
@@ -777,16 +780,16 @@
         <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F23" t="n">
-        <v>23.0</v>
+        <v>28.0</v>
       </c>
       <c r="G23" t="n">
         <v>0.0</v>
@@ -803,13 +806,13 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F24" t="n">
         <v>3.0</v>
@@ -829,13 +832,13 @@
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F25" t="n">
         <v>11.0</v>
@@ -855,13 +858,13 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F26" t="n">
         <v>20.0</v>
@@ -881,13 +884,13 @@
         <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F27" t="n">
         <v>2.0</v>
@@ -907,13 +910,13 @@
         <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
@@ -933,13 +936,13 @@
         <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F29" t="n">
         <v>23.0</v>
@@ -959,13 +962,13 @@
         <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F30" t="n">
         <v>14.0</v>
@@ -985,13 +988,13 @@
         <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F31" t="n">
         <v>3.0</v>
@@ -1011,13 +1014,13 @@
         <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F32" t="n">
         <v>2.0</v>
@@ -1037,13 +1040,13 @@
         <v>9</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E33" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F33" t="n">
         <v>11.0</v>
@@ -1063,13 +1066,13 @@
         <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F34" t="n">
         <v>2.0</v>
@@ -1089,13 +1092,13 @@
         <v>10</v>
       </c>
       <c r="C35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F35" t="n">
         <v>11.0</v>
@@ -1115,13 +1118,13 @@
         <v>10</v>
       </c>
       <c r="C36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F36" t="n">
         <v>0.0</v>
@@ -1141,13 +1144,13 @@
         <v>10</v>
       </c>
       <c r="C37" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F37" t="n">
         <v>5.0</v>
@@ -1167,13 +1170,13 @@
         <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F38" t="n">
         <v>2.0</v>
@@ -1193,13 +1196,13 @@
         <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E39" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F39" t="n">
         <v>2.0</v>
@@ -1219,13 +1222,13 @@
         <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F40" t="n">
         <v>1.0</v>
@@ -1245,13 +1248,13 @@
         <v>9</v>
       </c>
       <c r="C41" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E41" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F41" t="n">
         <v>13.0</v>
@@ -1271,13 +1274,13 @@
         <v>9</v>
       </c>
       <c r="C42" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E42" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F42" t="n">
         <v>18.0</v>
@@ -1297,13 +1300,13 @@
         <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F43" t="n">
         <v>117.0</v>
@@ -1323,13 +1326,13 @@
         <v>11</v>
       </c>
       <c r="C44" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E44" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F44" t="n">
         <v>2.0</v>
@@ -1349,13 +1352,13 @@
         <v>11</v>
       </c>
       <c r="C45" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E45" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F45" t="n">
         <v>22.0</v>
@@ -1375,13 +1378,13 @@
         <v>11</v>
       </c>
       <c r="C46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E46" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F46" t="n">
         <v>0.0</v>
@@ -1401,13 +1404,13 @@
         <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E47" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F47" t="n">
         <v>1.0</v>
@@ -1427,13 +1430,13 @@
         <v>11</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E48" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F48" t="n">
         <v>0.0</v>
@@ -1453,13 +1456,13 @@
         <v>11</v>
       </c>
       <c r="C49" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E49" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F49" t="n">
         <v>2.0</v>
@@ -1479,13 +1482,13 @@
         <v>11</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E50" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F50" t="n">
         <v>0.0</v>
@@ -1505,13 +1508,13 @@
         <v>11</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E51" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F51" t="n">
         <v>0.0</v>
@@ -1531,13 +1534,13 @@
         <v>11</v>
       </c>
       <c r="C52" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E52" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F52" t="n">
         <v>2.0</v>
@@ -1557,13 +1560,13 @@
         <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E53" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F53" t="n">
         <v>3.0</v>
@@ -1583,13 +1586,13 @@
         <v>11</v>
       </c>
       <c r="C54" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E54" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F54" t="n">
         <v>0.0</v>
@@ -1609,13 +1612,13 @@
         <v>11</v>
       </c>
       <c r="C55" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E55" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F55" t="n">
         <v>3.0</v>
@@ -1635,13 +1638,13 @@
         <v>11</v>
       </c>
       <c r="C56" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E56" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F56" t="n">
         <v>10.0</v>
@@ -1661,13 +1664,13 @@
         <v>9</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E57" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F57" t="n">
         <v>0.0</v>
@@ -1687,13 +1690,13 @@
         <v>9</v>
       </c>
       <c r="C58" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E58" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F58" t="n">
         <v>2.0</v>
@@ -1713,13 +1716,13 @@
         <v>9</v>
       </c>
       <c r="C59" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E59" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F59" t="n">
         <v>9.0</v>
@@ -1739,13 +1742,13 @@
         <v>9</v>
       </c>
       <c r="C60" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E60" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F60" t="n">
         <v>1.0</v>
@@ -1765,13 +1768,13 @@
         <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E61" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F61" t="n">
         <v>40.0</v>
@@ -1791,13 +1794,13 @@
         <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D62" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E62" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F62" t="n">
         <v>16.0</v>
@@ -1817,13 +1820,13 @@
         <v>9</v>
       </c>
       <c r="C63" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D63" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E63" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F63" t="n">
         <v>172.0</v>
@@ -1843,13 +1846,13 @@
         <v>10</v>
       </c>
       <c r="C64" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D64" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E64" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F64" t="n">
         <v>1.0</v>
@@ -1869,13 +1872,13 @@
         <v>10</v>
       </c>
       <c r="C65" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D65" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E65" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F65" t="n">
         <v>2.0</v>
@@ -1895,13 +1898,13 @@
         <v>9</v>
       </c>
       <c r="C66" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D66" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E66" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F66" t="n">
         <v>35.0</v>
@@ -1921,13 +1924,13 @@
         <v>9</v>
       </c>
       <c r="C67" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E67" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F67" t="n">
         <v>3.0</v>
@@ -1947,13 +1950,13 @@
         <v>9</v>
       </c>
       <c r="C68" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D68" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E68" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F68" t="n">
         <v>66.0</v>
@@ -1973,10 +1976,10 @@
         <v>9</v>
       </c>
       <c r="C69" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D69" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E69" t="e">
         <v>#N/A</v>
@@ -1999,13 +2002,13 @@
         <v>9</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E70" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F70" t="n">
         <v>18.0</v>
@@ -2025,13 +2028,13 @@
         <v>9</v>
       </c>
       <c r="C71" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E71" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F71" t="n">
         <v>10.0</v>
@@ -2051,13 +2054,13 @@
         <v>9</v>
       </c>
       <c r="C72" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E72" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F72" t="n">
         <v>17.0</v>
@@ -2077,13 +2080,13 @@
         <v>9</v>
       </c>
       <c r="C73" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E73" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F73" t="n">
         <v>8.0</v>
@@ -2103,13 +2106,13 @@
         <v>10</v>
       </c>
       <c r="C74" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E74" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F74" t="n">
         <v>9.0</v>
@@ -2129,10 +2132,10 @@
         <v>10</v>
       </c>
       <c r="C75" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D75" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E75" t="e">
         <v>#N/A</v>
@@ -2155,13 +2158,13 @@
         <v>10</v>
       </c>
       <c r="C76" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D76" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E76" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F76" t="n">
         <v>2.0</v>
@@ -2181,13 +2184,13 @@
         <v>10</v>
       </c>
       <c r="C77" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D77" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E77" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F77" t="n">
         <v>19.0</v>
@@ -2207,13 +2210,13 @@
         <v>11</v>
       </c>
       <c r="C78" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E78" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F78" t="n">
         <v>0.0</v>
@@ -2233,13 +2236,13 @@
         <v>11</v>
       </c>
       <c r="C79" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D79" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E79" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F79" t="n">
         <v>1.0</v>
@@ -2259,13 +2262,13 @@
         <v>11</v>
       </c>
       <c r="C80" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D80" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E80" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F80" t="n">
         <v>0.0</v>
@@ -2285,13 +2288,13 @@
         <v>11</v>
       </c>
       <c r="C81" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D81" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F81" t="n">
         <v>11.0</v>
@@ -2311,13 +2314,13 @@
         <v>11</v>
       </c>
       <c r="C82" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D82" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F82" t="n">
         <v>4.0</v>
@@ -2337,13 +2340,13 @@
         <v>9</v>
       </c>
       <c r="C83" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D83" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F83" t="n">
         <v>8.0</v>
@@ -2363,13 +2366,13 @@
         <v>9</v>
       </c>
       <c r="C84" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D84" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F84" t="n">
         <v>8.0</v>
@@ -2389,13 +2392,13 @@
         <v>9</v>
       </c>
       <c r="C85" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D85" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F85" t="n">
         <v>15.0</v>
@@ -2415,13 +2418,13 @@
         <v>9</v>
       </c>
       <c r="C86" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E86" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F86" t="n">
         <v>0.0</v>
@@ -2441,13 +2444,13 @@
         <v>9</v>
       </c>
       <c r="C87" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D87" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E87" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F87" t="n">
         <v>9.0</v>
@@ -2467,13 +2470,13 @@
         <v>9</v>
       </c>
       <c r="C88" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D88" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E88" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F88" t="n">
         <v>5.0</v>
@@ -2493,13 +2496,13 @@
         <v>9</v>
       </c>
       <c r="C89" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E89" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F89" t="n">
         <v>43.0</v>
@@ -2519,13 +2522,13 @@
         <v>9</v>
       </c>
       <c r="C90" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D90" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E90" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F90" t="n">
         <v>13.0</v>
@@ -2545,13 +2548,13 @@
         <v>10</v>
       </c>
       <c r="C91" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D91" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E91" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F91" t="n">
         <v>2.0</v>
@@ -2571,13 +2574,13 @@
         <v>10</v>
       </c>
       <c r="C92" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D92" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E92" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F92" t="n">
         <v>5.0</v>
@@ -2597,13 +2600,13 @@
         <v>10</v>
       </c>
       <c r="C93" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D93" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E93" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F93" t="n">
         <v>2.0</v>
@@ -2623,19 +2626,19 @@
         <v>11</v>
       </c>
       <c r="C94" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D94" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E94" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F94" t="n">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="G94" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H94" t="n">
         <v>0.0</v>
@@ -2649,19 +2652,19 @@
         <v>11</v>
       </c>
       <c r="C95" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D95" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E95" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F95" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G95" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H95" t="n">
         <v>0.0</v>
@@ -2675,16 +2678,16 @@
         <v>11</v>
       </c>
       <c r="C96" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D96" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E96" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F96" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>
@@ -2698,22 +2701,22 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C97" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D97" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E97" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F97" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -2724,22 +2727,22 @@
         <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C98" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D98" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E98" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F98" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H98" t="n">
         <v>0.0</v>
@@ -2750,22 +2753,22 @@
         <v>8</v>
       </c>
       <c r="B99" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C99" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D99" t="s">
         <v>31</v>
       </c>
       <c r="E99" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F99" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G99" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H99" t="n">
         <v>0.0</v>
@@ -2776,22 +2779,22 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C100" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D100" t="s">
         <v>31</v>
       </c>
       <c r="E100" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F100" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G100" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2805,19 +2808,19 @@
         <v>10</v>
       </c>
       <c r="C101" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D101" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E101" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F101" t="n">
         <v>1.0</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -2828,22 +2831,22 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C102" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D102" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E102" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F102" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2854,25 +2857,25 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C103" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D103" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E103" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F103" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
       </c>
       <c r="H103" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="104">
@@ -2883,16 +2886,16 @@
         <v>11</v>
       </c>
       <c r="C104" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D104" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E104" t="s">
         <v>42</v>
       </c>
       <c r="F104" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -2906,22 +2909,22 @@
         <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C105" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D105" t="s">
-        <v>31</v>
-      </c>
-      <c r="E105" t="e">
-        <v>#N/A</v>
+        <v>32</v>
+      </c>
+      <c r="E105" t="s">
+        <v>43</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G105" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H105" t="n">
         <v>0.0</v>
@@ -2932,22 +2935,22 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C106" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D106" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E106" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F106" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G106" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H106" t="n">
         <v>0.0</v>
@@ -2958,25 +2961,25 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C107" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D107" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E107" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F107" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G107" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="108">
@@ -2987,19 +2990,19 @@
         <v>9</v>
       </c>
       <c r="C108" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D108" t="s">
-        <v>31</v>
-      </c>
-      <c r="E108" t="s">
-        <v>42</v>
+        <v>32</v>
+      </c>
+      <c r="E108" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F108" t="n">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
       <c r="G108" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H108" t="n">
         <v>0.0</v>
@@ -3010,22 +3013,22 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C109" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D109" t="s">
         <v>32</v>
       </c>
       <c r="E109" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F109" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G109" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G109" t="n">
-        <v>1.0</v>
       </c>
       <c r="H109" t="n">
         <v>0.0</v>
@@ -3036,22 +3039,22 @@
         <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C110" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D110" t="s">
         <v>32</v>
       </c>
       <c r="E110" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F110" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G110" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H110" t="n">
         <v>0.0</v>
@@ -3062,22 +3065,22 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C111" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D111" t="s">
         <v>32</v>
       </c>
       <c r="E111" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F111" t="n">
-        <v>3.0</v>
+        <v>19.0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3088,19 +3091,19 @@
         <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C112" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D112" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E112" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F112" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G112" t="n">
         <v>1.0</v>
@@ -3114,25 +3117,25 @@
         <v>8</v>
       </c>
       <c r="B113" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C113" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D113" t="s">
-        <v>32</v>
-      </c>
-      <c r="E113" t="e">
-        <v>#N/A</v>
+        <v>33</v>
+      </c>
+      <c r="E113" t="s">
+        <v>42</v>
       </c>
       <c r="F113" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G113" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H113" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="114">
@@ -3140,22 +3143,22 @@
         <v>8</v>
       </c>
       <c r="B114" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C114" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D114" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E114" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F114" t="n">
-        <v>90.0</v>
+        <v>3.0</v>
       </c>
       <c r="G114" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3169,19 +3172,19 @@
         <v>9</v>
       </c>
       <c r="C115" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D115" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E115" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F115" t="n">
-        <v>27.0</v>
+        <v>0.0</v>
       </c>
       <c r="G115" t="n">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="H115" t="n">
         <v>0.0</v>
@@ -3195,22 +3198,22 @@
         <v>9</v>
       </c>
       <c r="C116" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D116" t="s">
-        <v>32</v>
-      </c>
-      <c r="E116" t="s">
-        <v>42</v>
+        <v>33</v>
+      </c>
+      <c r="E116" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F116" t="n">
-        <v>530.0</v>
+        <v>0.0</v>
       </c>
       <c r="G116" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H116" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="117">
@@ -3221,19 +3224,19 @@
         <v>9</v>
       </c>
       <c r="C117" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D117" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E117" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F117" t="n">
-        <v>0.0</v>
+        <v>90.0</v>
       </c>
       <c r="G117" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3247,19 +3250,19 @@
         <v>9</v>
       </c>
       <c r="C118" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D118" t="s">
         <v>33</v>
       </c>
-      <c r="E118" t="e">
-        <v>#N/A</v>
+      <c r="E118" t="s">
+        <v>42</v>
       </c>
       <c r="F118" t="n">
-        <v>1.0</v>
+        <v>27.0</v>
       </c>
       <c r="G118" t="n">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="H118" t="n">
         <v>0.0</v>
@@ -3273,22 +3276,22 @@
         <v>9</v>
       </c>
       <c r="C119" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D119" t="s">
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0</v>
+        <v>530.0</v>
       </c>
       <c r="G119" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="120">
@@ -3299,19 +3302,19 @@
         <v>9</v>
       </c>
       <c r="C120" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D120" t="s">
         <v>33</v>
       </c>
       <c r="E120" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F120" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="G120" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H120" t="n">
         <v>0.0</v>
@@ -3325,19 +3328,19 @@
         <v>9</v>
       </c>
       <c r="C121" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D121" t="s">
-        <v>33</v>
-      </c>
-      <c r="E121" t="s">
-        <v>42</v>
+        <v>34</v>
+      </c>
+      <c r="E121" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F121" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G121" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H121" t="n">
         <v>0.0</v>
@@ -3351,19 +3354,19 @@
         <v>9</v>
       </c>
       <c r="C122" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D122" t="s">
         <v>34</v>
       </c>
       <c r="E122" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F122" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3377,22 +3380,22 @@
         <v>9</v>
       </c>
       <c r="C123" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D123" t="s">
         <v>34</v>
       </c>
       <c r="E123" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F123" t="n">
-        <v>16.0</v>
+        <v>7.0</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H123" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="124">
@@ -3403,19 +3406,19 @@
         <v>9</v>
       </c>
       <c r="C124" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D124" t="s">
         <v>34</v>
       </c>
       <c r="E124" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F124" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>
@@ -3426,7 +3429,7 @@
         <v>8</v>
       </c>
       <c r="B125" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C125" t="s">
         <v>16</v>
@@ -3435,13 +3438,13 @@
         <v>35</v>
       </c>
       <c r="E125" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="G125" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3452,7 +3455,7 @@
         <v>8</v>
       </c>
       <c r="B126" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C126" t="s">
         <v>16</v>
@@ -3461,16 +3464,16 @@
         <v>35</v>
       </c>
       <c r="E126" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F126" t="n">
-        <v>6.0</v>
+        <v>16.0</v>
       </c>
       <c r="G126" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="127">
@@ -3478,7 +3481,7 @@
         <v>8</v>
       </c>
       <c r="B127" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C127" t="s">
         <v>16</v>
@@ -3490,10 +3493,10 @@
         <v>43</v>
       </c>
       <c r="F127" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="G127" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H127" t="n">
         <v>0.0</v>
@@ -3507,19 +3510,19 @@
         <v>10</v>
       </c>
       <c r="C128" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D128" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E128" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F128" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H128" t="n">
         <v>0.0</v>
@@ -3530,22 +3533,22 @@
         <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C129" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D129" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E129" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F129" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="G129" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -3556,22 +3559,22 @@
         <v>8</v>
       </c>
       <c r="B130" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C130" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D130" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E130" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F130" t="n">
         <v>0.0</v>
       </c>
       <c r="G130" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H130" t="n">
         <v>0.0</v>
@@ -3582,19 +3585,19 @@
         <v>8</v>
       </c>
       <c r="B131" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C131" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D131" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E131" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F131" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G131" t="n">
         <v>0.0</v>
@@ -3611,19 +3614,19 @@
         <v>11</v>
       </c>
       <c r="C132" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D132" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E132" t="s">
         <v>42</v>
       </c>
       <c r="F132" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -3634,22 +3637,22 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C133" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D133" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E133" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F133" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="G133" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H133" t="n">
         <v>0.0</v>
@@ -3660,19 +3663,19 @@
         <v>8</v>
       </c>
       <c r="B134" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C134" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D134" t="s">
-        <v>35</v>
-      </c>
-      <c r="E134" t="e">
-        <v>#N/A</v>
+        <v>36</v>
+      </c>
+      <c r="E134" t="s">
+        <v>40</v>
       </c>
       <c r="F134" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G134" t="n">
         <v>0.0</v>
@@ -3686,19 +3689,19 @@
         <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C135" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D135" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E135" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F135" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="G135" t="n">
         <v>0.0</v>
@@ -3715,19 +3718,19 @@
         <v>9</v>
       </c>
       <c r="C136" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D136" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E136" t="s">
         <v>42</v>
       </c>
       <c r="F136" t="n">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H136" t="n">
         <v>0.0</v>
@@ -3738,22 +3741,22 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C137" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D137" t="s">
         <v>36</v>
       </c>
-      <c r="E137" t="s">
-        <v>39</v>
+      <c r="E137" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F137" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G137" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3764,10 +3767,10 @@
         <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C138" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D138" t="s">
         <v>36</v>
@@ -3776,10 +3779,10 @@
         <v>41</v>
       </c>
       <c r="F138" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G138" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3790,10 +3793,10 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C139" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D139" t="s">
         <v>36</v>
@@ -3802,10 +3805,10 @@
         <v>43</v>
       </c>
       <c r="F139" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G139" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3819,19 +3822,19 @@
         <v>11</v>
       </c>
       <c r="C140" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E140" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F140" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H140" t="n">
         <v>0.0</v>
@@ -3845,19 +3848,19 @@
         <v>11</v>
       </c>
       <c r="C141" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E141" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F141" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G141" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H141" t="n">
         <v>0.0</v>
@@ -3871,19 +3874,19 @@
         <v>11</v>
       </c>
       <c r="C142" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D142" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E142" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F142" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3894,16 +3897,16 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C143" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D143" t="s">
         <v>37</v>
       </c>
       <c r="E143" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F143" t="n">
         <v>1.0</v>
@@ -3920,22 +3923,22 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C144" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D144" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E144" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F144" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G144" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3946,19 +3949,19 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C145" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D145" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E145" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F145" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G145" t="n">
         <v>0.0</v>
@@ -3972,19 +3975,19 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C146" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D146" t="s">
         <v>38</v>
       </c>
       <c r="E146" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F146" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G146" t="n">
         <v>0.0</v>
@@ -3998,22 +4001,22 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C147" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E147" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F147" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G147" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4024,22 +4027,22 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C148" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D148" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E148" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F148" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G148" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4050,22 +4053,22 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C149" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D149" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E149" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F149" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G149" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4079,16 +4082,16 @@
         <v>9</v>
       </c>
       <c r="C150" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D150" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E150" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F150" t="n">
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
       <c r="G150" t="n">
         <v>3.0</v>
@@ -4105,19 +4108,19 @@
         <v>9</v>
       </c>
       <c r="C151" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D151" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E151" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F151" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G151" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4131,21 +4134,99 @@
         <v>9</v>
       </c>
       <c r="C152" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D152" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E152" t="s">
+        <v>40</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>8</v>
+      </c>
+      <c r="B153" t="s">
+        <v>9</v>
+      </c>
+      <c r="C153" t="s">
+        <v>17</v>
+      </c>
+      <c r="D153" t="s">
+        <v>39</v>
+      </c>
+      <c r="E153" t="s">
+        <v>41</v>
+      </c>
+      <c r="F153" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="G153" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>8</v>
+      </c>
+      <c r="B154" t="s">
+        <v>9</v>
+      </c>
+      <c r="C154" t="s">
+        <v>17</v>
+      </c>
+      <c r="D154" t="s">
+        <v>39</v>
+      </c>
+      <c r="E154" t="s">
         <v>43</v>
       </c>
-      <c r="F152" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G152" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H152" t="n">
+      <c r="F154" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>8</v>
+      </c>
+      <c r="B155" t="s">
+        <v>9</v>
+      </c>
+      <c r="C155" t="s">
+        <v>17</v>
+      </c>
+      <c r="D155" t="s">
+        <v>39</v>
+      </c>
+      <c r="E155" t="s">
+        <v>44</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H155" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -789,7 +789,7 @@
         <v>43</v>
       </c>
       <c r="F23" t="n">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="G23" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3285,7 +3285,7 @@
         <v>43</v>
       </c>
       <c r="F119" t="n">
-        <v>530.0</v>
+        <v>529.0</v>
       </c>
       <c r="G119" t="n">
         <v>7.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1777,7 +1777,7 @@
         <v>40</v>
       </c>
       <c r="F61" t="n">
-        <v>40.0</v>
+        <v>39.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -815,7 +815,7 @@
         <v>40</v>
       </c>
       <c r="F24" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G24" t="n">
         <v>1.0</v>
@@ -867,7 +867,7 @@
         <v>43</v>
       </c>
       <c r="F26" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="G26" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1471,7 +1471,7 @@
         <v>2.0</v>
       </c>
       <c r="H49" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="50">
@@ -1829,7 +1829,7 @@
         <v>43</v>
       </c>
       <c r="F63" t="n">
-        <v>172.0</v>
+        <v>171.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -3779,7 +3779,7 @@
         <v>41</v>
       </c>
       <c r="F138" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="G138" t="n">
         <v>0.0</v>
@@ -3805,7 +3805,7 @@
         <v>43</v>
       </c>
       <c r="F139" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G139" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3259,7 +3259,7 @@
         <v>42</v>
       </c>
       <c r="F118" t="n">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
       <c r="G118" t="n">
         <v>14.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1829,7 +1829,7 @@
         <v>43</v>
       </c>
       <c r="F63" t="n">
-        <v>171.0</v>
+        <v>170.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -3285,7 +3285,7 @@
         <v>43</v>
       </c>
       <c r="F119" t="n">
-        <v>529.0</v>
+        <v>528.0</v>
       </c>
       <c r="G119" t="n">
         <v>7.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -581,7 +581,7 @@
         <v>42</v>
       </c>
       <c r="F15" t="n">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -607,7 +607,7 @@
         <v>43</v>
       </c>
       <c r="F16" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -321,7 +321,7 @@
         <v>43</v>
       </c>
       <c r="F5" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -529,7 +529,7 @@
         <v>40</v>
       </c>
       <c r="F13" t="n">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="G13" t="n">
         <v>3.0</v>
@@ -607,7 +607,7 @@
         <v>43</v>
       </c>
       <c r="F16" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -945,7 +945,7 @@
         <v>42</v>
       </c>
       <c r="F29" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G29" t="n">
         <v>0.0</v>
@@ -1101,7 +1101,7 @@
         <v>43</v>
       </c>
       <c r="F35" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="G35" t="n">
         <v>1.0</v>
@@ -1309,7 +1309,7 @@
         <v>43</v>
       </c>
       <c r="F43" t="n">
-        <v>117.0</v>
+        <v>116.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -1907,7 +1907,7 @@
         <v>40</v>
       </c>
       <c r="F66" t="n">
-        <v>35.0</v>
+        <v>34.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1959,7 +1959,7 @@
         <v>43</v>
       </c>
       <c r="F68" t="n">
-        <v>66.0</v>
+        <v>65.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2063,7 +2063,7 @@
         <v>43</v>
       </c>
       <c r="F72" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G72" t="n">
         <v>1.0</v>
@@ -2401,7 +2401,7 @@
         <v>43</v>
       </c>
       <c r="F85" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="G85" t="n">
         <v>0.0</v>
@@ -2843,7 +2843,7 @@
         <v>42</v>
       </c>
       <c r="F102" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G102" t="n">
         <v>2.0</v>
@@ -2895,7 +2895,7 @@
         <v>42</v>
       </c>
       <c r="F104" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -2921,7 +2921,7 @@
         <v>43</v>
       </c>
       <c r="F105" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
@@ -3051,10 +3051,10 @@
         <v>42</v>
       </c>
       <c r="F110" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="G110" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="H110" t="n">
         <v>0.0</v>
@@ -3077,7 +3077,7 @@
         <v>43</v>
       </c>
       <c r="F111" t="n">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="G111" t="n">
         <v>2.0</v>
@@ -3285,7 +3285,7 @@
         <v>43</v>
       </c>
       <c r="F119" t="n">
-        <v>528.0</v>
+        <v>531.0</v>
       </c>
       <c r="G119" t="n">
         <v>7.0</v>
@@ -3392,7 +3392,7 @@
         <v>7.0</v>
       </c>
       <c r="G123" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>
@@ -3805,7 +3805,7 @@
         <v>43</v>
       </c>
       <c r="F139" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G139" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="47">
   <si>
     <t>Area</t>
   </si>
@@ -581,7 +581,7 @@
         <v>42</v>
       </c>
       <c r="F15" t="n">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -815,10 +815,10 @@
         <v>40</v>
       </c>
       <c r="F24" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G24" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H24" t="n">
         <v>0.0</v>
@@ -841,7 +841,7 @@
         <v>42</v>
       </c>
       <c r="F25" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
       <c r="G25" t="n">
         <v>0.0</v>
@@ -867,7 +867,7 @@
         <v>43</v>
       </c>
       <c r="F26" t="n">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="G26" t="n">
         <v>0.0</v>
@@ -893,10 +893,10 @@
         <v>40</v>
       </c>
       <c r="F27" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G27" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1.0</v>
       </c>
       <c r="H27" t="n">
         <v>0.0</v>
@@ -945,7 +945,7 @@
         <v>42</v>
       </c>
       <c r="F29" t="n">
-        <v>24.0</v>
+        <v>29.0</v>
       </c>
       <c r="G29" t="n">
         <v>0.0</v>
@@ -971,7 +971,7 @@
         <v>43</v>
       </c>
       <c r="F30" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G30" t="n">
         <v>0.0</v>
@@ -1098,10 +1098,10 @@
         <v>22</v>
       </c>
       <c r="E35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F35" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
       <c r="G35" t="n">
         <v>1.0</v>
@@ -1124,10 +1124,10 @@
         <v>22</v>
       </c>
       <c r="E36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="G36" t="n">
         <v>1.0</v>
@@ -1150,13 +1150,13 @@
         <v>22</v>
       </c>
       <c r="E37" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F37" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H37" t="n">
         <v>0.0</v>
@@ -1283,10 +1283,10 @@
         <v>42</v>
       </c>
       <c r="F42" t="n">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="G42" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H42" t="n">
         <v>0.0</v>
@@ -1309,7 +1309,7 @@
         <v>43</v>
       </c>
       <c r="F43" t="n">
-        <v>116.0</v>
+        <v>115.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -1569,7 +1569,7 @@
         <v>42</v>
       </c>
       <c r="F53" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1647,7 +1647,7 @@
         <v>42</v>
       </c>
       <c r="F56" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -3100,10 +3100,10 @@
         <v>33</v>
       </c>
       <c r="E112" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F112" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G112" t="n">
         <v>1.0</v>
@@ -3129,7 +3129,7 @@
         <v>42</v>
       </c>
       <c r="F113" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G113" t="n">
         <v>2.0</v>
@@ -3155,7 +3155,7 @@
         <v>43</v>
       </c>
       <c r="F114" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G114" t="n">
         <v>0.0</v>
@@ -3169,7 +3169,7 @@
         <v>8</v>
       </c>
       <c r="B115" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C115" t="s">
         <v>16</v>
@@ -3178,10 +3178,10 @@
         <v>33</v>
       </c>
       <c r="E115" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F115" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G115" t="n">
         <v>1.0</v>
@@ -3195,7 +3195,7 @@
         <v>8</v>
       </c>
       <c r="B116" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C116" t="s">
         <v>16</v>
@@ -3203,17 +3203,17 @@
       <c r="D116" t="s">
         <v>33</v>
       </c>
-      <c r="E116" t="e">
-        <v>#N/A</v>
+      <c r="E116" t="s">
+        <v>42</v>
       </c>
       <c r="F116" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G116" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H116" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="117">
@@ -3221,7 +3221,7 @@
         <v>8</v>
       </c>
       <c r="B117" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C117" t="s">
         <v>16</v>
@@ -3230,13 +3230,13 @@
         <v>33</v>
       </c>
       <c r="E117" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F117" t="n">
-        <v>90.0</v>
+        <v>2.0</v>
       </c>
       <c r="G117" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3255,17 +3255,17 @@
       <c r="D118" t="s">
         <v>33</v>
       </c>
-      <c r="E118" t="s">
-        <v>42</v>
+      <c r="E118" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F118" t="n">
-        <v>26.0</v>
+        <v>0.0</v>
       </c>
       <c r="G118" t="n">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="119">
@@ -3282,16 +3282,16 @@
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F119" t="n">
-        <v>531.0</v>
+        <v>90.0</v>
       </c>
       <c r="G119" t="n">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
       <c r="H119" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="120">
@@ -3308,13 +3308,13 @@
         <v>33</v>
       </c>
       <c r="E120" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F120" t="n">
-        <v>0.0</v>
+        <v>26.0</v>
       </c>
       <c r="G120" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
       <c r="H120" t="n">
         <v>0.0</v>
@@ -3331,19 +3331,19 @@
         <v>16</v>
       </c>
       <c r="D121" t="s">
-        <v>34</v>
-      </c>
-      <c r="E121" t="e">
-        <v>#N/A</v>
+        <v>33</v>
+      </c>
+      <c r="E121" t="s">
+        <v>43</v>
       </c>
       <c r="F121" t="n">
-        <v>1.0</v>
+        <v>531.0</v>
       </c>
       <c r="G121" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="122">
@@ -3357,16 +3357,16 @@
         <v>16</v>
       </c>
       <c r="D122" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E122" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F122" t="n">
         <v>0.0</v>
       </c>
       <c r="G122" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3385,14 +3385,14 @@
       <c r="D123" t="s">
         <v>34</v>
       </c>
-      <c r="E123" t="s">
-        <v>42</v>
+      <c r="E123" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F123" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G123" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>
@@ -3412,13 +3412,13 @@
         <v>34</v>
       </c>
       <c r="E124" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F124" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="G124" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>
@@ -3435,16 +3435,16 @@
         <v>16</v>
       </c>
       <c r="D125" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E125" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F125" t="n">
         <v>7.0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3461,19 +3461,19 @@
         <v>16</v>
       </c>
       <c r="D126" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E126" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F126" t="n">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H126" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="127">
@@ -3490,10 +3490,10 @@
         <v>35</v>
       </c>
       <c r="E127" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F127" t="n">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="G127" t="n">
         <v>0.0</v>
@@ -3507,25 +3507,25 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C128" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D128" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E128" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F128" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="G128" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="129">
@@ -3533,22 +3533,22 @@
         <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C129" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D129" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E129" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F129" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="G129" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -3568,7 +3568,7 @@
         <v>36</v>
       </c>
       <c r="E130" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F130" t="n">
         <v>0.0</v>
@@ -3594,13 +3594,13 @@
         <v>36</v>
       </c>
       <c r="E131" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F131" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G131" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H131" t="n">
         <v>0.0</v>
@@ -3611,7 +3611,7 @@
         <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C132" t="s">
         <v>17</v>
@@ -3620,13 +3620,13 @@
         <v>36</v>
       </c>
       <c r="E132" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F132" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G132" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -3637,7 +3637,7 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C133" t="s">
         <v>17</v>
@@ -3646,13 +3646,13 @@
         <v>36</v>
       </c>
       <c r="E133" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F133" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G133" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H133" t="n">
         <v>0.0</v>
@@ -3672,13 +3672,13 @@
         <v>36</v>
       </c>
       <c r="E134" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F134" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H134" t="n">
         <v>0.0</v>
@@ -3698,13 +3698,13 @@
         <v>36</v>
       </c>
       <c r="E135" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F135" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G135" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G135" t="n">
-        <v>0.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3715,7 +3715,7 @@
         <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C136" t="s">
         <v>17</v>
@@ -3724,13 +3724,13 @@
         <v>36</v>
       </c>
       <c r="E136" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F136" t="n">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="G136" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H136" t="n">
         <v>0.0</v>
@@ -3741,7 +3741,7 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C137" t="s">
         <v>17</v>
@@ -3749,11 +3749,11 @@
       <c r="D137" t="s">
         <v>36</v>
       </c>
-      <c r="E137" t="e">
-        <v>#N/A</v>
+      <c r="E137" t="s">
+        <v>43</v>
       </c>
       <c r="F137" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G137" t="n">
         <v>0.0</v>
@@ -3776,13 +3776,13 @@
         <v>36</v>
       </c>
       <c r="E138" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F138" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3801,11 +3801,11 @@
       <c r="D139" t="s">
         <v>36</v>
       </c>
-      <c r="E139" t="s">
-        <v>43</v>
+      <c r="E139" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F139" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G139" t="n">
         <v>0.0</v>
@@ -3819,22 +3819,22 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C140" t="s">
         <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E140" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F140" t="n">
-        <v>4.0</v>
+        <v>11.0</v>
       </c>
       <c r="G140" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H140" t="n">
         <v>0.0</v>
@@ -3845,22 +3845,22 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C141" t="s">
         <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E141" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F141" t="n">
         <v>5.0</v>
       </c>
       <c r="G141" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H141" t="n">
         <v>0.0</v>
@@ -3880,13 +3880,13 @@
         <v>37</v>
       </c>
       <c r="E142" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F142" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G142" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3906,13 +3906,13 @@
         <v>37</v>
       </c>
       <c r="E143" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F143" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H143" t="n">
         <v>0.0</v>
@@ -3932,13 +3932,13 @@
         <v>37</v>
       </c>
       <c r="E144" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F144" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3958,10 +3958,10 @@
         <v>37</v>
       </c>
       <c r="E145" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F145" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G145" t="n">
         <v>0.0</v>
@@ -3975,19 +3975,19 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C146" t="s">
         <v>17</v>
       </c>
       <c r="D146" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E146" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F146" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G146" t="n">
         <v>0.0</v>
@@ -4001,22 +4001,22 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E147" t="s">
         <v>43</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G147" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4027,19 +4027,19 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
       </c>
       <c r="D148" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E148" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F148" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G148" t="n">
         <v>0.0</v>
@@ -4053,7 +4053,7 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C149" t="s">
         <v>17</v>
@@ -4062,13 +4062,13 @@
         <v>39</v>
       </c>
       <c r="E149" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F149" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4079,7 +4079,7 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C150" t="s">
         <v>17</v>
@@ -4088,13 +4088,13 @@
         <v>39</v>
       </c>
       <c r="E150" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F150" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G150" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>
@@ -4105,7 +4105,7 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
@@ -4114,13 +4114,13 @@
         <v>39</v>
       </c>
       <c r="E151" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F151" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G151" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4140,13 +4140,13 @@
         <v>39</v>
       </c>
       <c r="E152" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F152" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G152" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4166,13 +4166,13 @@
         <v>39</v>
       </c>
       <c r="E153" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F153" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G153" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H153" t="n">
         <v>0.0</v>
@@ -4192,10 +4192,10 @@
         <v>39</v>
       </c>
       <c r="E154" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F154" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G154" t="n">
         <v>1.0</v>
@@ -4218,15 +4218,67 @@
         <v>39</v>
       </c>
       <c r="E155" t="s">
+        <v>41</v>
+      </c>
+      <c r="F155" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>8</v>
+      </c>
+      <c r="B156" t="s">
+        <v>9</v>
+      </c>
+      <c r="C156" t="s">
+        <v>17</v>
+      </c>
+      <c r="D156" t="s">
+        <v>39</v>
+      </c>
+      <c r="E156" t="s">
+        <v>43</v>
+      </c>
+      <c r="F156" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>8</v>
+      </c>
+      <c r="B157" t="s">
+        <v>9</v>
+      </c>
+      <c r="C157" t="s">
+        <v>17</v>
+      </c>
+      <c r="D157" t="s">
+        <v>39</v>
+      </c>
+      <c r="E157" t="s">
         <v>44</v>
       </c>
-      <c r="F155" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G155" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H155" t="n">
+      <c r="F157" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H157" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -607,7 +607,7 @@
         <v>43</v>
       </c>
       <c r="F16" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -3051,7 +3051,7 @@
         <v>42</v>
       </c>
       <c r="F110" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="G110" t="n">
         <v>5.0</v>
@@ -3337,7 +3337,7 @@
         <v>43</v>
       </c>
       <c r="F121" t="n">
-        <v>531.0</v>
+        <v>530.0</v>
       </c>
       <c r="G121" t="n">
         <v>7.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3077,7 +3077,7 @@
         <v>43</v>
       </c>
       <c r="F111" t="n">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="G111" t="n">
         <v>2.0</v>
@@ -3285,7 +3285,7 @@
         <v>40</v>
       </c>
       <c r="F119" t="n">
-        <v>90.0</v>
+        <v>89.0</v>
       </c>
       <c r="G119" t="n">
         <v>12.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3337,7 +3337,7 @@
         <v>43</v>
       </c>
       <c r="F121" t="n">
-        <v>530.0</v>
+        <v>529.0</v>
       </c>
       <c r="G121" t="n">
         <v>7.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3337,7 +3337,7 @@
         <v>43</v>
       </c>
       <c r="F121" t="n">
-        <v>529.0</v>
+        <v>528.0</v>
       </c>
       <c r="G121" t="n">
         <v>7.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3337,7 +3337,7 @@
         <v>43</v>
       </c>
       <c r="F121" t="n">
-        <v>528.0</v>
+        <v>529.0</v>
       </c>
       <c r="G121" t="n">
         <v>7.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3675,7 +3675,7 @@
         <v>42</v>
       </c>
       <c r="F134" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G134" t="n">
         <v>4.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -2742,7 +2742,7 @@
         <v>1.0</v>
       </c>
       <c r="G98" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H98" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -2505,7 +2505,7 @@
         <v>41</v>
       </c>
       <c r="F89" t="n">
-        <v>43.0</v>
+        <v>42.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="47">
   <si>
     <t>Area</t>
   </si>
@@ -659,7 +659,7 @@
         <v>43</v>
       </c>
       <c r="F18" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="G18" t="n">
         <v>0.0</v>
@@ -1101,7 +1101,7 @@
         <v>42</v>
       </c>
       <c r="F35" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="G35" t="n">
         <v>1.0</v>
@@ -1465,7 +1465,7 @@
         <v>42</v>
       </c>
       <c r="F49" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G49" t="n">
         <v>2.0</v>
@@ -2268,13 +2268,13 @@
         <v>29</v>
       </c>
       <c r="E80" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="G80" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H80" t="n">
         <v>0.0</v>
@@ -2294,10 +2294,10 @@
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F81" t="n">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2311,7 +2311,7 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C82" t="s">
         <v>15</v>
@@ -2320,13 +2320,13 @@
         <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F82" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2346,13 +2346,13 @@
         <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F83" t="n">
         <v>8.0</v>
       </c>
       <c r="G83" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H83" t="n">
         <v>0.0</v>
@@ -2372,10 +2372,10 @@
         <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F84" t="n">
-        <v>8.0</v>
+        <v>14.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2395,16 +2395,16 @@
         <v>15</v>
       </c>
       <c r="D85" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E85" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F85" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H85" t="n">
         <v>0.0</v>
@@ -2424,16 +2424,16 @@
         <v>30</v>
       </c>
       <c r="E86" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="G86" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="87">
@@ -2450,16 +2450,16 @@
         <v>30</v>
       </c>
       <c r="E87" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F87" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="G87" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H87" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="88">
@@ -2476,16 +2476,16 @@
         <v>30</v>
       </c>
       <c r="E88" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F88" t="n">
-        <v>5.0</v>
+        <v>42.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
       </c>
       <c r="H88" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="89">
@@ -2502,16 +2502,16 @@
         <v>30</v>
       </c>
       <c r="E89" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F89" t="n">
-        <v>42.0</v>
+        <v>13.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
       </c>
       <c r="H89" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="90">
@@ -2519,25 +2519,25 @@
         <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C90" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D90" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E90" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F90" t="n">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
       </c>
       <c r="H90" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="91">
@@ -2554,10 +2554,10 @@
         <v>31</v>
       </c>
       <c r="E91" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F91" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2580,10 +2580,10 @@
         <v>31</v>
       </c>
       <c r="E92" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F92" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G92" t="n">
         <v>0.0</v>
@@ -2597,7 +2597,7 @@
         <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C93" t="s">
         <v>16</v>
@@ -2606,13 +2606,13 @@
         <v>31</v>
       </c>
       <c r="E93" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F93" t="n">
-        <v>2.0</v>
+        <v>27.0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H93" t="n">
         <v>0.0</v>
@@ -2632,13 +2632,13 @@
         <v>31</v>
       </c>
       <c r="E94" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F94" t="n">
-        <v>27.0</v>
+        <v>1.0</v>
       </c>
       <c r="G94" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H94" t="n">
         <v>0.0</v>
@@ -2658,10 +2658,10 @@
         <v>31</v>
       </c>
       <c r="E95" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F95" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -2675,7 +2675,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C96" t="s">
         <v>16</v>
@@ -2684,13 +2684,13 @@
         <v>31</v>
       </c>
       <c r="E96" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F96" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H96" t="n">
         <v>0.0</v>
@@ -2710,13 +2710,13 @@
         <v>31</v>
       </c>
       <c r="E97" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F97" t="n">
         <v>1.0</v>
       </c>
       <c r="G97" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -2727,7 +2727,7 @@
         <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C98" t="s">
         <v>16</v>
@@ -2736,10 +2736,10 @@
         <v>31</v>
       </c>
       <c r="E98" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F98" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G98" t="n">
         <v>0.0</v>
@@ -2762,10 +2762,10 @@
         <v>31</v>
       </c>
       <c r="E99" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F99" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G99" t="n">
         <v>0.0</v>
@@ -2779,22 +2779,22 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C100" t="s">
         <v>16</v>
       </c>
       <c r="D100" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E100" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F100" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2814,13 +2814,13 @@
         <v>32</v>
       </c>
       <c r="E101" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F101" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G101" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -2840,13 +2840,13 @@
         <v>32</v>
       </c>
       <c r="E102" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F102" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G102" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2857,7 +2857,7 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C103" t="s">
         <v>16</v>
@@ -2866,16 +2866,16 @@
         <v>32</v>
       </c>
       <c r="E103" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F103" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="104">
@@ -2892,10 +2892,10 @@
         <v>32</v>
       </c>
       <c r="E104" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F104" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -2909,7 +2909,7 @@
         <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C105" t="s">
         <v>16</v>
@@ -2918,10 +2918,10 @@
         <v>32</v>
       </c>
       <c r="E105" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F105" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
@@ -2944,7 +2944,7 @@
         <v>32</v>
       </c>
       <c r="E106" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F106" t="n">
         <v>1.0</v>
@@ -2953,7 +2953,7 @@
         <v>0.0</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="107">
@@ -2961,7 +2961,7 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C107" t="s">
         <v>16</v>
@@ -2969,17 +2969,17 @@
       <c r="D107" t="s">
         <v>32</v>
       </c>
-      <c r="E107" t="s">
-        <v>42</v>
+      <c r="E107" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F107" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H107" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="108">
@@ -2995,14 +2995,14 @@
       <c r="D108" t="s">
         <v>32</v>
       </c>
-      <c r="E108" t="e">
-        <v>#N/A</v>
+      <c r="E108" t="s">
+        <v>40</v>
       </c>
       <c r="F108" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G108" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H108" t="n">
         <v>0.0</v>
@@ -3022,13 +3022,13 @@
         <v>32</v>
       </c>
       <c r="E109" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F109" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="G109" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="H109" t="n">
         <v>0.0</v>
@@ -3048,13 +3048,13 @@
         <v>32</v>
       </c>
       <c r="E110" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F110" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
       <c r="G110" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="H110" t="n">
         <v>0.0</v>
@@ -3065,22 +3065,22 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C111" t="s">
         <v>16</v>
       </c>
       <c r="D111" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E111" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F111" t="n">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
       <c r="G111" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3100,13 +3100,13 @@
         <v>33</v>
       </c>
       <c r="E112" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F112" t="n">
         <v>0.0</v>
       </c>
       <c r="G112" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3126,13 +3126,13 @@
         <v>33</v>
       </c>
       <c r="E113" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F113" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G113" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H113" t="n">
         <v>0.0</v>
@@ -3143,7 +3143,7 @@
         <v>8</v>
       </c>
       <c r="B114" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C114" t="s">
         <v>16</v>
@@ -3152,13 +3152,13 @@
         <v>33</v>
       </c>
       <c r="E114" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F114" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3178,13 +3178,13 @@
         <v>33</v>
       </c>
       <c r="E115" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F115" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G115" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H115" t="n">
         <v>0.0</v>
@@ -3204,10 +3204,10 @@
         <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F116" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G116" t="n">
         <v>0.0</v>
@@ -3221,7 +3221,7 @@
         <v>8</v>
       </c>
       <c r="B117" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C117" t="s">
         <v>16</v>
@@ -3229,17 +3229,17 @@
       <c r="D117" t="s">
         <v>33</v>
       </c>
-      <c r="E117" t="s">
-        <v>43</v>
+      <c r="E117" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F117" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H117" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G117" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H117" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="118">
@@ -3255,17 +3255,17 @@
       <c r="D118" t="s">
         <v>33</v>
       </c>
-      <c r="E118" t="e">
-        <v>#N/A</v>
+      <c r="E118" t="s">
+        <v>40</v>
       </c>
       <c r="F118" t="n">
-        <v>0.0</v>
+        <v>89.0</v>
       </c>
       <c r="G118" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="H118" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="119">
@@ -3282,13 +3282,13 @@
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F119" t="n">
-        <v>89.0</v>
+        <v>26.0</v>
       </c>
       <c r="G119" t="n">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="H119" t="n">
         <v>0.0</v>
@@ -3308,16 +3308,16 @@
         <v>33</v>
       </c>
       <c r="E120" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F120" t="n">
-        <v>26.0</v>
+        <v>526.0</v>
       </c>
       <c r="G120" t="n">
-        <v>14.0</v>
+        <v>7.0</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="121">
@@ -3334,16 +3334,16 @@
         <v>33</v>
       </c>
       <c r="E121" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F121" t="n">
-        <v>528.0</v>
+        <v>0.0</v>
       </c>
       <c r="G121" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="H121" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="122">
@@ -3357,16 +3357,16 @@
         <v>16</v>
       </c>
       <c r="D122" t="s">
-        <v>33</v>
-      </c>
-      <c r="E122" t="s">
-        <v>44</v>
+        <v>34</v>
+      </c>
+      <c r="E122" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G122" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3385,11 +3385,11 @@
       <c r="D123" t="s">
         <v>34</v>
       </c>
-      <c r="E123" t="e">
-        <v>#N/A</v>
+      <c r="E123" t="s">
+        <v>40</v>
       </c>
       <c r="F123" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G123" t="n">
         <v>1.0</v>
@@ -3412,13 +3412,13 @@
         <v>34</v>
       </c>
       <c r="E124" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="G124" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>
@@ -3438,10 +3438,10 @@
         <v>34</v>
       </c>
       <c r="E125" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F125" t="n">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
       <c r="G125" t="n">
         <v>2.0</v>
@@ -3461,16 +3461,16 @@
         <v>16</v>
       </c>
       <c r="D126" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E126" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F126" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
       <c r="G126" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>
@@ -3490,16 +3490,16 @@
         <v>35</v>
       </c>
       <c r="E127" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F127" t="n">
-        <v>7.0</v>
+        <v>16.0</v>
       </c>
       <c r="G127" t="n">
         <v>0.0</v>
       </c>
       <c r="H127" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="128">
@@ -3516,16 +3516,16 @@
         <v>35</v>
       </c>
       <c r="E128" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F128" t="n">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
       <c r="G128" t="n">
         <v>0.0</v>
       </c>
       <c r="H128" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="129">
@@ -3533,22 +3533,22 @@
         <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C129" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D129" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E129" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F129" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="G129" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -3568,13 +3568,13 @@
         <v>36</v>
       </c>
       <c r="E130" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F130" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G130" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H130" t="n">
         <v>0.0</v>
@@ -3594,13 +3594,13 @@
         <v>36</v>
       </c>
       <c r="E131" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F131" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="G131" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H131" t="n">
         <v>0.0</v>
@@ -3620,13 +3620,13 @@
         <v>36</v>
       </c>
       <c r="E132" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F132" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G132" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -3637,7 +3637,7 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C133" t="s">
         <v>17</v>
@@ -3646,13 +3646,13 @@
         <v>36</v>
       </c>
       <c r="E133" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F133" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H133" t="n">
         <v>0.0</v>
@@ -3672,13 +3672,13 @@
         <v>36</v>
       </c>
       <c r="E134" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F134" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G134" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G134" t="n">
-        <v>4.0</v>
       </c>
       <c r="H134" t="n">
         <v>0.0</v>
@@ -3698,13 +3698,13 @@
         <v>36</v>
       </c>
       <c r="E135" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G135" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3724,7 +3724,7 @@
         <v>36</v>
       </c>
       <c r="E136" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F136" t="n">
         <v>2.0</v>
@@ -3741,7 +3741,7 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C137" t="s">
         <v>17</v>
@@ -3750,13 +3750,13 @@
         <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F137" t="n">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3775,14 +3775,14 @@
       <c r="D138" t="s">
         <v>36</v>
       </c>
-      <c r="E138" t="s">
-        <v>42</v>
+      <c r="E138" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F138" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G138" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3801,11 +3801,11 @@
       <c r="D139" t="s">
         <v>36</v>
       </c>
-      <c r="E139" t="e">
-        <v>#N/A</v>
+      <c r="E139" t="s">
+        <v>41</v>
       </c>
       <c r="F139" t="n">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="G139" t="n">
         <v>0.0</v>
@@ -3828,10 +3828,10 @@
         <v>36</v>
       </c>
       <c r="E140" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F140" t="n">
-        <v>11.0</v>
+        <v>5.0</v>
       </c>
       <c r="G140" t="n">
         <v>0.0</v>
@@ -3845,22 +3845,22 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C141" t="s">
         <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E141" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F141" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G141" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H141" t="n">
         <v>0.0</v>
@@ -3880,13 +3880,13 @@
         <v>37</v>
       </c>
       <c r="E142" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F142" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G142" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3906,13 +3906,13 @@
         <v>37</v>
       </c>
       <c r="E143" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F143" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G143" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="H143" t="n">
         <v>0.0</v>
@@ -3932,13 +3932,13 @@
         <v>37</v>
       </c>
       <c r="E144" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F144" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G144" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3958,10 +3958,10 @@
         <v>37</v>
       </c>
       <c r="E145" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F145" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G145" t="n">
         <v>0.0</v>
@@ -3984,10 +3984,10 @@
         <v>37</v>
       </c>
       <c r="E146" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F146" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G146" t="n">
         <v>0.0</v>
@@ -4001,19 +4001,19 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E147" t="s">
         <v>43</v>
       </c>
       <c r="F147" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G147" t="n">
         <v>0.0</v>
@@ -4027,22 +4027,22 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
       </c>
       <c r="D148" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E148" t="s">
         <v>43</v>
       </c>
       <c r="F148" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4062,13 +4062,13 @@
         <v>39</v>
       </c>
       <c r="E149" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F149" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G149" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4079,7 +4079,7 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C150" t="s">
         <v>17</v>
@@ -4105,7 +4105,7 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
@@ -4114,13 +4114,13 @@
         <v>39</v>
       </c>
       <c r="E151" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F151" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4140,13 +4140,13 @@
         <v>39</v>
       </c>
       <c r="E152" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F152" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G152" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4166,13 +4166,13 @@
         <v>39</v>
       </c>
       <c r="E153" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F153" t="n">
         <v>1.0</v>
       </c>
       <c r="G153" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H153" t="n">
         <v>0.0</v>
@@ -4192,13 +4192,13 @@
         <v>39</v>
       </c>
       <c r="E154" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F154" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G154" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H154" t="n">
         <v>0.0</v>
@@ -4218,13 +4218,13 @@
         <v>39</v>
       </c>
       <c r="E155" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F155" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="G155" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H155" t="n">
         <v>0.0</v>
@@ -4244,41 +4244,15 @@
         <v>39</v>
       </c>
       <c r="E156" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F156" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="G156" t="n">
         <v>1.0</v>
       </c>
       <c r="H156" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>8</v>
-      </c>
-      <c r="B157" t="s">
-        <v>9</v>
-      </c>
-      <c r="C157" t="s">
-        <v>17</v>
-      </c>
-      <c r="D157" t="s">
-        <v>39</v>
-      </c>
-      <c r="E157" t="s">
-        <v>44</v>
-      </c>
-      <c r="F157" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G157" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H157" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3311,7 +3311,7 @@
         <v>43</v>
       </c>
       <c r="F120" t="n">
-        <v>526.0</v>
+        <v>525.0</v>
       </c>
       <c r="G120" t="n">
         <v>7.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1829,7 +1829,7 @@
         <v>43</v>
       </c>
       <c r="F63" t="n">
-        <v>170.0</v>
+        <v>171.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -3311,7 +3311,7 @@
         <v>43</v>
       </c>
       <c r="F120" t="n">
-        <v>525.0</v>
+        <v>524.0</v>
       </c>
       <c r="G120" t="n">
         <v>7.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3259,7 +3259,7 @@
         <v>40</v>
       </c>
       <c r="F118" t="n">
-        <v>89.0</v>
+        <v>88.0</v>
       </c>
       <c r="G118" t="n">
         <v>12.0</v>
@@ -3311,7 +3311,7 @@
         <v>43</v>
       </c>
       <c r="F120" t="n">
-        <v>524.0</v>
+        <v>522.0</v>
       </c>
       <c r="G120" t="n">
         <v>7.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="47">
   <si>
     <t>Area</t>
   </si>
@@ -1843,7 +1843,7 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C64" t="s">
         <v>15</v>
@@ -1855,7 +1855,7 @@
         <v>40</v>
       </c>
       <c r="F64" t="n">
-        <v>1.0</v>
+        <v>35.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1869,7 +1869,7 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C65" t="s">
         <v>15</v>
@@ -1878,10 +1878,10 @@
         <v>27</v>
       </c>
       <c r="E65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F65" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1904,10 +1904,10 @@
         <v>27</v>
       </c>
       <c r="E66" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F66" t="n">
-        <v>34.0</v>
+        <v>67.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1927,16 +1927,16 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>27</v>
-      </c>
-      <c r="E67" t="s">
-        <v>42</v>
+        <v>28</v>
+      </c>
+      <c r="E67" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F67" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H67" t="n">
         <v>0.0</v>
@@ -1953,16 +1953,16 @@
         <v>15</v>
       </c>
       <c r="D68" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E68" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F68" t="n">
-        <v>65.0</v>
+        <v>18.0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H68" t="n">
         <v>0.0</v>
@@ -1981,11 +1981,11 @@
       <c r="D69" t="s">
         <v>28</v>
       </c>
-      <c r="E69" t="e">
-        <v>#N/A</v>
+      <c r="E69" t="s">
+        <v>42</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="G69" t="n">
         <v>1.0</v>
@@ -2008,7 +2008,7 @@
         <v>28</v>
       </c>
       <c r="E70" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F70" t="n">
         <v>18.0</v>
@@ -2034,16 +2034,16 @@
         <v>28</v>
       </c>
       <c r="E71" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F71" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="G71" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="72">
@@ -2051,19 +2051,19 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C72" t="s">
         <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E72" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F72" t="n">
-        <v>18.0</v>
+        <v>8.0</v>
       </c>
       <c r="G72" t="n">
         <v>1.0</v>
@@ -2077,25 +2077,25 @@
         <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C73" t="s">
         <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>28</v>
-      </c>
-      <c r="E73" t="s">
-        <v>41</v>
+        <v>29</v>
+      </c>
+      <c r="E73" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F73" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
       </c>
       <c r="H73" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="74">
@@ -2112,13 +2112,13 @@
         <v>29</v>
       </c>
       <c r="E74" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F74" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
       <c r="G74" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2137,11 +2137,11 @@
       <c r="D75" t="s">
         <v>29</v>
       </c>
-      <c r="E75" t="e">
-        <v>#N/A</v>
+      <c r="E75" t="s">
+        <v>43</v>
       </c>
       <c r="F75" t="n">
-        <v>1.0</v>
+        <v>19.0</v>
       </c>
       <c r="G75" t="n">
         <v>0.0</v>
@@ -2155,7 +2155,7 @@
         <v>8</v>
       </c>
       <c r="B76" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C76" t="s">
         <v>15</v>
@@ -2164,13 +2164,13 @@
         <v>29</v>
       </c>
       <c r="E76" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F76" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>
@@ -2181,7 +2181,7 @@
         <v>8</v>
       </c>
       <c r="B77" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C77" t="s">
         <v>15</v>
@@ -2190,13 +2190,13 @@
         <v>29</v>
       </c>
       <c r="E77" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F77" t="n">
-        <v>19.0</v>
+        <v>1.0</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H77" t="n">
         <v>0.0</v>
@@ -2216,13 +2216,13 @@
         <v>29</v>
       </c>
       <c r="E78" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="G78" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H78" t="n">
         <v>0.0</v>
@@ -2242,13 +2242,13 @@
         <v>29</v>
       </c>
       <c r="E79" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F79" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G79" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H79" t="n">
         <v>0.0</v>
@@ -2259,7 +2259,7 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C80" t="s">
         <v>15</v>
@@ -2271,10 +2271,10 @@
         <v>42</v>
       </c>
       <c r="F80" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H80" t="n">
         <v>0.0</v>
@@ -2285,7 +2285,7 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C81" t="s">
         <v>15</v>
@@ -2294,10 +2294,10 @@
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F81" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2320,13 +2320,13 @@
         <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F82" t="n">
-        <v>8.0</v>
+        <v>14.0</v>
       </c>
       <c r="G82" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2343,16 +2343,16 @@
         <v>15</v>
       </c>
       <c r="D83" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E83" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F83" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H83" t="n">
         <v>0.0</v>
@@ -2369,19 +2369,19 @@
         <v>15</v>
       </c>
       <c r="D84" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E84" t="s">
         <v>43</v>
       </c>
       <c r="F84" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="85">
@@ -2398,16 +2398,16 @@
         <v>30</v>
       </c>
       <c r="E85" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G85" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="86">
@@ -2424,16 +2424,16 @@
         <v>30</v>
       </c>
       <c r="E86" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F86" t="n">
-        <v>9.0</v>
+        <v>42.0</v>
       </c>
       <c r="G86" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H86" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="87">
@@ -2450,16 +2450,16 @@
         <v>30</v>
       </c>
       <c r="E87" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F87" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
       </c>
       <c r="H87" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="88">
@@ -2467,25 +2467,25 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C88" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D88" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E88" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F88" t="n">
-        <v>42.0</v>
+        <v>11.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
       </c>
       <c r="H88" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="89">
@@ -2493,25 +2493,25 @@
         <v>8</v>
       </c>
       <c r="B89" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C89" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D89" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E89" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F89" t="n">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
       </c>
       <c r="H89" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="90">
@@ -2519,7 +2519,7 @@
         <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C90" t="s">
         <v>16</v>
@@ -2528,13 +2528,13 @@
         <v>31</v>
       </c>
       <c r="E90" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F90" t="n">
-        <v>2.0</v>
+        <v>17.0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H90" t="n">
         <v>0.0</v>
@@ -2545,7 +2545,7 @@
         <v>8</v>
       </c>
       <c r="B91" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C91" t="s">
         <v>16</v>
@@ -2554,10 +2554,10 @@
         <v>31</v>
       </c>
       <c r="E91" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F91" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2571,7 +2571,7 @@
         <v>8</v>
       </c>
       <c r="B92" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C92" t="s">
         <v>16</v>
@@ -2597,7 +2597,7 @@
         <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C93" t="s">
         <v>16</v>
@@ -2609,10 +2609,10 @@
         <v>42</v>
       </c>
       <c r="F93" t="n">
-        <v>27.0</v>
+        <v>1.0</v>
       </c>
       <c r="G93" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H93" t="n">
         <v>0.0</v>
@@ -2623,7 +2623,7 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C94" t="s">
         <v>16</v>
@@ -2632,7 +2632,7 @@
         <v>31</v>
       </c>
       <c r="E94" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F94" t="n">
         <v>1.0</v>
@@ -2649,7 +2649,7 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C95" t="s">
         <v>16</v>
@@ -2658,10 +2658,10 @@
         <v>31</v>
       </c>
       <c r="E95" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F95" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -2675,7 +2675,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C96" t="s">
         <v>16</v>
@@ -2687,10 +2687,10 @@
         <v>42</v>
       </c>
       <c r="F96" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G96" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H96" t="n">
         <v>0.0</v>
@@ -2701,7 +2701,7 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C97" t="s">
         <v>16</v>
@@ -2713,7 +2713,7 @@
         <v>43</v>
       </c>
       <c r="F97" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G97" t="n">
         <v>0.0</v>
@@ -2727,25 +2727,25 @@
         <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C98" t="s">
         <v>16</v>
       </c>
       <c r="D98" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E98" t="s">
         <v>42</v>
       </c>
       <c r="F98" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="99">
@@ -2753,19 +2753,19 @@
         <v>8</v>
       </c>
       <c r="B99" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C99" t="s">
         <v>16</v>
       </c>
       <c r="D99" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E99" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F99" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G99" t="n">
         <v>0.0</v>
@@ -2788,13 +2788,13 @@
         <v>32</v>
       </c>
       <c r="E100" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F100" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G100" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2805,7 +2805,7 @@
         <v>8</v>
       </c>
       <c r="B101" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C101" t="s">
         <v>16</v>
@@ -2817,10 +2817,10 @@
         <v>42</v>
       </c>
       <c r="F101" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G101" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -2831,7 +2831,7 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C102" t="s">
         <v>16</v>
@@ -2840,7 +2840,7 @@
         <v>32</v>
       </c>
       <c r="E102" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F102" t="n">
         <v>1.0</v>
@@ -2857,7 +2857,7 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C103" t="s">
         <v>16</v>
@@ -2869,7 +2869,7 @@
         <v>42</v>
       </c>
       <c r="F103" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
@@ -2883,7 +2883,7 @@
         <v>8</v>
       </c>
       <c r="B104" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C104" t="s">
         <v>16</v>
@@ -2891,14 +2891,14 @@
       <c r="D104" t="s">
         <v>32</v>
       </c>
-      <c r="E104" t="s">
-        <v>43</v>
+      <c r="E104" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F104" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H104" t="n">
         <v>0.0</v>
@@ -2909,7 +2909,7 @@
         <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C105" t="s">
         <v>16</v>
@@ -2921,10 +2921,10 @@
         <v>40</v>
       </c>
       <c r="F105" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H105" t="n">
         <v>0.0</v>
@@ -2935,7 +2935,7 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C106" t="s">
         <v>16</v>
@@ -2947,13 +2947,13 @@
         <v>42</v>
       </c>
       <c r="F106" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H106" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="107">
@@ -2969,14 +2969,14 @@
       <c r="D107" t="s">
         <v>32</v>
       </c>
-      <c r="E107" t="e">
-        <v>#N/A</v>
+      <c r="E107" t="s">
+        <v>43</v>
       </c>
       <c r="F107" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="G107" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H107" t="n">
         <v>0.0</v>
@@ -2987,22 +2987,22 @@
         <v>8</v>
       </c>
       <c r="B108" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C108" t="s">
         <v>16</v>
       </c>
       <c r="D108" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E108" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F108" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G108" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H108" t="n">
         <v>0.0</v>
@@ -3013,22 +3013,22 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C109" t="s">
         <v>16</v>
       </c>
       <c r="D109" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E109" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F109" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="G109" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="H109" t="n">
         <v>0.0</v>
@@ -3039,22 +3039,22 @@
         <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C110" t="s">
         <v>16</v>
       </c>
       <c r="D110" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E110" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F110" t="n">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
       <c r="G110" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H110" t="n">
         <v>0.0</v>
@@ -3074,13 +3074,13 @@
         <v>33</v>
       </c>
       <c r="E111" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F111" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="G111" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3091,7 +3091,7 @@
         <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C112" t="s">
         <v>16</v>
@@ -3100,13 +3100,13 @@
         <v>33</v>
       </c>
       <c r="E112" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F112" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G112" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3117,7 +3117,7 @@
         <v>8</v>
       </c>
       <c r="B113" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C113" t="s">
         <v>16</v>
@@ -3126,7 +3126,7 @@
         <v>33</v>
       </c>
       <c r="E113" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F113" t="n">
         <v>1.0</v>
@@ -3152,13 +3152,13 @@
         <v>33</v>
       </c>
       <c r="E114" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F114" t="n">
         <v>2.0</v>
       </c>
       <c r="G114" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3169,7 +3169,7 @@
         <v>8</v>
       </c>
       <c r="B115" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C115" t="s">
         <v>16</v>
@@ -3177,17 +3177,17 @@
       <c r="D115" t="s">
         <v>33</v>
       </c>
-      <c r="E115" t="s">
-        <v>42</v>
+      <c r="E115" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F115" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="116">
@@ -3195,7 +3195,7 @@
         <v>8</v>
       </c>
       <c r="B116" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C116" t="s">
         <v>16</v>
@@ -3204,13 +3204,13 @@
         <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F116" t="n">
-        <v>2.0</v>
+        <v>86.0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="H116" t="n">
         <v>0.0</v>
@@ -3229,17 +3229,17 @@
       <c r="D117" t="s">
         <v>33</v>
       </c>
-      <c r="E117" t="e">
-        <v>#N/A</v>
+      <c r="E117" t="s">
+        <v>42</v>
       </c>
       <c r="F117" t="n">
-        <v>0.0</v>
+        <v>26.0</v>
       </c>
       <c r="G117" t="n">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="H117" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="118">
@@ -3256,16 +3256,16 @@
         <v>33</v>
       </c>
       <c r="E118" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F118" t="n">
-        <v>88.0</v>
+        <v>514.0</v>
       </c>
       <c r="G118" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="119">
@@ -3282,13 +3282,13 @@
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F119" t="n">
-        <v>26.0</v>
+        <v>0.0</v>
       </c>
       <c r="G119" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="H119" t="n">
         <v>0.0</v>
@@ -3305,19 +3305,19 @@
         <v>16</v>
       </c>
       <c r="D120" t="s">
-        <v>33</v>
-      </c>
-      <c r="E120" t="s">
-        <v>43</v>
+        <v>34</v>
+      </c>
+      <c r="E120" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F120" t="n">
-        <v>522.0</v>
+        <v>1.0</v>
       </c>
       <c r="G120" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H120" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="121">
@@ -3331,16 +3331,16 @@
         <v>16</v>
       </c>
       <c r="D121" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E121" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F121" t="n">
         <v>0.0</v>
       </c>
       <c r="G121" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H121" t="n">
         <v>0.0</v>
@@ -3359,14 +3359,14 @@
       <c r="D122" t="s">
         <v>34</v>
       </c>
-      <c r="E122" t="e">
-        <v>#N/A</v>
+      <c r="E122" t="s">
+        <v>42</v>
       </c>
       <c r="F122" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G122" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3386,13 +3386,13 @@
         <v>34</v>
       </c>
       <c r="E123" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="G123" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>
@@ -3409,16 +3409,16 @@
         <v>16</v>
       </c>
       <c r="D124" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E124" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F124" t="n">
         <v>7.0</v>
       </c>
       <c r="G124" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>
@@ -3435,19 +3435,19 @@
         <v>16</v>
       </c>
       <c r="D125" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E125" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F125" t="n">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
       <c r="G125" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H125" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="126">
@@ -3464,10 +3464,10 @@
         <v>35</v>
       </c>
       <c r="E126" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F126" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="G126" t="n">
         <v>0.0</v>
@@ -3481,25 +3481,25 @@
         <v>8</v>
       </c>
       <c r="B127" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C127" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D127" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E127" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F127" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H127" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="128">
@@ -3507,22 +3507,22 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C128" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D128" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E128" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F128" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H128" t="n">
         <v>0.0</v>
@@ -3542,7 +3542,7 @@
         <v>36</v>
       </c>
       <c r="E129" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F129" t="n">
         <v>0.0</v>
@@ -3568,13 +3568,13 @@
         <v>36</v>
       </c>
       <c r="E130" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F130" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G130" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H130" t="n">
         <v>0.0</v>
@@ -3585,7 +3585,7 @@
         <v>8</v>
       </c>
       <c r="B131" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C131" t="s">
         <v>17</v>
@@ -3594,13 +3594,13 @@
         <v>36</v>
       </c>
       <c r="E131" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F131" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G131" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H131" t="n">
         <v>0.0</v>
@@ -3611,7 +3611,7 @@
         <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C132" t="s">
         <v>17</v>
@@ -3620,13 +3620,13 @@
         <v>36</v>
       </c>
       <c r="E132" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F132" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -3646,13 +3646,13 @@
         <v>36</v>
       </c>
       <c r="E133" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F133" t="n">
         <v>2.0</v>
       </c>
       <c r="G133" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H133" t="n">
         <v>0.0</v>
@@ -3672,13 +3672,13 @@
         <v>36</v>
       </c>
       <c r="E134" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G134" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H134" t="n">
         <v>0.0</v>
@@ -3689,7 +3689,7 @@
         <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C135" t="s">
         <v>17</v>
@@ -3698,13 +3698,13 @@
         <v>36</v>
       </c>
       <c r="E135" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F135" t="n">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3715,7 +3715,7 @@
         <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C136" t="s">
         <v>17</v>
@@ -3723,11 +3723,11 @@
       <c r="D136" t="s">
         <v>36</v>
       </c>
-      <c r="E136" t="s">
-        <v>43</v>
+      <c r="E136" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F136" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G136" t="n">
         <v>0.0</v>
@@ -3750,13 +3750,13 @@
         <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F137" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="G137" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3775,11 +3775,11 @@
       <c r="D138" t="s">
         <v>36</v>
       </c>
-      <c r="E138" t="e">
-        <v>#N/A</v>
+      <c r="E138" t="s">
+        <v>43</v>
       </c>
       <c r="F138" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G138" t="n">
         <v>0.0</v>
@@ -3793,22 +3793,22 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C139" t="s">
         <v>17</v>
       </c>
       <c r="D139" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E139" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F139" t="n">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3819,22 +3819,22 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C140" t="s">
         <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E140" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F140" t="n">
         <v>5.0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H140" t="n">
         <v>0.0</v>
@@ -3854,13 +3854,13 @@
         <v>37</v>
       </c>
       <c r="E141" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F141" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G141" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H141" t="n">
         <v>0.0</v>
@@ -3880,13 +3880,13 @@
         <v>37</v>
       </c>
       <c r="E142" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F142" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G142" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3906,13 +3906,13 @@
         <v>37</v>
       </c>
       <c r="E143" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F143" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G143" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H143" t="n">
         <v>0.0</v>
@@ -3932,10 +3932,10 @@
         <v>37</v>
       </c>
       <c r="E144" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F144" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G144" t="n">
         <v>0.0</v>
@@ -3949,19 +3949,19 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
       </c>
       <c r="D145" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E145" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F145" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G145" t="n">
         <v>0.0</v>
@@ -3975,22 +3975,22 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C146" t="s">
         <v>17</v>
       </c>
       <c r="D146" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E146" t="s">
         <v>43</v>
       </c>
       <c r="F146" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4001,19 +4001,19 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E147" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F147" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G147" t="n">
         <v>0.0</v>
@@ -4027,7 +4027,7 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
@@ -4036,13 +4036,13 @@
         <v>39</v>
       </c>
       <c r="E148" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F148" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G148" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4053,7 +4053,7 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C149" t="s">
         <v>17</v>
@@ -4062,13 +4062,13 @@
         <v>39</v>
       </c>
       <c r="E149" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F149" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4079,7 +4079,7 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C150" t="s">
         <v>17</v>
@@ -4088,13 +4088,13 @@
         <v>39</v>
       </c>
       <c r="E150" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F150" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G150" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G150" t="n">
-        <v>0.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>
@@ -4114,13 +4114,13 @@
         <v>39</v>
       </c>
       <c r="E151" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F151" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G151" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4140,13 +4140,13 @@
         <v>39</v>
       </c>
       <c r="E152" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F152" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G152" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4166,10 +4166,10 @@
         <v>39</v>
       </c>
       <c r="E153" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F153" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G153" t="n">
         <v>1.0</v>
@@ -4192,67 +4192,15 @@
         <v>39</v>
       </c>
       <c r="E154" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F154" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="G154" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H154" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>8</v>
-      </c>
-      <c r="B155" t="s">
-        <v>9</v>
-      </c>
-      <c r="C155" t="s">
-        <v>17</v>
-      </c>
-      <c r="D155" t="s">
-        <v>39</v>
-      </c>
-      <c r="E155" t="s">
-        <v>43</v>
-      </c>
-      <c r="F155" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="G155" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H155" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>8</v>
-      </c>
-      <c r="B156" t="s">
-        <v>9</v>
-      </c>
-      <c r="C156" t="s">
-        <v>17</v>
-      </c>
-      <c r="D156" t="s">
-        <v>39</v>
-      </c>
-      <c r="E156" t="s">
-        <v>44</v>
-      </c>
-      <c r="F156" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G156" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H156" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3259,7 +3259,7 @@
         <v>43</v>
       </c>
       <c r="F118" t="n">
-        <v>514.0</v>
+        <v>513.0</v>
       </c>
       <c r="G118" t="n">
         <v>7.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -2375,7 +2375,7 @@
         <v>43</v>
       </c>
       <c r="F84" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="G84" t="n">
         <v>2.0</v>
@@ -2479,7 +2479,7 @@
         <v>42</v>
       </c>
       <c r="F88" t="n">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2817,7 +2817,7 @@
         <v>42</v>
       </c>
       <c r="F101" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -945,7 +945,7 @@
         <v>42</v>
       </c>
       <c r="F29" t="n">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
       <c r="G29" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3259,7 +3259,7 @@
         <v>43</v>
       </c>
       <c r="F118" t="n">
-        <v>513.0</v>
+        <v>511.0</v>
       </c>
       <c r="G118" t="n">
         <v>7.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -4039,7 +4039,7 @@
         <v>41</v>
       </c>
       <c r="F148" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G148" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1777,7 +1777,7 @@
         <v>40</v>
       </c>
       <c r="F61" t="n">
-        <v>39.0</v>
+        <v>38.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1829,7 +1829,7 @@
         <v>43</v>
       </c>
       <c r="F63" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -971,7 +971,7 @@
         <v>43</v>
       </c>
       <c r="F30" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="G30" t="n">
         <v>0.0</v>
@@ -2427,7 +2427,7 @@
         <v>41</v>
       </c>
       <c r="F86" t="n">
-        <v>42.0</v>
+        <v>38.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -3935,7 +3935,7 @@
         <v>43</v>
       </c>
       <c r="F144" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G144" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1777,7 +1777,7 @@
         <v>40</v>
       </c>
       <c r="F61" t="n">
-        <v>38.0</v>
+        <v>37.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -2271,7 +2271,7 @@
         <v>42</v>
       </c>
       <c r="F80" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="G80" t="n">
         <v>1.0</v>
@@ -3259,7 +3259,7 @@
         <v>43</v>
       </c>
       <c r="F118" t="n">
-        <v>511.0</v>
+        <v>512.0</v>
       </c>
       <c r="G118" t="n">
         <v>7.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="47">
   <si>
     <t>Area</t>
   </si>
@@ -41,15 +41,15 @@
     <t>Pl</t>
   </si>
   <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
     <t>LIM</t>
   </si>
   <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>II</t>
-  </si>
-  <si>
     <t>III</t>
   </si>
   <si>
@@ -134,19 +134,19 @@
     <t>PT</t>
   </si>
   <si>
+    <t>Not for consumption</t>
+  </si>
+  <si>
+    <t>Fattening pigs for own consumption</t>
+  </si>
+  <si>
+    <t>Fattening pigs</t>
+  </si>
+  <si>
+    <t>Hunting facility</t>
+  </si>
+  <si>
     <t>Breeding animals</t>
-  </si>
-  <si>
-    <t>Fattening pigs for own consumption</t>
-  </si>
-  <si>
-    <t>Not for consumption</t>
-  </si>
-  <si>
-    <t>Fattening pigs</t>
-  </si>
-  <si>
-    <t>Hunting facility</t>
   </si>
   <si>
     <t>Zoological garden</t>
@@ -243,10 +243,10 @@
         <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G2" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="H2" t="n">
         <v>0.0</v>
@@ -269,10 +269,10 @@
         <v>41</v>
       </c>
       <c r="F3" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H3" t="n">
         <v>0.0</v>
@@ -295,10 +295,10 @@
         <v>42</v>
       </c>
       <c r="F4" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H4" t="n">
         <v>0.0</v>
@@ -321,7 +321,7 @@
         <v>43</v>
       </c>
       <c r="F5" t="n">
-        <v>35.0</v>
+        <v>0.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -335,7 +335,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -344,10 +344,10 @@
         <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G6" t="n">
         <v>1.0</v>
@@ -361,22 +361,22 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H7" t="n">
         <v>0.0</v>
@@ -387,22 +387,22 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F8" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="H8" t="n">
         <v>0.0</v>
@@ -413,22 +413,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F9" t="n">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="H9" t="n">
         <v>0.0</v>
@@ -445,16 +445,16 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.0</v>
+        <v>30.0</v>
       </c>
       <c r="H10" t="n">
         <v>0.0</v>
@@ -471,10 +471,10 @@
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F11" t="n">
         <v>1.0</v>
@@ -491,7 +491,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
@@ -500,13 +500,13 @@
         <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F12" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G12" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.0</v>
       </c>
       <c r="H12" t="n">
         <v>0.0</v>
@@ -526,13 +526,13 @@
         <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F13" t="n">
-        <v>25.0</v>
+        <v>1.0</v>
       </c>
       <c r="G13" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H13" t="n">
         <v>0.0</v>
@@ -552,13 +552,13 @@
         <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F14" t="n">
         <v>0.0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H14" t="n">
         <v>0.0</v>
@@ -581,10 +581,10 @@
         <v>42</v>
       </c>
       <c r="F15" t="n">
-        <v>30.0</v>
+        <v>0.0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="H15" t="n">
         <v>0.0</v>
@@ -595,7 +595,7 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
@@ -604,10 +604,10 @@
         <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F16" t="n">
-        <v>70.0</v>
+        <v>2.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -627,16 +627,16 @@
         <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s">
         <v>40</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H17" t="n">
         <v>0.0</v>
@@ -653,16 +653,16 @@
         <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F18" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H18" t="n">
         <v>0.0</v>
@@ -679,16 +679,16 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E19" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F19" t="n">
-        <v>11.0</v>
+        <v>2.0</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0</v>
+        <v>25.0</v>
       </c>
       <c r="H19" t="n">
         <v>0.0</v>
@@ -705,16 +705,16 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F20" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0</v>
+        <v>30.0</v>
       </c>
       <c r="H20" t="n">
         <v>0.0</v>
@@ -731,16 +731,16 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0</v>
+        <v>70.0</v>
       </c>
       <c r="H21" t="n">
         <v>0.0</v>
@@ -751,7 +751,7 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
         <v>13</v>
@@ -759,14 +759,14 @@
       <c r="D22" t="s">
         <v>20</v>
       </c>
-      <c r="E22" t="e">
-        <v>#N/A</v>
+      <c r="E22" t="s">
+        <v>44</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H22" t="n">
         <v>0.0</v>
@@ -777,7 +777,7 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
@@ -786,13 +786,13 @@
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F23" t="n">
-        <v>27.0</v>
+        <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="H23" t="n">
         <v>0.0</v>
@@ -809,16 +809,16 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E24" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="H24" t="n">
         <v>0.0</v>
@@ -835,16 +835,16 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F25" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="H25" t="n">
         <v>0.0</v>
@@ -861,16 +861,16 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F26" t="n">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H26" t="n">
         <v>0.0</v>
@@ -881,22 +881,22 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C27" t="s">
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" t="s">
-        <v>40</v>
+        <v>20</v>
+      </c>
+      <c r="E27" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F27" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G27" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H27" t="n">
         <v>0.0</v>
@@ -907,22 +907,22 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28" t="s">
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
       </c>
       <c r="G28" t="n">
-        <v>2.0</v>
+        <v>26.0</v>
       </c>
       <c r="H28" t="n">
         <v>0.0</v>
@@ -933,7 +933,7 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C29" t="s">
         <v>13</v>
@@ -942,13 +942,13 @@
         <v>21</v>
       </c>
       <c r="E29" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F29" t="n">
-        <v>28.0</v>
+        <v>0.0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H29" t="n">
         <v>0.0</v>
@@ -959,7 +959,7 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C30" t="s">
         <v>13</v>
@@ -968,13 +968,13 @@
         <v>21</v>
       </c>
       <c r="E30" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F30" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H30" t="n">
         <v>0.0</v>
@@ -994,13 +994,13 @@
         <v>21</v>
       </c>
       <c r="E31" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F31" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="H31" t="n">
         <v>0.0</v>
@@ -1011,7 +1011,7 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C32" t="s">
         <v>13</v>
@@ -1020,13 +1020,13 @@
         <v>21</v>
       </c>
       <c r="E32" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F32" t="n">
         <v>2.0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H32" t="n">
         <v>0.0</v>
@@ -1037,7 +1037,7 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C33" t="s">
         <v>13</v>
@@ -1049,7 +1049,7 @@
         <v>43</v>
       </c>
       <c r="F33" t="n">
-        <v>11.0</v>
+        <v>2.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -1069,16 +1069,16 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E34" t="s">
         <v>40</v>
       </c>
       <c r="F34" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G34" t="n">
-        <v>3.0</v>
+        <v>28.0</v>
       </c>
       <c r="H34" t="n">
         <v>0.0</v>
@@ -1095,16 +1095,16 @@
         <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E35" t="s">
         <v>42</v>
       </c>
       <c r="F35" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="H35" t="n">
         <v>0.0</v>
@@ -1115,22 +1115,22 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F36" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="G36" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H36" t="n">
         <v>0.0</v>
@@ -1141,22 +1141,22 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C37" t="s">
         <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E37" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F37" t="n">
         <v>0.0</v>
       </c>
       <c r="G37" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H37" t="n">
         <v>0.0</v>
@@ -1173,16 +1173,16 @@
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F38" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G38" t="n">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="H38" t="n">
         <v>0.0</v>
@@ -1193,7 +1193,7 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C39" t="s">
         <v>13</v>
@@ -1202,13 +1202,13 @@
         <v>22</v>
       </c>
       <c r="E39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F39" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G39" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1.0</v>
       </c>
       <c r="H39" t="n">
         <v>0.0</v>
@@ -1219,7 +1219,7 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C40" t="s">
         <v>13</v>
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="E40" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F40" t="n">
         <v>1.0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H40" t="n">
         <v>0.0</v>
@@ -1254,13 +1254,13 @@
         <v>22</v>
       </c>
       <c r="E41" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F41" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G41" t="n">
         <v>13.0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1.0</v>
       </c>
       <c r="H41" t="n">
         <v>0.0</v>
@@ -1280,10 +1280,10 @@
         <v>22</v>
       </c>
       <c r="E42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F42" t="n">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="G42" t="n">
         <v>0.0</v>
@@ -1297,7 +1297,7 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C43" t="s">
         <v>13</v>
@@ -1306,13 +1306,13 @@
         <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F43" t="n">
-        <v>115.0</v>
+        <v>3.0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H43" t="n">
         <v>0.0</v>
@@ -1323,22 +1323,22 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F44" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G44" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>4.0</v>
       </c>
       <c r="H44" t="n">
         <v>0.0</v>
@@ -1349,22 +1349,22 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F45" t="n">
-        <v>22.0</v>
+        <v>0.0</v>
       </c>
       <c r="G45" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H45" t="n">
         <v>0.0</v>
@@ -1378,19 +1378,19 @@
         <v>11</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E46" t="s">
         <v>44</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G46" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
       <c r="H46" t="n">
         <v>0.0</v>
@@ -1404,19 +1404,19 @@
         <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E47" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F47" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1430,19 +1430,19 @@
         <v>11</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E48" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F48" t="n">
         <v>0.0</v>
       </c>
       <c r="G48" t="n">
-        <v>1.0</v>
+        <v>115.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1453,16 +1453,16 @@
         <v>8</v>
       </c>
       <c r="B49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E49" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F49" t="n">
         <v>4.0</v>
@@ -1479,22 +1479,22 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E50" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G50" t="n">
-        <v>1.0</v>
+        <v>22.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -1505,22 +1505,22 @@
         <v>8</v>
       </c>
       <c r="B51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E51" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G51" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H51" t="n">
         <v>0.0</v>
@@ -1531,22 +1531,22 @@
         <v>8</v>
       </c>
       <c r="B52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E52" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F52" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H52" t="n">
         <v>0.0</v>
@@ -1563,13 +1563,13 @@
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E53" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F53" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1583,22 +1583,22 @@
         <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E54" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G54" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H54" t="n">
         <v>0.0</v>
@@ -1609,19 +1609,19 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F55" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G55" t="n">
         <v>0.0</v>
@@ -1635,19 +1635,19 @@
         <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F56" t="n">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1661,13 +1661,13 @@
         <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E57" t="s">
         <v>44</v>
@@ -1676,7 +1676,7 @@
         <v>0.0</v>
       </c>
       <c r="G57" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H57" t="n">
         <v>0.0</v>
@@ -1696,13 +1696,13 @@
         <v>25</v>
       </c>
       <c r="E58" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F58" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G58" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.0</v>
       </c>
       <c r="H58" t="n">
         <v>0.0</v>
@@ -1725,10 +1725,10 @@
         <v>42</v>
       </c>
       <c r="F59" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H59" t="n">
         <v>0.0</v>
@@ -1739,7 +1739,7 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
@@ -1751,7 +1751,7 @@
         <v>43</v>
       </c>
       <c r="F60" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1765,25 +1765,25 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E61" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F61" t="n">
-        <v>37.0</v>
+        <v>0.0</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H61" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="62">
@@ -1791,25 +1791,25 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E62" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F62" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="H62" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="63">
@@ -1817,25 +1817,25 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E63" t="s">
         <v>43</v>
       </c>
       <c r="F63" t="n">
-        <v>172.0</v>
+        <v>1.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
       </c>
       <c r="H63" t="n">
-        <v>34.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="64">
@@ -1843,22 +1843,22 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E64" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F64" t="n">
-        <v>35.0</v>
+        <v>0.0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H64" t="n">
         <v>0.0</v>
@@ -1869,22 +1869,22 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E65" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F65" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H65" t="n">
         <v>0.0</v>
@@ -1895,25 +1895,25 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C66" t="s">
         <v>15</v>
       </c>
       <c r="D66" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E66" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F66" t="n">
-        <v>67.0</v>
+        <v>0.0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0</v>
+        <v>37.0</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="67">
@@ -1921,25 +1921,25 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C67" t="s">
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>28</v>
-      </c>
-      <c r="E67" t="e">
-        <v>#N/A</v>
+        <v>26</v>
+      </c>
+      <c r="E67" t="s">
+        <v>41</v>
       </c>
       <c r="F67" t="n">
         <v>0.0</v>
       </c>
       <c r="G67" t="n">
-        <v>1.0</v>
+        <v>16.0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="68">
@@ -1947,25 +1947,25 @@
         <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C68" t="s">
         <v>15</v>
       </c>
       <c r="D68" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E68" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F68" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="G68" t="n">
-        <v>1.0</v>
+        <v>172.0</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="69">
@@ -1973,22 +1973,22 @@
         <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C69" t="s">
         <v>15</v>
       </c>
       <c r="D69" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E69" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F69" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="G69" t="n">
-        <v>1.0</v>
+        <v>35.0</v>
       </c>
       <c r="H69" t="n">
         <v>0.0</v>
@@ -1999,22 +1999,22 @@
         <v>8</v>
       </c>
       <c r="B70" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C70" t="s">
         <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E70" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F70" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="G70" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H70" t="n">
         <v>0.0</v>
@@ -2025,25 +2025,25 @@
         <v>8</v>
       </c>
       <c r="B71" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C71" t="s">
         <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E71" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F71" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0</v>
+        <v>67.0</v>
       </c>
       <c r="H71" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="72">
@@ -2051,22 +2051,22 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C72" t="s">
         <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>29</v>
-      </c>
-      <c r="E72" t="s">
-        <v>42</v>
+        <v>28</v>
+      </c>
+      <c r="E72" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F72" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="G72" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H72" t="n">
         <v>0.0</v>
@@ -2077,22 +2077,22 @@
         <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C73" t="s">
         <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>29</v>
-      </c>
-      <c r="E73" t="e">
-        <v>#N/A</v>
+        <v>28</v>
+      </c>
+      <c r="E73" t="s">
+        <v>44</v>
       </c>
       <c r="F73" t="n">
         <v>1.0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="H73" t="n">
         <v>0.0</v>
@@ -2103,22 +2103,22 @@
         <v>8</v>
       </c>
       <c r="B74" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C74" t="s">
         <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E74" t="s">
         <v>40</v>
       </c>
       <c r="F74" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2129,22 +2129,22 @@
         <v>8</v>
       </c>
       <c r="B75" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C75" t="s">
         <v>15</v>
       </c>
       <c r="D75" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E75" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F75" t="n">
-        <v>19.0</v>
+        <v>1.0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="H75" t="n">
         <v>0.0</v>
@@ -2161,19 +2161,19 @@
         <v>15</v>
       </c>
       <c r="D76" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E76" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F76" t="n">
         <v>0.0</v>
       </c>
       <c r="G76" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="77">
@@ -2181,7 +2181,7 @@
         <v>8</v>
       </c>
       <c r="B77" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C77" t="s">
         <v>15</v>
@@ -2196,7 +2196,7 @@
         <v>1.0</v>
       </c>
       <c r="G77" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="H77" t="n">
         <v>0.0</v>
@@ -2207,7 +2207,7 @@
         <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C78" t="s">
         <v>15</v>
@@ -2215,14 +2215,14 @@
       <c r="D78" t="s">
         <v>29</v>
       </c>
-      <c r="E78" t="s">
-        <v>42</v>
+      <c r="E78" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F78" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H78" t="n">
         <v>0.0</v>
@@ -2233,7 +2233,7 @@
         <v>8</v>
       </c>
       <c r="B79" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C79" t="s">
         <v>15</v>
@@ -2242,13 +2242,13 @@
         <v>29</v>
       </c>
       <c r="E79" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F79" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H79" t="n">
         <v>0.0</v>
@@ -2271,10 +2271,10 @@
         <v>42</v>
       </c>
       <c r="F80" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="G80" t="n">
-        <v>1.0</v>
+        <v>19.0</v>
       </c>
       <c r="H80" t="n">
         <v>0.0</v>
@@ -2285,7 +2285,7 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C81" t="s">
         <v>15</v>
@@ -2294,10 +2294,10 @@
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F81" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2311,7 +2311,7 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C82" t="s">
         <v>15</v>
@@ -2320,13 +2320,13 @@
         <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F82" t="n">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2337,22 +2337,22 @@
         <v>8</v>
       </c>
       <c r="B83" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C83" t="s">
         <v>15</v>
       </c>
       <c r="D83" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F83" t="n">
         <v>0.0</v>
       </c>
       <c r="G83" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="H83" t="n">
         <v>0.0</v>
@@ -2363,25 +2363,25 @@
         <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C84" t="s">
         <v>15</v>
       </c>
       <c r="D84" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F84" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="G84" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H84" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="85">
@@ -2389,25 +2389,25 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C85" t="s">
         <v>15</v>
       </c>
       <c r="D85" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E85" t="s">
         <v>40</v>
       </c>
       <c r="F85" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H85" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="86">
@@ -2415,25 +2415,25 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C86" t="s">
         <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E86" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F86" t="n">
-        <v>38.0</v>
+        <v>0.0</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H86" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="87">
@@ -2441,25 +2441,25 @@
         <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C87" t="s">
         <v>15</v>
       </c>
       <c r="D87" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E87" t="s">
         <v>42</v>
       </c>
       <c r="F87" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="H87" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="88">
@@ -2467,19 +2467,19 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C88" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D88" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E88" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F88" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2493,25 +2493,25 @@
         <v>8</v>
       </c>
       <c r="B89" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C89" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E89" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F89" t="n">
         <v>2.0</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="90">
@@ -2522,22 +2522,22 @@
         <v>11</v>
       </c>
       <c r="C90" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D90" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E90" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F90" t="n">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
       <c r="G90" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="91">
@@ -2548,22 +2548,22 @@
         <v>11</v>
       </c>
       <c r="C91" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D91" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E91" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F91" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G91" t="n">
-        <v>0.0</v>
+        <v>38.0</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="92">
@@ -2574,22 +2574,22 @@
         <v>11</v>
       </c>
       <c r="C92" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D92" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E92" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F92" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="H92" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G92" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="93">
@@ -2597,7 +2597,7 @@
         <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C93" t="s">
         <v>16</v>
@@ -2606,13 +2606,13 @@
         <v>31</v>
       </c>
       <c r="E93" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F93" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G93" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="H93" t="n">
         <v>0.0</v>
@@ -2623,7 +2623,7 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C94" t="s">
         <v>16</v>
@@ -2632,13 +2632,13 @@
         <v>31</v>
       </c>
       <c r="E94" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F94" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H94" t="n">
         <v>0.0</v>
@@ -2649,7 +2649,7 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C95" t="s">
         <v>16</v>
@@ -2661,10 +2661,10 @@
         <v>40</v>
       </c>
       <c r="F95" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0</v>
+        <v>17.0</v>
       </c>
       <c r="H95" t="n">
         <v>0.0</v>
@@ -2675,7 +2675,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C96" t="s">
         <v>16</v>
@@ -2684,13 +2684,13 @@
         <v>31</v>
       </c>
       <c r="E96" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F96" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H96" t="n">
         <v>0.0</v>
@@ -2701,7 +2701,7 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C97" t="s">
         <v>16</v>
@@ -2710,13 +2710,13 @@
         <v>31</v>
       </c>
       <c r="E97" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F97" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -2727,25 +2727,25 @@
         <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C98" t="s">
         <v>16</v>
       </c>
       <c r="D98" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E98" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F98" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G98" t="n">
         <v>1.0</v>
       </c>
       <c r="H98" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="99">
@@ -2753,22 +2753,22 @@
         <v>8</v>
       </c>
       <c r="B99" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C99" t="s">
         <v>16</v>
       </c>
       <c r="D99" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E99" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F99" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H99" t="n">
         <v>0.0</v>
@@ -2779,22 +2779,22 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C100" t="s">
         <v>16</v>
       </c>
       <c r="D100" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E100" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F100" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G100" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2811,16 +2811,16 @@
         <v>16</v>
       </c>
       <c r="D101" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E101" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F101" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -2831,22 +2831,22 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C102" t="s">
         <v>16</v>
       </c>
       <c r="D102" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E102" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F102" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2857,7 +2857,7 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C103" t="s">
         <v>16</v>
@@ -2866,13 +2866,13 @@
         <v>32</v>
       </c>
       <c r="E103" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F103" t="n">
         <v>1.0</v>
       </c>
       <c r="G103" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H103" t="n">
         <v>1.0</v>
@@ -2891,8 +2891,8 @@
       <c r="D104" t="s">
         <v>32</v>
       </c>
-      <c r="E104" t="e">
-        <v>#N/A</v>
+      <c r="E104" t="s">
+        <v>44</v>
       </c>
       <c r="F104" t="n">
         <v>0.0</v>
@@ -2918,13 +2918,13 @@
         <v>32</v>
       </c>
       <c r="E105" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F105" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G105" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H105" t="n">
         <v>0.0</v>
@@ -2935,7 +2935,7 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C106" t="s">
         <v>16</v>
@@ -2944,13 +2944,13 @@
         <v>32</v>
       </c>
       <c r="E106" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F106" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="G106" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="H106" t="n">
         <v>0.0</v>
@@ -2961,7 +2961,7 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C107" t="s">
         <v>16</v>
@@ -2970,13 +2970,13 @@
         <v>32</v>
       </c>
       <c r="E107" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F107" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="G107" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H107" t="n">
         <v>0.0</v>
@@ -2987,16 +2987,16 @@
         <v>8</v>
       </c>
       <c r="B108" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C108" t="s">
         <v>16</v>
       </c>
       <c r="D108" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E108" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F108" t="n">
         <v>0.0</v>
@@ -3005,7 +3005,7 @@
         <v>1.0</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="109">
@@ -3013,22 +3013,22 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C109" t="s">
         <v>16</v>
       </c>
       <c r="D109" t="s">
-        <v>33</v>
-      </c>
-      <c r="E109" t="s">
-        <v>40</v>
+        <v>32</v>
+      </c>
+      <c r="E109" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F109" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G109" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H109" t="n">
         <v>0.0</v>
@@ -3039,22 +3039,22 @@
         <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C110" t="s">
         <v>16</v>
       </c>
       <c r="D110" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E110" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F110" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G110" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H110" t="n">
         <v>0.0</v>
@@ -3065,22 +3065,22 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C111" t="s">
         <v>16</v>
       </c>
       <c r="D111" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E111" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F111" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3097,16 +3097,16 @@
         <v>16</v>
       </c>
       <c r="D112" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E112" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F112" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G112" t="n">
-        <v>1.0</v>
+        <v>18.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3117,7 +3117,7 @@
         <v>8</v>
       </c>
       <c r="B113" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C113" t="s">
         <v>16</v>
@@ -3126,13 +3126,13 @@
         <v>33</v>
       </c>
       <c r="E113" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F113" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H113" t="n">
         <v>0.0</v>
@@ -3143,7 +3143,7 @@
         <v>8</v>
       </c>
       <c r="B114" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C114" t="s">
         <v>16</v>
@@ -3152,13 +3152,13 @@
         <v>33</v>
       </c>
       <c r="E114" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F114" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3177,17 +3177,17 @@
       <c r="D115" t="s">
         <v>33</v>
       </c>
-      <c r="E115" t="e">
-        <v>#N/A</v>
+      <c r="E115" t="s">
+        <v>42</v>
       </c>
       <c r="F115" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G115" t="n">
-        <v>1.0</v>
+        <v>36.0</v>
       </c>
       <c r="H115" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="116">
@@ -3204,13 +3204,13 @@
         <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F116" t="n">
-        <v>86.0</v>
+        <v>2.0</v>
       </c>
       <c r="G116" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="H116" t="n">
         <v>0.0</v>
@@ -3221,7 +3221,7 @@
         <v>8</v>
       </c>
       <c r="B117" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C117" t="s">
         <v>16</v>
@@ -3230,13 +3230,13 @@
         <v>33</v>
       </c>
       <c r="E117" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F117" t="n">
-        <v>26.0</v>
+        <v>1.0</v>
       </c>
       <c r="G117" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3247,7 +3247,7 @@
         <v>8</v>
       </c>
       <c r="B118" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C118" t="s">
         <v>16</v>
@@ -3256,16 +3256,16 @@
         <v>33</v>
       </c>
       <c r="E118" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F118" t="n">
-        <v>512.0</v>
+        <v>1.0</v>
       </c>
       <c r="G118" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="H118" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="119">
@@ -3273,7 +3273,7 @@
         <v>8</v>
       </c>
       <c r="B119" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C119" t="s">
         <v>16</v>
@@ -3282,13 +3282,13 @@
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F119" t="n">
         <v>0.0</v>
       </c>
       <c r="G119" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H119" t="n">
         <v>0.0</v>
@@ -3299,22 +3299,22 @@
         <v>8</v>
       </c>
       <c r="B120" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C120" t="s">
         <v>16</v>
       </c>
       <c r="D120" t="s">
-        <v>34</v>
-      </c>
-      <c r="E120" t="e">
-        <v>#N/A</v>
+        <v>33</v>
+      </c>
+      <c r="E120" t="s">
+        <v>42</v>
       </c>
       <c r="F120" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G120" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H120" t="n">
         <v>0.0</v>
@@ -3325,25 +3325,25 @@
         <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C121" t="s">
         <v>16</v>
       </c>
       <c r="D121" t="s">
-        <v>34</v>
-      </c>
-      <c r="E121" t="s">
-        <v>40</v>
+        <v>33</v>
+      </c>
+      <c r="E121" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G121" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="122">
@@ -3351,22 +3351,22 @@
         <v>8</v>
       </c>
       <c r="B122" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C122" t="s">
         <v>16</v>
       </c>
       <c r="D122" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E122" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F122" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="G122" t="n">
-        <v>2.0</v>
+        <v>79.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3377,22 +3377,22 @@
         <v>8</v>
       </c>
       <c r="B123" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C123" t="s">
         <v>16</v>
       </c>
       <c r="D123" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E123" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F123" t="n">
         <v>12.0</v>
       </c>
       <c r="G123" t="n">
-        <v>2.0</v>
+        <v>25.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>
@@ -3403,25 +3403,25 @@
         <v>8</v>
       </c>
       <c r="B124" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C124" t="s">
         <v>16</v>
       </c>
       <c r="D124" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E124" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F124" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0</v>
+        <v>485.0</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="125">
@@ -3429,25 +3429,25 @@
         <v>8</v>
       </c>
       <c r="B125" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C125" t="s">
         <v>16</v>
       </c>
       <c r="D125" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E125" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F125" t="n">
-        <v>16.0</v>
+        <v>2.0</v>
       </c>
       <c r="G125" t="n">
         <v>0.0</v>
       </c>
       <c r="H125" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="126">
@@ -3455,22 +3455,22 @@
         <v>8</v>
       </c>
       <c r="B126" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C126" t="s">
         <v>16</v>
       </c>
       <c r="D126" t="s">
-        <v>35</v>
-      </c>
-      <c r="E126" t="s">
-        <v>43</v>
+        <v>34</v>
+      </c>
+      <c r="E126" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F126" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>
@@ -3481,22 +3481,22 @@
         <v>8</v>
       </c>
       <c r="B127" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C127" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D127" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E127" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F127" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G127" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H127" t="n">
         <v>0.0</v>
@@ -3507,22 +3507,22 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C128" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D128" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E128" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F128" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G128" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="H128" t="n">
         <v>0.0</v>
@@ -3533,22 +3533,22 @@
         <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C129" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D129" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E129" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F129" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G129" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -3559,22 +3559,22 @@
         <v>8</v>
       </c>
       <c r="B130" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C130" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D130" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E130" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F130" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H130" t="n">
         <v>0.0</v>
@@ -3588,22 +3588,22 @@
         <v>11</v>
       </c>
       <c r="C131" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D131" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E131" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F131" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G131" t="n">
-        <v>4.0</v>
+        <v>16.0</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="132">
@@ -3614,19 +3614,19 @@
         <v>11</v>
       </c>
       <c r="C132" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D132" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E132" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F132" t="n">
         <v>0.0</v>
       </c>
       <c r="G132" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -3637,7 +3637,7 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C133" t="s">
         <v>17</v>
@@ -3652,7 +3652,7 @@
         <v>2.0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="H133" t="n">
         <v>0.0</v>
@@ -3663,7 +3663,7 @@
         <v>8</v>
       </c>
       <c r="B134" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C134" t="s">
         <v>17</v>
@@ -3675,7 +3675,7 @@
         <v>43</v>
       </c>
       <c r="F134" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G134" t="n">
         <v>0.0</v>
@@ -3698,13 +3698,13 @@
         <v>36</v>
       </c>
       <c r="E135" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F135" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="G135" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3723,14 +3723,14 @@
       <c r="D136" t="s">
         <v>36</v>
       </c>
-      <c r="E136" t="e">
-        <v>#N/A</v>
+      <c r="E136" t="s">
+        <v>42</v>
       </c>
       <c r="F136" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H136" t="n">
         <v>0.0</v>
@@ -3741,7 +3741,7 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C137" t="s">
         <v>17</v>
@@ -3750,13 +3750,13 @@
         <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F137" t="n">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3767,7 +3767,7 @@
         <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C138" t="s">
         <v>17</v>
@@ -3776,13 +3776,13 @@
         <v>36</v>
       </c>
       <c r="E138" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F138" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3793,22 +3793,22 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C139" t="s">
         <v>17</v>
       </c>
       <c r="D139" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E139" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F139" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G139" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3819,22 +3819,22 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C140" t="s">
         <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E140" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F140" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G140" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="H140" t="n">
         <v>0.0</v>
@@ -3845,22 +3845,22 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C141" t="s">
         <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E141" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F141" t="n">
         <v>0.0</v>
       </c>
       <c r="G141" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H141" t="n">
         <v>0.0</v>
@@ -3877,16 +3877,16 @@
         <v>17</v>
       </c>
       <c r="D142" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E142" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F142" t="n">
         <v>1.0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3903,16 +3903,16 @@
         <v>17</v>
       </c>
       <c r="D143" t="s">
-        <v>37</v>
-      </c>
-      <c r="E143" t="s">
-        <v>41</v>
+        <v>36</v>
+      </c>
+      <c r="E143" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F143" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H143" t="n">
         <v>0.0</v>
@@ -3923,7 +3923,7 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C144" t="s">
         <v>17</v>
@@ -3932,13 +3932,13 @@
         <v>37</v>
       </c>
       <c r="E144" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F144" t="n">
         <v>3.0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3949,22 +3949,22 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
       </c>
       <c r="D145" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E145" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F145" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H145" t="n">
         <v>0.0</v>
@@ -3981,16 +3981,16 @@
         <v>17</v>
       </c>
       <c r="D146" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E146" t="s">
         <v>43</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G146" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4007,16 +4007,16 @@
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E147" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F147" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4027,22 +4027,22 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
       </c>
       <c r="D148" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E148" t="s">
         <v>41</v>
       </c>
       <c r="F148" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4053,19 +4053,19 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C149" t="s">
         <v>17</v>
       </c>
       <c r="D149" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E149" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F149" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G149" t="n">
         <v>3.0</v>
@@ -4085,7 +4085,7 @@
         <v>17</v>
       </c>
       <c r="D150" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E150" t="s">
         <v>45</v>
@@ -4094,7 +4094,7 @@
         <v>1.0</v>
       </c>
       <c r="G150" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>
@@ -4111,16 +4111,16 @@
         <v>17</v>
       </c>
       <c r="D151" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E151" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F151" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G151" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4137,16 +4137,16 @@
         <v>17</v>
       </c>
       <c r="D152" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E152" t="s">
         <v>41</v>
       </c>
       <c r="F152" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G152" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4163,13 +4163,13 @@
         <v>17</v>
       </c>
       <c r="D153" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E153" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F153" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G153" t="n">
         <v>1.0</v>
@@ -4189,18 +4189,304 @@
         <v>17</v>
       </c>
       <c r="D154" t="s">
+        <v>38</v>
+      </c>
+      <c r="E154" t="s">
+        <v>43</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>8</v>
+      </c>
+      <c r="B155" t="s">
+        <v>11</v>
+      </c>
+      <c r="C155" t="s">
+        <v>17</v>
+      </c>
+      <c r="D155" t="s">
+        <v>38</v>
+      </c>
+      <c r="E155" t="s">
+        <v>44</v>
+      </c>
+      <c r="F155" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>8</v>
+      </c>
+      <c r="B156" t="s">
+        <v>11</v>
+      </c>
+      <c r="C156" t="s">
+        <v>17</v>
+      </c>
+      <c r="D156" t="s">
+        <v>38</v>
+      </c>
+      <c r="E156" t="s">
+        <v>40</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>8</v>
+      </c>
+      <c r="B157" t="s">
+        <v>9</v>
+      </c>
+      <c r="C157" t="s">
+        <v>17</v>
+      </c>
+      <c r="D157" t="s">
         <v>39</v>
       </c>
-      <c r="E154" t="s">
+      <c r="E157" t="s">
+        <v>46</v>
+      </c>
+      <c r="F157" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>8</v>
+      </c>
+      <c r="B158" t="s">
+        <v>9</v>
+      </c>
+      <c r="C158" t="s">
+        <v>17</v>
+      </c>
+      <c r="D158" t="s">
+        <v>39</v>
+      </c>
+      <c r="E158" t="s">
+        <v>41</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G158" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>8</v>
+      </c>
+      <c r="B159" t="s">
+        <v>9</v>
+      </c>
+      <c r="C159" t="s">
+        <v>17</v>
+      </c>
+      <c r="D159" t="s">
+        <v>39</v>
+      </c>
+      <c r="E159" t="s">
+        <v>42</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G159" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>8</v>
+      </c>
+      <c r="B160" t="s">
+        <v>10</v>
+      </c>
+      <c r="C160" t="s">
+        <v>17</v>
+      </c>
+      <c r="D160" t="s">
+        <v>39</v>
+      </c>
+      <c r="E160" t="s">
+        <v>46</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>8</v>
+      </c>
+      <c r="B161" t="s">
+        <v>10</v>
+      </c>
+      <c r="C161" t="s">
+        <v>17</v>
+      </c>
+      <c r="D161" t="s">
+        <v>39</v>
+      </c>
+      <c r="E161" t="s">
+        <v>45</v>
+      </c>
+      <c r="F161" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G161" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>8</v>
+      </c>
+      <c r="B162" t="s">
+        <v>10</v>
+      </c>
+      <c r="C162" t="s">
+        <v>17</v>
+      </c>
+      <c r="D162" t="s">
+        <v>39</v>
+      </c>
+      <c r="E162" t="s">
         <v>44</v>
       </c>
-      <c r="F154" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G154" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H154" t="n">
+      <c r="F162" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G162" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>8</v>
+      </c>
+      <c r="B163" t="s">
+        <v>10</v>
+      </c>
+      <c r="C163" t="s">
+        <v>17</v>
+      </c>
+      <c r="D163" t="s">
+        <v>39</v>
+      </c>
+      <c r="E163" t="s">
+        <v>41</v>
+      </c>
+      <c r="F163" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G163" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>8</v>
+      </c>
+      <c r="B164" t="s">
+        <v>10</v>
+      </c>
+      <c r="C164" t="s">
+        <v>17</v>
+      </c>
+      <c r="D164" t="s">
+        <v>39</v>
+      </c>
+      <c r="E164" t="s">
+        <v>42</v>
+      </c>
+      <c r="F164" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>8</v>
+      </c>
+      <c r="B165" t="s">
+        <v>10</v>
+      </c>
+      <c r="C165" t="s">
+        <v>17</v>
+      </c>
+      <c r="D165" t="s">
+        <v>39</v>
+      </c>
+      <c r="E165" t="s">
+        <v>43</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H165" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1078,7 +1078,7 @@
         <v>0.0</v>
       </c>
       <c r="G34" t="n">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="H34" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3418,7 +3418,7 @@
         <v>4.0</v>
       </c>
       <c r="G124" t="n">
-        <v>485.0</v>
+        <v>484.0</v>
       </c>
       <c r="H124" t="n">
         <v>1.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -2274,7 +2274,7 @@
         <v>0.0</v>
       </c>
       <c r="G80" t="n">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="H80" t="n">
         <v>0.0</v>
@@ -2560,7 +2560,7 @@
         <v>0.0</v>
       </c>
       <c r="G91" t="n">
-        <v>38.0</v>
+        <v>36.0</v>
       </c>
       <c r="H91" t="n">
         <v>3.0</v>
@@ -2586,7 +2586,7 @@
         <v>0.0</v>
       </c>
       <c r="G92" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="H92" t="n">
         <v>2.0</v>
@@ -3418,7 +3418,7 @@
         <v>4.0</v>
       </c>
       <c r="G124" t="n">
-        <v>484.0</v>
+        <v>485.0</v>
       </c>
       <c r="H124" t="n">
         <v>1.0</v>
@@ -3652,7 +3652,7 @@
         <v>2.0</v>
       </c>
       <c r="G133" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="H133" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -454,7 +454,7 @@
         <v>1.0</v>
       </c>
       <c r="G10" t="n">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
       <c r="H10" t="n">
         <v>0.0</v>
@@ -766,7 +766,7 @@
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H22" t="n">
         <v>0.0</v>
@@ -922,7 +922,7 @@
         <v>0.0</v>
       </c>
       <c r="G28" t="n">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="H28" t="n">
         <v>0.0</v>
@@ -1338,7 +1338,7 @@
         <v>1.0</v>
       </c>
       <c r="G44" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H44" t="n">
         <v>0.0</v>
@@ -1442,7 +1442,7 @@
         <v>0.0</v>
       </c>
       <c r="G48" t="n">
-        <v>115.0</v>
+        <v>114.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1910,7 +1910,7 @@
         <v>0.0</v>
       </c>
       <c r="G66" t="n">
-        <v>37.0</v>
+        <v>36.0</v>
       </c>
       <c r="H66" t="n">
         <v>11.0</v>
@@ -1962,10 +1962,10 @@
         <v>0.0</v>
       </c>
       <c r="G68" t="n">
-        <v>172.0</v>
+        <v>168.0</v>
       </c>
       <c r="H68" t="n">
-        <v>34.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="69">
@@ -1988,7 +1988,7 @@
         <v>0.0</v>
       </c>
       <c r="G69" t="n">
-        <v>35.0</v>
+        <v>34.0</v>
       </c>
       <c r="H69" t="n">
         <v>0.0</v>
@@ -2144,7 +2144,7 @@
         <v>1.0</v>
       </c>
       <c r="G75" t="n">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="H75" t="n">
         <v>0.0</v>
@@ -3184,7 +3184,7 @@
         <v>3.0</v>
       </c>
       <c r="G115" t="n">
-        <v>36.0</v>
+        <v>33.0</v>
       </c>
       <c r="H115" t="n">
         <v>0.0</v>
@@ -3366,7 +3366,7 @@
         <v>9.0</v>
       </c>
       <c r="G122" t="n">
-        <v>79.0</v>
+        <v>78.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3418,7 +3418,7 @@
         <v>4.0</v>
       </c>
       <c r="G124" t="n">
-        <v>485.0</v>
+        <v>472.0</v>
       </c>
       <c r="H124" t="n">
         <v>1.0</v>
@@ -3548,7 +3548,7 @@
         <v>2.0</v>
       </c>
       <c r="G129" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -4068,7 +4068,7 @@
         <v>0.0</v>
       </c>
       <c r="G149" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="47">
   <si>
     <t>Area</t>
   </si>
@@ -44,13 +44,13 @@
     <t>I</t>
   </si>
   <si>
-    <t>II</t>
+    <t>III</t>
   </si>
   <si>
     <t>LIM</t>
   </si>
   <si>
-    <t>III</t>
+    <t>II</t>
   </si>
   <si>
     <t>Emilia romagna</t>
@@ -595,7 +595,7 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
@@ -621,7 +621,7 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s">
         <v>13</v>
@@ -636,7 +636,7 @@
         <v>0.0</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H17" t="n">
         <v>0.0</v>
@@ -647,7 +647,7 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C18" t="s">
         <v>13</v>
@@ -662,7 +662,7 @@
         <v>0.0</v>
       </c>
       <c r="G18" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H18" t="n">
         <v>0.0</v>
@@ -673,7 +673,7 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C19" t="s">
         <v>13</v>
@@ -682,13 +682,13 @@
         <v>19</v>
       </c>
       <c r="E19" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G19" t="n">
-        <v>25.0</v>
+        <v>1.0</v>
       </c>
       <c r="H19" t="n">
         <v>0.0</v>
@@ -699,7 +699,7 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C20" t="s">
         <v>13</v>
@@ -708,13 +708,13 @@
         <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F20" t="n">
         <v>0.0</v>
       </c>
       <c r="G20" t="n">
-        <v>30.0</v>
+        <v>1.0</v>
       </c>
       <c r="H20" t="n">
         <v>0.0</v>
@@ -734,13 +734,13 @@
         <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G21" t="n">
-        <v>70.0</v>
+        <v>25.0</v>
       </c>
       <c r="H21" t="n">
         <v>0.0</v>
@@ -751,22 +751,22 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C22" t="s">
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E22" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0</v>
+        <v>30.0</v>
       </c>
       <c r="H22" t="n">
         <v>0.0</v>
@@ -777,13 +777,13 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E23" t="s">
         <v>42</v>
@@ -792,7 +792,7 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>9.0</v>
+        <v>70.0</v>
       </c>
       <c r="H23" t="n">
         <v>0.0</v>
@@ -803,7 +803,7 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C24" t="s">
         <v>13</v>
@@ -815,10 +815,10 @@
         <v>44</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="H24" t="n">
         <v>0.0</v>
@@ -829,7 +829,7 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C25" t="s">
         <v>13</v>
@@ -838,13 +838,13 @@
         <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G25" t="n">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="H25" t="n">
         <v>0.0</v>
@@ -855,7 +855,7 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
@@ -864,13 +864,13 @@
         <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="H26" t="n">
         <v>0.0</v>
@@ -881,7 +881,7 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C27" t="s">
         <v>13</v>
@@ -889,14 +889,14 @@
       <c r="D27" t="s">
         <v>20</v>
       </c>
-      <c r="E27" t="e">
-        <v>#N/A</v>
+      <c r="E27" t="s">
+        <v>40</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G27" t="n">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="H27" t="n">
         <v>0.0</v>
@@ -907,7 +907,7 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C28" t="s">
         <v>13</v>
@@ -916,13 +916,13 @@
         <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
       </c>
       <c r="G28" t="n">
-        <v>25.0</v>
+        <v>1.0</v>
       </c>
       <c r="H28" t="n">
         <v>0.0</v>
@@ -933,16 +933,16 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C29" t="s">
         <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" t="s">
-        <v>44</v>
+        <v>20</v>
+      </c>
+      <c r="E29" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -959,22 +959,22 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C30" t="s">
         <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
       </c>
       <c r="G30" t="n">
-        <v>6.0</v>
+        <v>25.0</v>
       </c>
       <c r="H30" t="n">
         <v>0.0</v>
@@ -994,13 +994,13 @@
         <v>21</v>
       </c>
       <c r="E31" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
       </c>
       <c r="G31" t="n">
-        <v>20.0</v>
+        <v>1.0</v>
       </c>
       <c r="H31" t="n">
         <v>0.0</v>
@@ -1011,7 +1011,7 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" t="s">
         <v>13</v>
@@ -1020,13 +1020,13 @@
         <v>21</v>
       </c>
       <c r="E32" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F32" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G32" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="H32" t="n">
         <v>0.0</v>
@@ -1037,7 +1037,7 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C33" t="s">
         <v>13</v>
@@ -1046,13 +1046,13 @@
         <v>21</v>
       </c>
       <c r="E33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F33" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="H33" t="n">
         <v>0.0</v>
@@ -1063,7 +1063,7 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C34" t="s">
         <v>13</v>
@@ -1072,13 +1072,13 @@
         <v>21</v>
       </c>
       <c r="E34" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G34" t="n">
-        <v>27.0</v>
+        <v>3.0</v>
       </c>
       <c r="H34" t="n">
         <v>0.0</v>
@@ -1089,7 +1089,7 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
         <v>13</v>
@@ -1098,13 +1098,13 @@
         <v>21</v>
       </c>
       <c r="E35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G35" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="H35" t="n">
         <v>0.0</v>
@@ -1115,7 +1115,7 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
@@ -1124,13 +1124,13 @@
         <v>21</v>
       </c>
       <c r="E36" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F36" t="n">
         <v>0.0</v>
       </c>
       <c r="G36" t="n">
-        <v>3.0</v>
+        <v>27.0</v>
       </c>
       <c r="H36" t="n">
         <v>0.0</v>
@@ -1141,7 +1141,7 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
         <v>13</v>
@@ -1150,13 +1150,13 @@
         <v>21</v>
       </c>
       <c r="E37" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F37" t="n">
         <v>0.0</v>
       </c>
       <c r="G37" t="n">
-        <v>2.0</v>
+        <v>14.0</v>
       </c>
       <c r="H37" t="n">
         <v>0.0</v>
@@ -1176,13 +1176,13 @@
         <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F38" t="n">
         <v>0.0</v>
       </c>
       <c r="G38" t="n">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
       <c r="H38" t="n">
         <v>0.0</v>
@@ -1193,19 +1193,19 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C39" t="s">
         <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F39" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G39" t="n">
         <v>2.0</v>
@@ -1219,22 +1219,22 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C40" t="s">
         <v>13</v>
       </c>
       <c r="D40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E40" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F40" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G40" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
       <c r="H40" t="n">
         <v>0.0</v>
@@ -1254,13 +1254,13 @@
         <v>22</v>
       </c>
       <c r="E41" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F41" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G41" t="n">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="H41" t="n">
         <v>0.0</v>
@@ -1280,13 +1280,13 @@
         <v>22</v>
       </c>
       <c r="E42" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F42" t="n">
         <v>1.0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H42" t="n">
         <v>0.0</v>
@@ -1297,7 +1297,7 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C43" t="s">
         <v>13</v>
@@ -1306,13 +1306,13 @@
         <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F43" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G43" t="n">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
       <c r="H43" t="n">
         <v>0.0</v>
@@ -1323,7 +1323,7 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C44" t="s">
         <v>13</v>
@@ -1332,13 +1332,13 @@
         <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F44" t="n">
         <v>1.0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H44" t="n">
         <v>0.0</v>
@@ -1349,7 +1349,7 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C45" t="s">
         <v>13</v>
@@ -1358,13 +1358,13 @@
         <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G45" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H45" t="n">
         <v>0.0</v>
@@ -1375,7 +1375,7 @@
         <v>8</v>
       </c>
       <c r="B46" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
         <v>13</v>
@@ -1384,13 +1384,13 @@
         <v>22</v>
       </c>
       <c r="E46" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F46" t="n">
         <v>1.0</v>
       </c>
       <c r="G46" t="n">
-        <v>13.0</v>
+        <v>1.0</v>
       </c>
       <c r="H46" t="n">
         <v>0.0</v>
@@ -1401,7 +1401,7 @@
         <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C47" t="s">
         <v>13</v>
@@ -1416,7 +1416,7 @@
         <v>0.0</v>
       </c>
       <c r="G47" t="n">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1436,13 +1436,13 @@
         <v>22</v>
       </c>
       <c r="E48" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G48" t="n">
-        <v>114.0</v>
+        <v>13.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1453,22 +1453,22 @@
         <v>8</v>
       </c>
       <c r="B49" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E49" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F49" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G49" t="n">
-        <v>2.0</v>
+        <v>16.0</v>
       </c>
       <c r="H49" t="n">
         <v>0.0</v>
@@ -1479,22 +1479,22 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E50" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F50" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G50" t="n">
-        <v>22.0</v>
+        <v>114.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -1505,7 +1505,7 @@
         <v>8</v>
       </c>
       <c r="B51" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
@@ -1514,13 +1514,13 @@
         <v>23</v>
       </c>
       <c r="E51" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F51" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H51" t="n">
         <v>0.0</v>
@@ -1531,7 +1531,7 @@
         <v>8</v>
       </c>
       <c r="B52" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
@@ -1540,13 +1540,13 @@
         <v>23</v>
       </c>
       <c r="E52" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G52" t="n">
-        <v>1.0</v>
+        <v>22.0</v>
       </c>
       <c r="H52" t="n">
         <v>0.0</v>
@@ -1557,16 +1557,16 @@
         <v>8</v>
       </c>
       <c r="B53" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E53" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F53" t="n">
         <v>1.0</v>
@@ -1583,22 +1583,22 @@
         <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E54" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F54" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G54" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H54" t="n">
         <v>0.0</v>
@@ -1609,7 +1609,7 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
@@ -1618,7 +1618,7 @@
         <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F55" t="n">
         <v>1.0</v>
@@ -1635,7 +1635,7 @@
         <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -1644,13 +1644,13 @@
         <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F56" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H56" t="n">
         <v>0.0</v>
@@ -1661,7 +1661,7 @@
         <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
@@ -1670,13 +1670,13 @@
         <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G57" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H57" t="n">
         <v>0.0</v>
@@ -1687,22 +1687,22 @@
         <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C58" t="s">
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G58" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H58" t="n">
         <v>0.0</v>
@@ -1713,22 +1713,22 @@
         <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C59" t="s">
         <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F59" t="n">
         <v>0.0</v>
       </c>
       <c r="G59" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H59" t="n">
         <v>0.0</v>
@@ -1739,7 +1739,7 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
@@ -1748,13 +1748,13 @@
         <v>25</v>
       </c>
       <c r="E60" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F60" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G60" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0.0</v>
       </c>
       <c r="H60" t="n">
         <v>0.0</v>
@@ -1765,7 +1765,7 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="E61" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F61" t="n">
         <v>0.0</v>
       </c>
       <c r="G61" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H61" t="n">
         <v>0.0</v>
@@ -1791,7 +1791,7 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
@@ -1800,13 +1800,13 @@
         <v>25</v>
       </c>
       <c r="E62" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G62" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="H62" t="n">
         <v>0.0</v>
@@ -1817,7 +1817,7 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C63" t="s">
         <v>14</v>
@@ -1826,13 +1826,13 @@
         <v>25</v>
       </c>
       <c r="E63" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F63" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H63" t="n">
         <v>0.0</v>
@@ -1843,7 +1843,7 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
@@ -1852,13 +1852,13 @@
         <v>25</v>
       </c>
       <c r="E64" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F64" t="n">
         <v>0.0</v>
       </c>
       <c r="G64" t="n">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="H64" t="n">
         <v>0.0</v>
@@ -1878,13 +1878,13 @@
         <v>25</v>
       </c>
       <c r="E65" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G65" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H65" t="n">
         <v>0.0</v>
@@ -1898,22 +1898,22 @@
         <v>11</v>
       </c>
       <c r="C66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E66" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F66" t="n">
         <v>0.0</v>
       </c>
       <c r="G66" t="n">
-        <v>36.0</v>
+        <v>2.0</v>
       </c>
       <c r="H66" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="67">
@@ -1924,22 +1924,22 @@
         <v>11</v>
       </c>
       <c r="C67" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E67" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F67" t="n">
         <v>0.0</v>
       </c>
       <c r="G67" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
       <c r="H67" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="68">
@@ -1956,16 +1956,16 @@
         <v>26</v>
       </c>
       <c r="E68" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F68" t="n">
         <v>0.0</v>
       </c>
       <c r="G68" t="n">
-        <v>168.0</v>
+        <v>36.0</v>
       </c>
       <c r="H68" t="n">
-        <v>33.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="69">
@@ -1979,19 +1979,19 @@
         <v>15</v>
       </c>
       <c r="D69" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E69" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F69" t="n">
         <v>0.0</v>
       </c>
       <c r="G69" t="n">
-        <v>34.0</v>
+        <v>16.0</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="70">
@@ -2005,19 +2005,19 @@
         <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E70" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F70" t="n">
         <v>0.0</v>
       </c>
       <c r="G70" t="n">
-        <v>3.0</v>
+        <v>168.0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="71">
@@ -2034,13 +2034,13 @@
         <v>27</v>
       </c>
       <c r="E71" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F71" t="n">
         <v>0.0</v>
       </c>
       <c r="G71" t="n">
-        <v>67.0</v>
+        <v>33.0</v>
       </c>
       <c r="H71" t="n">
         <v>0.0</v>
@@ -2057,16 +2057,16 @@
         <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>28</v>
-      </c>
-      <c r="E72" t="e">
-        <v>#N/A</v>
+        <v>27</v>
+      </c>
+      <c r="E72" t="s">
+        <v>40</v>
       </c>
       <c r="F72" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H72" t="n">
         <v>0.0</v>
@@ -2083,16 +2083,16 @@
         <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E73" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F73" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G73" t="n">
-        <v>18.0</v>
+        <v>68.0</v>
       </c>
       <c r="H73" t="n">
         <v>0.0</v>
@@ -2111,14 +2111,14 @@
       <c r="D74" t="s">
         <v>28</v>
       </c>
-      <c r="E74" t="s">
-        <v>40</v>
+      <c r="E74" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F74" t="n">
         <v>1.0</v>
       </c>
       <c r="G74" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2138,13 +2138,13 @@
         <v>28</v>
       </c>
       <c r="E75" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F75" t="n">
         <v>1.0</v>
       </c>
       <c r="G75" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="H75" t="n">
         <v>0.0</v>
@@ -2164,16 +2164,16 @@
         <v>28</v>
       </c>
       <c r="E76" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G76" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H76" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="77">
@@ -2181,22 +2181,22 @@
         <v>8</v>
       </c>
       <c r="B77" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C77" t="s">
         <v>15</v>
       </c>
       <c r="D77" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E77" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F77" t="n">
         <v>1.0</v>
       </c>
       <c r="G77" t="n">
-        <v>8.0</v>
+        <v>17.0</v>
       </c>
       <c r="H77" t="n">
         <v>0.0</v>
@@ -2207,25 +2207,25 @@
         <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C78" t="s">
         <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>29</v>
-      </c>
-      <c r="E78" t="e">
-        <v>#N/A</v>
+        <v>28</v>
+      </c>
+      <c r="E78" t="s">
+        <v>41</v>
       </c>
       <c r="F78" t="n">
         <v>0.0</v>
       </c>
       <c r="G78" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="79">
@@ -2242,13 +2242,13 @@
         <v>29</v>
       </c>
       <c r="E79" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G79" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="H79" t="n">
         <v>0.0</v>
@@ -2267,14 +2267,14 @@
       <c r="D80" t="s">
         <v>29</v>
       </c>
-      <c r="E80" t="s">
-        <v>42</v>
+      <c r="E80" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F80" t="n">
         <v>0.0</v>
       </c>
       <c r="G80" t="n">
-        <v>18.0</v>
+        <v>1.0</v>
       </c>
       <c r="H80" t="n">
         <v>0.0</v>
@@ -2285,7 +2285,7 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C81" t="s">
         <v>15</v>
@@ -2294,13 +2294,13 @@
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F81" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H81" t="n">
         <v>0.0</v>
@@ -2311,7 +2311,7 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C82" t="s">
         <v>15</v>
@@ -2320,13 +2320,13 @@
         <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F82" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G82" t="n">
-        <v>1.0</v>
+        <v>18.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2337,7 +2337,7 @@
         <v>8</v>
       </c>
       <c r="B83" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C83" t="s">
         <v>15</v>
@@ -2346,13 +2346,13 @@
         <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G83" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H83" t="n">
         <v>0.0</v>
@@ -2363,7 +2363,7 @@
         <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C84" t="s">
         <v>15</v>
@@ -2372,13 +2372,13 @@
         <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G84" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H84" t="n">
         <v>0.0</v>
@@ -2389,7 +2389,7 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C85" t="s">
         <v>15</v>
@@ -2401,7 +2401,7 @@
         <v>40</v>
       </c>
       <c r="F85" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G85" t="n">
         <v>8.0</v>
@@ -2415,7 +2415,7 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C86" t="s">
         <v>15</v>
@@ -2424,13 +2424,13 @@
         <v>29</v>
       </c>
       <c r="E86" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F86" t="n">
         <v>0.0</v>
       </c>
       <c r="G86" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="H86" t="n">
         <v>0.0</v>
@@ -2450,13 +2450,13 @@
         <v>29</v>
       </c>
       <c r="E87" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F87" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G87" t="n">
-        <v>14.0</v>
+        <v>8.0</v>
       </c>
       <c r="H87" t="n">
         <v>0.0</v>
@@ -2473,16 +2473,16 @@
         <v>15</v>
       </c>
       <c r="D88" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E88" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F88" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H88" t="n">
         <v>0.0</v>
@@ -2499,19 +2499,19 @@
         <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E89" t="s">
         <v>42</v>
       </c>
       <c r="F89" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G89" t="n">
-        <v>8.0</v>
+        <v>14.0</v>
       </c>
       <c r="H89" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="90">
@@ -2528,16 +2528,16 @@
         <v>30</v>
       </c>
       <c r="E90" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G90" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H90" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="91">
@@ -2554,16 +2554,16 @@
         <v>30</v>
       </c>
       <c r="E91" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G91" t="n">
-        <v>36.0</v>
+        <v>8.0</v>
       </c>
       <c r="H91" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="92">
@@ -2580,16 +2580,16 @@
         <v>30</v>
       </c>
       <c r="E92" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F92" t="n">
         <v>0.0</v>
       </c>
       <c r="G92" t="n">
-        <v>14.0</v>
+        <v>5.0</v>
       </c>
       <c r="H92" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="93">
@@ -2597,25 +2597,25 @@
         <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C93" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D93" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E93" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F93" t="n">
         <v>0.0</v>
       </c>
       <c r="G93" t="n">
-        <v>10.0</v>
+        <v>36.0</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="94">
@@ -2623,25 +2623,25 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C94" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D94" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E94" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F94" t="n">
         <v>0.0</v>
       </c>
       <c r="G94" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="H94" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="95">
@@ -2649,7 +2649,7 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C95" t="s">
         <v>16</v>
@@ -2661,10 +2661,10 @@
         <v>40</v>
       </c>
       <c r="F95" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G95" t="n">
-        <v>17.0</v>
+        <v>10.0</v>
       </c>
       <c r="H95" t="n">
         <v>0.0</v>
@@ -2675,7 +2675,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C96" t="s">
         <v>16</v>
@@ -2684,13 +2684,13 @@
         <v>31</v>
       </c>
       <c r="E96" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F96" t="n">
         <v>0.0</v>
       </c>
       <c r="G96" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H96" t="n">
         <v>0.0</v>
@@ -2701,7 +2701,7 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C97" t="s">
         <v>16</v>
@@ -2710,13 +2710,13 @@
         <v>31</v>
       </c>
       <c r="E97" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F97" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G97" t="n">
-        <v>2.0</v>
+        <v>17.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -2736,10 +2736,10 @@
         <v>31</v>
       </c>
       <c r="E98" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F98" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G98" t="n">
         <v>1.0</v>
@@ -2768,7 +2768,7 @@
         <v>0.0</v>
       </c>
       <c r="G99" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H99" t="n">
         <v>0.0</v>
@@ -2779,7 +2779,7 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C100" t="s">
         <v>16</v>
@@ -2788,13 +2788,13 @@
         <v>31</v>
       </c>
       <c r="E100" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F100" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G100" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2805,7 +2805,7 @@
         <v>8</v>
       </c>
       <c r="B101" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C101" t="s">
         <v>16</v>
@@ -2814,13 +2814,13 @@
         <v>31</v>
       </c>
       <c r="E101" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F101" t="n">
         <v>0.0</v>
       </c>
       <c r="G101" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -2840,13 +2840,13 @@
         <v>31</v>
       </c>
       <c r="E102" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F102" t="n">
         <v>0.0</v>
       </c>
       <c r="G102" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2857,25 +2857,25 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C103" t="s">
         <v>16</v>
       </c>
       <c r="D103" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E103" t="s">
         <v>40</v>
       </c>
       <c r="F103" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G103" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="H103" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="104">
@@ -2883,22 +2883,22 @@
         <v>8</v>
       </c>
       <c r="B104" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C104" t="s">
         <v>16</v>
       </c>
       <c r="D104" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E104" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F104" t="n">
         <v>0.0</v>
       </c>
       <c r="G104" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H104" t="n">
         <v>0.0</v>
@@ -2918,16 +2918,16 @@
         <v>32</v>
       </c>
       <c r="E105" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G105" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="106">
@@ -2935,7 +2935,7 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C106" t="s">
         <v>16</v>
@@ -2944,7 +2944,7 @@
         <v>32</v>
       </c>
       <c r="E106" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F106" t="n">
         <v>0.0</v>
@@ -2961,7 +2961,7 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C107" t="s">
         <v>16</v>
@@ -2970,13 +2970,13 @@
         <v>32</v>
       </c>
       <c r="E107" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F107" t="n">
         <v>0.0</v>
       </c>
       <c r="G107" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H107" t="n">
         <v>0.0</v>
@@ -3005,7 +3005,7 @@
         <v>1.0</v>
       </c>
       <c r="H108" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="109">
@@ -3013,7 +3013,7 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C109" t="s">
         <v>16</v>
@@ -3021,14 +3021,14 @@
       <c r="D109" t="s">
         <v>32</v>
       </c>
-      <c r="E109" t="e">
-        <v>#N/A</v>
+      <c r="E109" t="s">
+        <v>44</v>
       </c>
       <c r="F109" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G109" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H109" t="n">
         <v>0.0</v>
@@ -3039,7 +3039,7 @@
         <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C110" t="s">
         <v>16</v>
@@ -3048,16 +3048,16 @@
         <v>32</v>
       </c>
       <c r="E110" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F110" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G110" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="111">
@@ -3073,14 +3073,14 @@
       <c r="D111" t="s">
         <v>32</v>
       </c>
-      <c r="E111" t="s">
-        <v>40</v>
+      <c r="E111" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F111" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G111" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3100,13 +3100,13 @@
         <v>32</v>
       </c>
       <c r="E112" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F112" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G112" t="n">
-        <v>18.0</v>
+        <v>4.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3117,22 +3117,22 @@
         <v>8</v>
       </c>
       <c r="B113" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C113" t="s">
         <v>16</v>
       </c>
       <c r="D113" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E113" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F113" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="G113" t="n">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="H113" t="n">
         <v>0.0</v>
@@ -3143,22 +3143,22 @@
         <v>8</v>
       </c>
       <c r="B114" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C114" t="s">
         <v>16</v>
       </c>
       <c r="D114" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E114" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F114" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G114" t="n">
-        <v>1.0</v>
+        <v>18.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3178,13 +3178,13 @@
         <v>33</v>
       </c>
       <c r="E115" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F115" t="n">
         <v>3.0</v>
       </c>
       <c r="G115" t="n">
-        <v>33.0</v>
+        <v>7.0</v>
       </c>
       <c r="H115" t="n">
         <v>0.0</v>
@@ -3204,13 +3204,13 @@
         <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F116" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H116" t="n">
         <v>0.0</v>
@@ -3221,7 +3221,7 @@
         <v>8</v>
       </c>
       <c r="B117" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C117" t="s">
         <v>16</v>
@@ -3230,13 +3230,13 @@
         <v>33</v>
       </c>
       <c r="E117" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F117" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0</v>
+        <v>33.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3247,7 +3247,7 @@
         <v>8</v>
       </c>
       <c r="B118" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C118" t="s">
         <v>16</v>
@@ -3256,13 +3256,13 @@
         <v>33</v>
       </c>
       <c r="E118" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F118" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G118" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H118" t="n">
         <v>0.0</v>
@@ -3273,7 +3273,7 @@
         <v>8</v>
       </c>
       <c r="B119" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C119" t="s">
         <v>16</v>
@@ -3282,13 +3282,13 @@
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G119" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H119" t="n">
         <v>0.0</v>
@@ -3299,7 +3299,7 @@
         <v>8</v>
       </c>
       <c r="B120" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C120" t="s">
         <v>16</v>
@@ -3308,13 +3308,13 @@
         <v>33</v>
       </c>
       <c r="E120" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F120" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G120" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H120" t="n">
         <v>0.0</v>
@@ -3325,7 +3325,7 @@
         <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C121" t="s">
         <v>16</v>
@@ -3333,17 +3333,17 @@
       <c r="D121" t="s">
         <v>33</v>
       </c>
-      <c r="E121" t="e">
-        <v>#N/A</v>
+      <c r="E121" t="s">
+        <v>40</v>
       </c>
       <c r="F121" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H121" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="122">
@@ -3351,7 +3351,7 @@
         <v>8</v>
       </c>
       <c r="B122" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C122" t="s">
         <v>16</v>
@@ -3360,13 +3360,13 @@
         <v>33</v>
       </c>
       <c r="E122" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F122" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="G122" t="n">
-        <v>78.0</v>
+        <v>2.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3385,17 +3385,17 @@
       <c r="D123" t="s">
         <v>33</v>
       </c>
-      <c r="E123" t="s">
-        <v>40</v>
+      <c r="E123" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F123" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G123" t="n">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="124">
@@ -3412,16 +3412,16 @@
         <v>33</v>
       </c>
       <c r="E124" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F124" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="G124" t="n">
-        <v>472.0</v>
+        <v>78.0</v>
       </c>
       <c r="H124" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="125">
@@ -3438,13 +3438,13 @@
         <v>33</v>
       </c>
       <c r="E125" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F125" t="n">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0</v>
+        <v>25.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3461,19 +3461,19 @@
         <v>16</v>
       </c>
       <c r="D126" t="s">
-        <v>34</v>
-      </c>
-      <c r="E126" t="e">
-        <v>#N/A</v>
+        <v>33</v>
+      </c>
+      <c r="E126" t="s">
+        <v>42</v>
       </c>
       <c r="F126" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G126" t="n">
-        <v>1.0</v>
+        <v>472.0</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="127">
@@ -3487,13 +3487,13 @@
         <v>16</v>
       </c>
       <c r="D127" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E127" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F127" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G127" t="n">
         <v>0.0</v>
@@ -3515,14 +3515,14 @@
       <c r="D128" t="s">
         <v>34</v>
       </c>
-      <c r="E128" t="s">
-        <v>40</v>
+      <c r="E128" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F128" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G128" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H128" t="n">
         <v>0.0</v>
@@ -3542,13 +3542,13 @@
         <v>34</v>
       </c>
       <c r="E129" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F129" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G129" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -3565,13 +3565,13 @@
         <v>16</v>
       </c>
       <c r="D130" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E130" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F130" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G130" t="n">
         <v>7.0</v>
@@ -3591,19 +3591,19 @@
         <v>16</v>
       </c>
       <c r="D131" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E131" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F131" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G131" t="n">
-        <v>16.0</v>
+        <v>11.0</v>
       </c>
       <c r="H131" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="132">
@@ -3620,13 +3620,13 @@
         <v>35</v>
       </c>
       <c r="E132" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F132" t="n">
         <v>0.0</v>
       </c>
       <c r="G132" t="n">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -3637,25 +3637,25 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C133" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D133" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E133" t="s">
         <v>40</v>
       </c>
       <c r="F133" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G133" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="H133" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="134">
@@ -3663,22 +3663,22 @@
         <v>8</v>
       </c>
       <c r="B134" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C134" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D134" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E134" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F134" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H134" t="n">
         <v>0.0</v>
@@ -3698,13 +3698,13 @@
         <v>36</v>
       </c>
       <c r="E135" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G135" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3724,13 +3724,13 @@
         <v>36</v>
       </c>
       <c r="E136" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F136" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G136" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="H136" t="n">
         <v>0.0</v>
@@ -3741,7 +3741,7 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C137" t="s">
         <v>17</v>
@@ -3750,13 +3750,13 @@
         <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F137" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G137" t="n">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3767,7 +3767,7 @@
         <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C138" t="s">
         <v>17</v>
@@ -3776,13 +3776,13 @@
         <v>36</v>
       </c>
       <c r="E138" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F138" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G138" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3793,7 +3793,7 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C139" t="s">
         <v>17</v>
@@ -3802,13 +3802,13 @@
         <v>36</v>
       </c>
       <c r="E139" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F139" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3819,7 +3819,7 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C140" t="s">
         <v>17</v>
@@ -3828,13 +3828,13 @@
         <v>36</v>
       </c>
       <c r="E140" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F140" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G140" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H140" t="n">
         <v>0.0</v>
@@ -3845,7 +3845,7 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C141" t="s">
         <v>17</v>
@@ -3854,7 +3854,7 @@
         <v>36</v>
       </c>
       <c r="E141" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F141" t="n">
         <v>0.0</v>
@@ -3871,7 +3871,7 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C142" t="s">
         <v>17</v>
@@ -3880,13 +3880,13 @@
         <v>36</v>
       </c>
       <c r="E142" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F142" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G142" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3897,7 +3897,7 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C143" t="s">
         <v>17</v>
@@ -3905,14 +3905,14 @@
       <c r="D143" t="s">
         <v>36</v>
       </c>
-      <c r="E143" t="e">
-        <v>#N/A</v>
+      <c r="E143" t="s">
+        <v>42</v>
       </c>
       <c r="F143" t="n">
         <v>0.0</v>
       </c>
       <c r="G143" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H143" t="n">
         <v>0.0</v>
@@ -3929,16 +3929,16 @@
         <v>17</v>
       </c>
       <c r="D144" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E144" t="s">
         <v>44</v>
       </c>
       <c r="F144" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G144" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3949,19 +3949,19 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
       </c>
       <c r="D145" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E145" t="s">
         <v>40</v>
       </c>
       <c r="F145" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G145" t="n">
         <v>5.0</v>
@@ -3975,22 +3975,22 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C146" t="s">
         <v>17</v>
       </c>
       <c r="D146" t="s">
-        <v>37</v>
-      </c>
-      <c r="E146" t="s">
-        <v>43</v>
+        <v>36</v>
+      </c>
+      <c r="E146" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F146" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4001,7 +4001,7 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
@@ -4010,13 +4010,13 @@
         <v>37</v>
       </c>
       <c r="E147" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G147" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4027,7 +4027,7 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
@@ -4036,13 +4036,13 @@
         <v>37</v>
       </c>
       <c r="E148" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F148" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G148" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4053,7 +4053,7 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C149" t="s">
         <v>17</v>
@@ -4062,13 +4062,13 @@
         <v>37</v>
       </c>
       <c r="E149" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F149" t="n">
         <v>0.0</v>
       </c>
       <c r="G149" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4079,22 +4079,22 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C150" t="s">
         <v>17</v>
       </c>
       <c r="D150" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E150" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F150" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>
@@ -4105,22 +4105,22 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
       </c>
       <c r="D151" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E151" t="s">
         <v>44</v>
       </c>
       <c r="F151" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4131,22 +4131,22 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C152" t="s">
         <v>17</v>
       </c>
       <c r="D152" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E152" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F152" t="n">
         <v>1.0</v>
       </c>
       <c r="G152" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4157,22 +4157,22 @@
         <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C153" t="s">
         <v>17</v>
       </c>
       <c r="D153" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E153" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F153" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G153" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H153" t="n">
         <v>0.0</v>
@@ -4183,22 +4183,22 @@
         <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C154" t="s">
         <v>17</v>
       </c>
       <c r="D154" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E154" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F154" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G154" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H154" t="n">
         <v>0.0</v>
@@ -4209,7 +4209,7 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C155" t="s">
         <v>17</v>
@@ -4218,7 +4218,7 @@
         <v>38</v>
       </c>
       <c r="E155" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F155" t="n">
         <v>1.0</v>
@@ -4235,7 +4235,7 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C156" t="s">
         <v>17</v>
@@ -4244,13 +4244,13 @@
         <v>38</v>
       </c>
       <c r="E156" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F156" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G156" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H156" t="n">
         <v>0.0</v>
@@ -4267,16 +4267,16 @@
         <v>17</v>
       </c>
       <c r="D157" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E157" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F157" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G157" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="H157" t="n">
         <v>0.0</v>
@@ -4293,16 +4293,16 @@
         <v>17</v>
       </c>
       <c r="D158" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E158" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F158" t="n">
         <v>1.0</v>
       </c>
       <c r="G158" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="H158" t="n">
         <v>0.0</v>
@@ -4319,16 +4319,16 @@
         <v>17</v>
       </c>
       <c r="D159" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E159" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F159" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G159" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="H159" t="n">
         <v>0.0</v>
@@ -4339,16 +4339,16 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C160" t="s">
         <v>17</v>
       </c>
       <c r="D160" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E160" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F160" t="n">
         <v>1.0</v>
@@ -4365,19 +4365,19 @@
         <v>8</v>
       </c>
       <c r="B161" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C161" t="s">
         <v>17</v>
       </c>
       <c r="D161" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E161" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F161" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G161" t="n">
         <v>1.0</v>
@@ -4391,7 +4391,7 @@
         <v>8</v>
       </c>
       <c r="B162" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C162" t="s">
         <v>17</v>
@@ -4400,13 +4400,13 @@
         <v>39</v>
       </c>
       <c r="E162" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F162" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G162" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H162" t="n">
         <v>0.0</v>
@@ -4417,7 +4417,7 @@
         <v>8</v>
       </c>
       <c r="B163" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C163" t="s">
         <v>17</v>
@@ -4429,10 +4429,10 @@
         <v>41</v>
       </c>
       <c r="F163" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G163" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="H163" t="n">
         <v>0.0</v>
@@ -4443,7 +4443,7 @@
         <v>8</v>
       </c>
       <c r="B164" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C164" t="s">
         <v>17</v>
@@ -4455,10 +4455,10 @@
         <v>42</v>
       </c>
       <c r="F164" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4478,15 +4478,145 @@
         <v>39</v>
       </c>
       <c r="E165" t="s">
+        <v>46</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>8</v>
+      </c>
+      <c r="B166" t="s">
+        <v>10</v>
+      </c>
+      <c r="C166" t="s">
+        <v>17</v>
+      </c>
+      <c r="D166" t="s">
+        <v>39</v>
+      </c>
+      <c r="E166" t="s">
+        <v>45</v>
+      </c>
+      <c r="F166" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G166" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>8</v>
+      </c>
+      <c r="B167" t="s">
+        <v>10</v>
+      </c>
+      <c r="C167" t="s">
+        <v>17</v>
+      </c>
+      <c r="D167" t="s">
+        <v>39</v>
+      </c>
+      <c r="E167" t="s">
+        <v>44</v>
+      </c>
+      <c r="F167" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G167" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>8</v>
+      </c>
+      <c r="B168" t="s">
+        <v>10</v>
+      </c>
+      <c r="C168" t="s">
+        <v>17</v>
+      </c>
+      <c r="D168" t="s">
+        <v>39</v>
+      </c>
+      <c r="E168" t="s">
+        <v>41</v>
+      </c>
+      <c r="F168" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G168" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>8</v>
+      </c>
+      <c r="B169" t="s">
+        <v>10</v>
+      </c>
+      <c r="C169" t="s">
+        <v>17</v>
+      </c>
+      <c r="D169" t="s">
+        <v>39</v>
+      </c>
+      <c r="E169" t="s">
+        <v>42</v>
+      </c>
+      <c r="F169" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>8</v>
+      </c>
+      <c r="B170" t="s">
+        <v>10</v>
+      </c>
+      <c r="C170" t="s">
+        <v>17</v>
+      </c>
+      <c r="D170" t="s">
+        <v>39</v>
+      </c>
+      <c r="E170" t="s">
         <v>43</v>
       </c>
-      <c r="F165" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G165" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H165" t="n">
+      <c r="F170" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H170" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -2170,7 +2170,7 @@
         <v>1.0</v>
       </c>
       <c r="G76" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>
@@ -2222,7 +2222,7 @@
         <v>0.0</v>
       </c>
       <c r="G78" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="H78" t="n">
         <v>1.0</v>
@@ -2248,7 +2248,7 @@
         <v>1.0</v>
       </c>
       <c r="G79" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="H79" t="n">
         <v>0.0</v>
@@ -2274,7 +2274,7 @@
         <v>0.0</v>
       </c>
       <c r="G80" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H80" t="n">
         <v>0.0</v>
@@ -4276,7 +4276,7 @@
         <v>1.0</v>
       </c>
       <c r="G157" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="H157" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3314,7 +3314,7 @@
         <v>1.0</v>
       </c>
       <c r="G120" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H120" t="n">
         <v>0.0</v>
@@ -3366,7 +3366,7 @@
         <v>0.0</v>
       </c>
       <c r="G122" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -2430,7 +2430,7 @@
         <v>0.0</v>
       </c>
       <c r="G86" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H86" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3415,7 +3415,7 @@
         <v>44</v>
       </c>
       <c r="F124" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G124" t="n">
         <v>78.0</v>
@@ -3467,7 +3467,7 @@
         <v>42</v>
       </c>
       <c r="F126" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G126" t="n">
         <v>472.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3470,7 +3470,7 @@
         <v>3.0</v>
       </c>
       <c r="G126" t="n">
-        <v>472.0</v>
+        <v>471.0</v>
       </c>
       <c r="H126" t="n">
         <v>1.0</v>
@@ -3805,7 +3805,7 @@
         <v>40</v>
       </c>
       <c r="F139" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G139" t="n">
         <v>3.0</v>
@@ -4198,7 +4198,7 @@
         <v>0.0</v>
       </c>
       <c r="G154" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H154" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3470,7 +3470,7 @@
         <v>3.0</v>
       </c>
       <c r="G126" t="n">
-        <v>471.0</v>
+        <v>470.0</v>
       </c>
       <c r="H126" t="n">
         <v>1.0</v>
@@ -4198,7 +4198,7 @@
         <v>0.0</v>
       </c>
       <c r="G154" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H154" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -2040,7 +2040,7 @@
         <v>0.0</v>
       </c>
       <c r="G71" t="n">
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
       <c r="H71" t="n">
         <v>0.0</v>
@@ -3470,7 +3470,7 @@
         <v>3.0</v>
       </c>
       <c r="G126" t="n">
-        <v>470.0</v>
+        <v>471.0</v>
       </c>
       <c r="H126" t="n">
         <v>1.0</v>
@@ -3574,7 +3574,7 @@
         <v>2.0</v>
       </c>
       <c r="G130" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="H130" t="n">
         <v>0.0</v>
@@ -4039,10 +4039,10 @@
         <v>40</v>
       </c>
       <c r="F148" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G148" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4062,7 +4062,7 @@
         <v>37</v>
       </c>
       <c r="E149" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F149" t="n">
         <v>0.0</v>
@@ -4510,7 +4510,7 @@
         <v>2.0</v>
       </c>
       <c r="G166" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H166" t="n">
         <v>0.0</v>
@@ -4559,10 +4559,10 @@
         <v>41</v>
       </c>
       <c r="F168" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G168" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="H168" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -2040,7 +2040,7 @@
         <v>0.0</v>
       </c>
       <c r="G71" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="H71" t="n">
         <v>0.0</v>
@@ -3701,10 +3701,10 @@
         <v>40</v>
       </c>
       <c r="F135" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G135" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1234,7 +1234,7 @@
         <v>0.0</v>
       </c>
       <c r="G40" t="n">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="H40" t="n">
         <v>0.0</v>
@@ -3704,7 +3704,7 @@
         <v>3.0</v>
       </c>
       <c r="G135" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3756,7 +3756,7 @@
         <v>0.0</v>
       </c>
       <c r="G137" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -4403,10 +4403,10 @@
         <v>46</v>
       </c>
       <c r="F162" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G162" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G162" t="n">
-        <v>3.0</v>
       </c>
       <c r="H162" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="47">
   <si>
     <t>Area</t>
   </si>
@@ -1494,7 +1494,7 @@
         <v>0.0</v>
       </c>
       <c r="G50" t="n">
-        <v>114.0</v>
+        <v>113.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -2716,7 +2716,7 @@
         <v>3.0</v>
       </c>
       <c r="G97" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -2735,8 +2735,8 @@
       <c r="D98" t="s">
         <v>31</v>
       </c>
-      <c r="E98" t="s">
-        <v>44</v>
+      <c r="E98" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F98" t="n">
         <v>0.0</v>
@@ -2762,13 +2762,13 @@
         <v>31</v>
       </c>
       <c r="E99" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F99" t="n">
         <v>0.0</v>
       </c>
       <c r="G99" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H99" t="n">
         <v>0.0</v>
@@ -2779,7 +2779,7 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C100" t="s">
         <v>16</v>
@@ -2788,13 +2788,13 @@
         <v>31</v>
       </c>
       <c r="E100" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F100" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G100" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2814,10 +2814,10 @@
         <v>31</v>
       </c>
       <c r="E101" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G101" t="n">
         <v>1.0</v>
@@ -2831,7 +2831,7 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C102" t="s">
         <v>16</v>
@@ -2840,13 +2840,13 @@
         <v>31</v>
       </c>
       <c r="E102" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F102" t="n">
         <v>0.0</v>
       </c>
       <c r="G102" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2866,13 +2866,13 @@
         <v>31</v>
       </c>
       <c r="E103" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F103" t="n">
         <v>0.0</v>
       </c>
       <c r="G103" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="H103" t="n">
         <v>0.0</v>
@@ -2892,13 +2892,13 @@
         <v>31</v>
       </c>
       <c r="E104" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F104" t="n">
         <v>0.0</v>
       </c>
       <c r="G104" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="H104" t="n">
         <v>0.0</v>
@@ -2909,25 +2909,25 @@
         <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C105" t="s">
         <v>16</v>
       </c>
       <c r="D105" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E105" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F105" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G105" t="n">
         <v>4.0</v>
       </c>
       <c r="H105" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="106">
@@ -2944,16 +2944,16 @@
         <v>32</v>
       </c>
       <c r="E106" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F106" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G106" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="107">
@@ -2970,13 +2970,13 @@
         <v>32</v>
       </c>
       <c r="E107" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F107" t="n">
         <v>0.0</v>
       </c>
       <c r="G107" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H107" t="n">
         <v>0.0</v>
@@ -2987,7 +2987,7 @@
         <v>8</v>
       </c>
       <c r="B108" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C108" t="s">
         <v>16</v>
@@ -2996,13 +2996,13 @@
         <v>32</v>
       </c>
       <c r="E108" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F108" t="n">
         <v>0.0</v>
       </c>
       <c r="G108" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H108" t="n">
         <v>0.0</v>
@@ -3013,7 +3013,7 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C109" t="s">
         <v>16</v>
@@ -3022,7 +3022,7 @@
         <v>32</v>
       </c>
       <c r="E109" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F109" t="n">
         <v>0.0</v>
@@ -3048,7 +3048,7 @@
         <v>32</v>
       </c>
       <c r="E110" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F110" t="n">
         <v>0.0</v>
@@ -3057,7 +3057,7 @@
         <v>1.0</v>
       </c>
       <c r="H110" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="111">
@@ -3065,7 +3065,7 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C111" t="s">
         <v>16</v>
@@ -3073,17 +3073,17 @@
       <c r="D111" t="s">
         <v>32</v>
       </c>
-      <c r="E111" t="e">
-        <v>#N/A</v>
+      <c r="E111" t="s">
+        <v>40</v>
       </c>
       <c r="F111" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H111" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="112">
@@ -3099,14 +3099,14 @@
       <c r="D112" t="s">
         <v>32</v>
       </c>
-      <c r="E112" t="s">
-        <v>44</v>
+      <c r="E112" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F112" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G112" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3126,13 +3126,13 @@
         <v>32</v>
       </c>
       <c r="E113" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F113" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="G113" t="n">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="H113" t="n">
         <v>0.0</v>
@@ -3152,13 +3152,13 @@
         <v>32</v>
       </c>
       <c r="E114" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F114" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G114" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3169,22 +3169,22 @@
         <v>8</v>
       </c>
       <c r="B115" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C115" t="s">
         <v>16</v>
       </c>
       <c r="D115" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E115" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F115" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G115" t="n">
-        <v>7.0</v>
+        <v>18.0</v>
       </c>
       <c r="H115" t="n">
         <v>0.0</v>
@@ -3204,13 +3204,13 @@
         <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F116" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G116" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="H116" t="n">
         <v>0.0</v>
@@ -3230,13 +3230,13 @@
         <v>33</v>
       </c>
       <c r="E117" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F117" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G117" t="n">
-        <v>33.0</v>
+        <v>1.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3256,13 +3256,13 @@
         <v>33</v>
       </c>
       <c r="E118" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F118" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0</v>
+        <v>33.0</v>
       </c>
       <c r="H118" t="n">
         <v>0.0</v>
@@ -3273,7 +3273,7 @@
         <v>8</v>
       </c>
       <c r="B119" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C119" t="s">
         <v>16</v>
@@ -3282,10 +3282,10 @@
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F119" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G119" t="n">
         <v>0.0</v>
@@ -3308,13 +3308,13 @@
         <v>33</v>
       </c>
       <c r="E120" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F120" t="n">
         <v>1.0</v>
       </c>
       <c r="G120" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H120" t="n">
         <v>0.0</v>
@@ -3334,13 +3334,13 @@
         <v>33</v>
       </c>
       <c r="E121" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G121" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H121" t="n">
         <v>0.0</v>
@@ -3360,13 +3360,13 @@
         <v>33</v>
       </c>
       <c r="E122" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F122" t="n">
         <v>0.0</v>
       </c>
       <c r="G122" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3377,7 +3377,7 @@
         <v>8</v>
       </c>
       <c r="B123" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C123" t="s">
         <v>16</v>
@@ -3385,17 +3385,17 @@
       <c r="D123" t="s">
         <v>33</v>
       </c>
-      <c r="E123" t="e">
-        <v>#N/A</v>
+      <c r="E123" t="s">
+        <v>42</v>
       </c>
       <c r="F123" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H123" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="124">
@@ -3411,17 +3411,17 @@
       <c r="D124" t="s">
         <v>33</v>
       </c>
-      <c r="E124" t="s">
-        <v>44</v>
+      <c r="E124" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F124" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G124" t="n">
-        <v>78.0</v>
+        <v>0.0</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="125">
@@ -3438,13 +3438,13 @@
         <v>33</v>
       </c>
       <c r="E125" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F125" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="G125" t="n">
-        <v>25.0</v>
+        <v>78.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3464,16 +3464,16 @@
         <v>33</v>
       </c>
       <c r="E126" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F126" t="n">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
       <c r="G126" t="n">
-        <v>471.0</v>
+        <v>25.0</v>
       </c>
       <c r="H126" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="127">
@@ -3490,16 +3490,16 @@
         <v>33</v>
       </c>
       <c r="E127" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F127" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0</v>
+        <v>471.0</v>
       </c>
       <c r="H127" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="128">
@@ -3513,16 +3513,16 @@
         <v>16</v>
       </c>
       <c r="D128" t="s">
-        <v>34</v>
-      </c>
-      <c r="E128" t="e">
-        <v>#N/A</v>
+        <v>33</v>
+      </c>
+      <c r="E128" t="s">
+        <v>43</v>
       </c>
       <c r="F128" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G128" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H128" t="n">
         <v>0.0</v>
@@ -3541,14 +3541,14 @@
       <c r="D129" t="s">
         <v>34</v>
       </c>
-      <c r="E129" t="s">
-        <v>44</v>
+      <c r="E129" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F129" t="n">
         <v>1.0</v>
       </c>
       <c r="G129" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -3568,13 +3568,13 @@
         <v>34</v>
       </c>
       <c r="E130" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F130" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G130" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="H130" t="n">
         <v>0.0</v>
@@ -3594,13 +3594,13 @@
         <v>34</v>
       </c>
       <c r="E131" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F131" t="n">
         <v>2.0</v>
       </c>
       <c r="G131" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
       <c r="H131" t="n">
         <v>0.0</v>
@@ -3617,16 +3617,16 @@
         <v>16</v>
       </c>
       <c r="D132" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E132" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F132" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G132" t="n">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -3646,16 +3646,16 @@
         <v>35</v>
       </c>
       <c r="E133" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F133" t="n">
         <v>0.0</v>
       </c>
       <c r="G133" t="n">
-        <v>16.0</v>
+        <v>7.0</v>
       </c>
       <c r="H133" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="134">
@@ -3672,16 +3672,16 @@
         <v>35</v>
       </c>
       <c r="E134" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F134" t="n">
         <v>0.0</v>
       </c>
       <c r="G134" t="n">
-        <v>10.0</v>
+        <v>16.0</v>
       </c>
       <c r="H134" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="135">
@@ -3689,22 +3689,22 @@
         <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C135" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D135" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E135" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F135" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G135" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3724,13 +3724,13 @@
         <v>36</v>
       </c>
       <c r="E136" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F136" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="H136" t="n">
         <v>0.0</v>
@@ -3750,13 +3750,13 @@
         <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G137" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3776,13 +3776,13 @@
         <v>36</v>
       </c>
       <c r="E138" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F138" t="n">
         <v>0.0</v>
       </c>
       <c r="G138" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3793,7 +3793,7 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C139" t="s">
         <v>17</v>
@@ -3802,13 +3802,13 @@
         <v>36</v>
       </c>
       <c r="E139" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F139" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G139" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3828,13 +3828,13 @@
         <v>36</v>
       </c>
       <c r="E140" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F140" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H140" t="n">
         <v>0.0</v>
@@ -3854,13 +3854,13 @@
         <v>36</v>
       </c>
       <c r="E141" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F141" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G141" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H141" t="n">
         <v>0.0</v>
@@ -3880,13 +3880,13 @@
         <v>36</v>
       </c>
       <c r="E142" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F142" t="n">
         <v>0.0</v>
       </c>
       <c r="G142" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3906,13 +3906,13 @@
         <v>36</v>
       </c>
       <c r="E143" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F143" t="n">
         <v>0.0</v>
       </c>
       <c r="G143" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H143" t="n">
         <v>0.0</v>
@@ -3923,7 +3923,7 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C144" t="s">
         <v>17</v>
@@ -3932,13 +3932,13 @@
         <v>36</v>
       </c>
       <c r="E144" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F144" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3949,7 +3949,7 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
@@ -3958,13 +3958,13 @@
         <v>36</v>
       </c>
       <c r="E145" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F145" t="n">
         <v>1.0</v>
       </c>
       <c r="G145" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H145" t="n">
         <v>0.0</v>
@@ -3983,14 +3983,14 @@
       <c r="D146" t="s">
         <v>36</v>
       </c>
-      <c r="E146" t="e">
-        <v>#N/A</v>
+      <c r="E146" t="s">
+        <v>40</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G146" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4001,22 +4001,22 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>37</v>
-      </c>
-      <c r="E147" t="s">
-        <v>44</v>
+        <v>36</v>
+      </c>
+      <c r="E147" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F147" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G147" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4036,13 +4036,13 @@
         <v>37</v>
       </c>
       <c r="E148" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F148" t="n">
         <v>1.0</v>
       </c>
       <c r="G148" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4062,13 +4062,13 @@
         <v>37</v>
       </c>
       <c r="E149" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F149" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G149" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4088,13 +4088,13 @@
         <v>37</v>
       </c>
       <c r="E150" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F150" t="n">
         <v>0.0</v>
       </c>
       <c r="G150" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>
@@ -4105,7 +4105,7 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
@@ -4114,13 +4114,13 @@
         <v>37</v>
       </c>
       <c r="E151" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F151" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G151" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4140,13 +4140,13 @@
         <v>37</v>
       </c>
       <c r="E152" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F152" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G152" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4166,13 +4166,13 @@
         <v>37</v>
       </c>
       <c r="E153" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F153" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G153" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H153" t="n">
         <v>0.0</v>
@@ -4192,7 +4192,7 @@
         <v>37</v>
       </c>
       <c r="E154" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F154" t="n">
         <v>0.0</v>
@@ -4209,22 +4209,22 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C155" t="s">
         <v>17</v>
       </c>
       <c r="D155" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E155" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F155" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H155" t="n">
         <v>0.0</v>
@@ -4244,10 +4244,10 @@
         <v>38</v>
       </c>
       <c r="E156" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F156" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G156" t="n">
         <v>0.0</v>
@@ -4270,13 +4270,13 @@
         <v>38</v>
       </c>
       <c r="E157" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F157" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G157" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H157" t="n">
         <v>0.0</v>
@@ -4296,13 +4296,13 @@
         <v>38</v>
       </c>
       <c r="E158" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F158" t="n">
         <v>1.0</v>
       </c>
       <c r="G158" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="H158" t="n">
         <v>0.0</v>
@@ -4322,13 +4322,13 @@
         <v>38</v>
       </c>
       <c r="E159" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F159" t="n">
         <v>1.0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H159" t="n">
         <v>0.0</v>
@@ -4339,7 +4339,7 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C160" t="s">
         <v>17</v>
@@ -4348,7 +4348,7 @@
         <v>38</v>
       </c>
       <c r="E160" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F160" t="n">
         <v>1.0</v>
@@ -4374,13 +4374,13 @@
         <v>38</v>
       </c>
       <c r="E161" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F161" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G161" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H161" t="n">
         <v>0.0</v>
@@ -4391,22 +4391,22 @@
         <v>8</v>
       </c>
       <c r="B162" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C162" t="s">
         <v>17</v>
       </c>
       <c r="D162" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E162" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F162" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G162" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H162" t="n">
         <v>0.0</v>
@@ -4426,13 +4426,13 @@
         <v>39</v>
       </c>
       <c r="E163" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F163" t="n">
         <v>1.0</v>
       </c>
       <c r="G163" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="H163" t="n">
         <v>0.0</v>
@@ -4452,13 +4452,13 @@
         <v>39</v>
       </c>
       <c r="E164" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F164" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G164" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4469,7 +4469,7 @@
         <v>8</v>
       </c>
       <c r="B165" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C165" t="s">
         <v>17</v>
@@ -4478,13 +4478,13 @@
         <v>39</v>
       </c>
       <c r="E165" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F165" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H165" t="n">
         <v>0.0</v>
@@ -4504,10 +4504,10 @@
         <v>39</v>
       </c>
       <c r="E166" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F166" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G166" t="n">
         <v>0.0</v>
@@ -4530,13 +4530,13 @@
         <v>39</v>
       </c>
       <c r="E167" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F167" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G167" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H167" t="n">
         <v>0.0</v>
@@ -4556,13 +4556,13 @@
         <v>39</v>
       </c>
       <c r="E168" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F168" t="n">
         <v>1.0</v>
       </c>
       <c r="G168" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H168" t="n">
         <v>0.0</v>
@@ -4582,13 +4582,13 @@
         <v>39</v>
       </c>
       <c r="E169" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F169" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G169" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H169" t="n">
         <v>0.0</v>
@@ -4608,15 +4608,41 @@
         <v>39</v>
       </c>
       <c r="E170" t="s">
+        <v>42</v>
+      </c>
+      <c r="F170" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>8</v>
+      </c>
+      <c r="B171" t="s">
+        <v>10</v>
+      </c>
+      <c r="C171" t="s">
+        <v>17</v>
+      </c>
+      <c r="D171" t="s">
+        <v>39</v>
+      </c>
+      <c r="E171" t="s">
         <v>43</v>
       </c>
-      <c r="F170" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G170" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H170" t="n">
+      <c r="F171" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H171" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3496,7 +3496,7 @@
         <v>3.0</v>
       </c>
       <c r="G127" t="n">
-        <v>471.0</v>
+        <v>470.0</v>
       </c>
       <c r="H127" t="n">
         <v>1.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -454,7 +454,7 @@
         <v>1.0</v>
       </c>
       <c r="G10" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="H10" t="n">
         <v>0.0</v>
@@ -818,7 +818,7 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H24" t="n">
         <v>0.0</v>
@@ -974,7 +974,7 @@
         <v>0.0</v>
       </c>
       <c r="G30" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="H30" t="n">
         <v>0.0</v>
@@ -1494,7 +1494,7 @@
         <v>0.0</v>
       </c>
       <c r="G50" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -1962,7 +1962,7 @@
         <v>0.0</v>
       </c>
       <c r="G68" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="H68" t="n">
         <v>11.0</v>
@@ -2014,10 +2014,10 @@
         <v>0.0</v>
       </c>
       <c r="G70" t="n">
-        <v>168.0</v>
+        <v>172.0</v>
       </c>
       <c r="H70" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="71">
@@ -2040,7 +2040,7 @@
         <v>0.0</v>
       </c>
       <c r="G71" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="H71" t="n">
         <v>0.0</v>
@@ -2196,7 +2196,7 @@
         <v>1.0</v>
       </c>
       <c r="G77" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="H77" t="n">
         <v>0.0</v>
@@ -3262,7 +3262,7 @@
         <v>3.0</v>
       </c>
       <c r="G118" t="n">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
       <c r="H118" t="n">
         <v>0.0</v>
@@ -3444,7 +3444,7 @@
         <v>10.0</v>
       </c>
       <c r="G125" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3496,7 +3496,7 @@
         <v>3.0</v>
       </c>
       <c r="G127" t="n">
-        <v>470.0</v>
+        <v>483.0</v>
       </c>
       <c r="H127" t="n">
         <v>1.0</v>
@@ -3626,7 +3626,7 @@
         <v>2.0</v>
       </c>
       <c r="G132" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -4458,7 +4458,7 @@
         <v>1.0</v>
       </c>
       <c r="G164" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4588,7 +4588,7 @@
         <v>1.0</v>
       </c>
       <c r="G169" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H169" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="47">
   <si>
     <t>Area</t>
   </si>
@@ -1442,7 +1442,7 @@
         <v>1.0</v>
       </c>
       <c r="G48" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1494,7 +1494,7 @@
         <v>0.0</v>
       </c>
       <c r="G50" t="n">
-        <v>114.0</v>
+        <v>113.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -1965,7 +1965,7 @@
         <v>37.0</v>
       </c>
       <c r="H68" t="n">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="69">
@@ -2092,7 +2092,7 @@
         <v>0.0</v>
       </c>
       <c r="G73" t="n">
-        <v>68.0</v>
+        <v>66.0</v>
       </c>
       <c r="H73" t="n">
         <v>0.0</v>
@@ -3184,7 +3184,7 @@
         <v>2.0</v>
       </c>
       <c r="G115" t="n">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="H115" t="n">
         <v>0.0</v>
@@ -3444,7 +3444,7 @@
         <v>10.0</v>
       </c>
       <c r="G125" t="n">
-        <v>79.0</v>
+        <v>78.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3496,7 +3496,7 @@
         <v>3.0</v>
       </c>
       <c r="G127" t="n">
-        <v>483.0</v>
+        <v>478.0</v>
       </c>
       <c r="H127" t="n">
         <v>1.0</v>
@@ -3782,7 +3782,7 @@
         <v>0.0</v>
       </c>
       <c r="G138" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3983,14 +3983,14 @@
       <c r="D146" t="s">
         <v>36</v>
       </c>
-      <c r="E146" t="s">
-        <v>40</v>
+      <c r="E146" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F146" t="n">
         <v>1.0</v>
       </c>
       <c r="G146" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4009,14 +4009,14 @@
       <c r="D147" t="s">
         <v>36</v>
       </c>
-      <c r="E147" t="e">
-        <v>#N/A</v>
+      <c r="E147" t="s">
+        <v>40</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G147" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4458,7 +4458,7 @@
         <v>1.0</v>
       </c>
       <c r="G164" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4478,13 +4478,13 @@
         <v>39</v>
       </c>
       <c r="E165" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F165" t="n">
         <v>0.0</v>
       </c>
       <c r="G165" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="H165" t="n">
         <v>0.0</v>
@@ -4495,7 +4495,7 @@
         <v>8</v>
       </c>
       <c r="B166" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C166" t="s">
         <v>17</v>
@@ -4504,13 +4504,13 @@
         <v>39</v>
       </c>
       <c r="E166" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F166" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G166" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H166" t="n">
         <v>0.0</v>
@@ -4530,10 +4530,10 @@
         <v>39</v>
       </c>
       <c r="E167" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F167" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G167" t="n">
         <v>0.0</v>
@@ -4556,13 +4556,13 @@
         <v>39</v>
       </c>
       <c r="E168" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F168" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G168" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H168" t="n">
         <v>0.0</v>
@@ -4582,13 +4582,13 @@
         <v>39</v>
       </c>
       <c r="E169" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F169" t="n">
         <v>1.0</v>
       </c>
       <c r="G169" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H169" t="n">
         <v>0.0</v>
@@ -4608,13 +4608,13 @@
         <v>39</v>
       </c>
       <c r="E170" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F170" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H170" t="n">
         <v>0.0</v>
@@ -4634,15 +4634,41 @@
         <v>39</v>
       </c>
       <c r="E171" t="s">
+        <v>42</v>
+      </c>
+      <c r="F171" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>8</v>
+      </c>
+      <c r="B172" t="s">
+        <v>10</v>
+      </c>
+      <c r="C172" t="s">
+        <v>17</v>
+      </c>
+      <c r="D172" t="s">
+        <v>39</v>
+      </c>
+      <c r="E172" t="s">
         <v>43</v>
       </c>
-      <c r="F171" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G171" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H171" t="n">
+      <c r="F172" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H172" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -2040,7 +2040,7 @@
         <v>0.0</v>
       </c>
       <c r="G71" t="n">
-        <v>34.0</v>
+        <v>33.0</v>
       </c>
       <c r="H71" t="n">
         <v>0.0</v>
@@ -3496,7 +3496,7 @@
         <v>3.0</v>
       </c>
       <c r="G127" t="n">
-        <v>478.0</v>
+        <v>476.0</v>
       </c>
       <c r="H127" t="n">
         <v>1.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3987,7 +3987,7 @@
         <v>#N/A</v>
       </c>
       <c r="F146" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G146" t="n">
         <v>0.0</v>
@@ -4013,7 +4013,7 @@
         <v>40</v>
       </c>
       <c r="F147" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G147" t="n">
         <v>5.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -396,13 +396,13 @@
         <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G8" t="n">
-        <v>16.0</v>
+        <v>9.0</v>
       </c>
       <c r="H8" t="n">
         <v>0.0</v>
@@ -422,13 +422,13 @@
         <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G9" t="n">
-        <v>9.0</v>
+        <v>30.0</v>
       </c>
       <c r="H9" t="n">
         <v>0.0</v>
@@ -448,13 +448,13 @@
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
       </c>
       <c r="G10" t="n">
-        <v>30.0</v>
+        <v>0.0</v>
       </c>
       <c r="H10" t="n">
         <v>0.0</v>
@@ -474,13 +474,13 @@
         <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="H11" t="n">
         <v>0.0</v>
@@ -2040,7 +2040,7 @@
         <v>0.0</v>
       </c>
       <c r="G71" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="H71" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1384,10 +1384,10 @@
         <v>22</v>
       </c>
       <c r="E46" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F46" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G46" t="n">
         <v>1.0</v>
@@ -1410,7 +1410,7 @@
         <v>22</v>
       </c>
       <c r="E47" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F47" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1280,13 +1280,13 @@
         <v>22</v>
       </c>
       <c r="E42" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F42" t="n">
         <v>1.0</v>
       </c>
       <c r="G42" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
       <c r="H42" t="n">
         <v>0.0</v>
@@ -1306,13 +1306,13 @@
         <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F43" t="n">
         <v>1.0</v>
       </c>
       <c r="G43" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="H43" t="n">
         <v>0.0</v>
@@ -1332,13 +1332,13 @@
         <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F44" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H44" t="n">
         <v>0.0</v>
@@ -4458,7 +4458,7 @@
         <v>1.0</v>
       </c>
       <c r="G164" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4484,7 +4484,7 @@
         <v>0.0</v>
       </c>
       <c r="G165" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H165" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3470,7 +3470,7 @@
         <v>12.0</v>
       </c>
       <c r="G126" t="n">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -4016,7 +4016,7 @@
         <v>0.0</v>
       </c>
       <c r="G147" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="47">
   <si>
     <t>Area</t>
   </si>
@@ -1306,13 +1306,13 @@
         <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F43" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H43" t="n">
         <v>0.0</v>
@@ -1323,7 +1323,7 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C44" t="s">
         <v>13</v>
@@ -1332,13 +1332,13 @@
         <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G44" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="H44" t="n">
         <v>0.0</v>
@@ -1358,13 +1358,13 @@
         <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F45" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G45" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H45" t="n">
         <v>0.0</v>
@@ -1384,7 +1384,7 @@
         <v>22</v>
       </c>
       <c r="E46" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F46" t="n">
         <v>0.0</v>
@@ -1401,7 +1401,7 @@
         <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C47" t="s">
         <v>13</v>
@@ -1410,13 +1410,13 @@
         <v>22</v>
       </c>
       <c r="E47" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G47" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1436,13 +1436,13 @@
         <v>22</v>
       </c>
       <c r="E48" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F48" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G48" t="n">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1462,13 +1462,13 @@
         <v>22</v>
       </c>
       <c r="E49" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F49" t="n">
         <v>0.0</v>
       </c>
       <c r="G49" t="n">
-        <v>16.0</v>
+        <v>113.0</v>
       </c>
       <c r="H49" t="n">
         <v>0.0</v>
@@ -1479,22 +1479,22 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E50" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G50" t="n">
-        <v>113.0</v>
+        <v>2.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -1514,13 +1514,13 @@
         <v>23</v>
       </c>
       <c r="E51" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F51" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G51" t="n">
-        <v>2.0</v>
+        <v>22.0</v>
       </c>
       <c r="H51" t="n">
         <v>0.0</v>
@@ -1540,13 +1540,13 @@
         <v>23</v>
       </c>
       <c r="E52" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F52" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G52" t="n">
-        <v>22.0</v>
+        <v>0.0</v>
       </c>
       <c r="H52" t="n">
         <v>0.0</v>
@@ -1566,13 +1566,13 @@
         <v>23</v>
       </c>
       <c r="E53" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F53" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H53" t="n">
         <v>0.0</v>
@@ -1589,16 +1589,16 @@
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G54" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H54" t="n">
         <v>0.0</v>
@@ -1618,13 +1618,13 @@
         <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F55" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H55" t="n">
         <v>0.0</v>
@@ -1644,13 +1644,13 @@
         <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F56" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G56" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H56" t="n">
         <v>0.0</v>
@@ -1670,10 +1670,10 @@
         <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F57" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1696,13 +1696,13 @@
         <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F58" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H58" t="n">
         <v>0.0</v>
@@ -1713,16 +1713,16 @@
         <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C59" t="s">
         <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E59" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F59" t="n">
         <v>0.0</v>
@@ -1748,13 +1748,13 @@
         <v>25</v>
       </c>
       <c r="E60" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F60" t="n">
         <v>0.0</v>
       </c>
       <c r="G60" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H60" t="n">
         <v>0.0</v>
@@ -1765,7 +1765,7 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="E61" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G61" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H61" t="n">
         <v>0.0</v>
@@ -1800,13 +1800,13 @@
         <v>25</v>
       </c>
       <c r="E62" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F62" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H62" t="n">
         <v>0.0</v>
@@ -1826,13 +1826,13 @@
         <v>25</v>
       </c>
       <c r="E63" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F63" t="n">
         <v>0.0</v>
       </c>
       <c r="G63" t="n">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
       <c r="H63" t="n">
         <v>0.0</v>
@@ -1843,7 +1843,7 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
@@ -1852,13 +1852,13 @@
         <v>25</v>
       </c>
       <c r="E64" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G64" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="H64" t="n">
         <v>0.0</v>
@@ -1878,13 +1878,13 @@
         <v>25</v>
       </c>
       <c r="E65" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F65" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H65" t="n">
         <v>0.0</v>
@@ -1904,13 +1904,13 @@
         <v>25</v>
       </c>
       <c r="E66" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F66" t="n">
         <v>0.0</v>
       </c>
       <c r="G66" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="H66" t="n">
         <v>0.0</v>
@@ -1924,22 +1924,22 @@
         <v>11</v>
       </c>
       <c r="C67" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E67" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F67" t="n">
         <v>0.0</v>
       </c>
       <c r="G67" t="n">
-        <v>8.0</v>
+        <v>37.0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="68">
@@ -1956,16 +1956,16 @@
         <v>26</v>
       </c>
       <c r="E68" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F68" t="n">
         <v>0.0</v>
       </c>
       <c r="G68" t="n">
-        <v>37.0</v>
+        <v>16.0</v>
       </c>
       <c r="H68" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="69">
@@ -1982,16 +1982,16 @@
         <v>26</v>
       </c>
       <c r="E69" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F69" t="n">
         <v>0.0</v>
       </c>
       <c r="G69" t="n">
-        <v>16.0</v>
+        <v>172.0</v>
       </c>
       <c r="H69" t="n">
-        <v>3.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="70">
@@ -2005,19 +2005,19 @@
         <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E70" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F70" t="n">
         <v>0.0</v>
       </c>
       <c r="G70" t="n">
-        <v>172.0</v>
+        <v>34.0</v>
       </c>
       <c r="H70" t="n">
-        <v>34.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="71">
@@ -2034,13 +2034,13 @@
         <v>27</v>
       </c>
       <c r="E71" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F71" t="n">
         <v>0.0</v>
       </c>
       <c r="G71" t="n">
-        <v>34.0</v>
+        <v>3.0</v>
       </c>
       <c r="H71" t="n">
         <v>0.0</v>
@@ -2060,13 +2060,13 @@
         <v>27</v>
       </c>
       <c r="E72" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F72" t="n">
         <v>0.0</v>
       </c>
       <c r="G72" t="n">
-        <v>3.0</v>
+        <v>66.0</v>
       </c>
       <c r="H72" t="n">
         <v>0.0</v>
@@ -2083,16 +2083,16 @@
         <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>27</v>
-      </c>
-      <c r="E73" t="s">
-        <v>42</v>
+        <v>28</v>
+      </c>
+      <c r="E73" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G73" t="n">
-        <v>66.0</v>
+        <v>0.0</v>
       </c>
       <c r="H73" t="n">
         <v>0.0</v>
@@ -2111,14 +2111,14 @@
       <c r="D74" t="s">
         <v>28</v>
       </c>
-      <c r="E74" t="e">
-        <v>#N/A</v>
+      <c r="E74" t="s">
+        <v>44</v>
       </c>
       <c r="F74" t="n">
         <v>1.0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2138,13 +2138,13 @@
         <v>28</v>
       </c>
       <c r="E75" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F75" t="n">
         <v>1.0</v>
       </c>
       <c r="G75" t="n">
-        <v>18.0</v>
+        <v>11.0</v>
       </c>
       <c r="H75" t="n">
         <v>0.0</v>
@@ -2164,13 +2164,13 @@
         <v>28</v>
       </c>
       <c r="E76" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F76" t="n">
         <v>1.0</v>
       </c>
       <c r="G76" t="n">
-        <v>11.0</v>
+        <v>18.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>
@@ -2190,16 +2190,16 @@
         <v>28</v>
       </c>
       <c r="E77" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F77" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G77" t="n">
-        <v>18.0</v>
+        <v>7.0</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="78">
@@ -2207,25 +2207,25 @@
         <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C78" t="s">
         <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G78" t="n">
         <v>7.0</v>
       </c>
       <c r="H78" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="79">
@@ -2241,14 +2241,14 @@
       <c r="D79" t="s">
         <v>29</v>
       </c>
-      <c r="E79" t="s">
-        <v>40</v>
+      <c r="E79" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F79" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G79" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="H79" t="n">
         <v>0.0</v>
@@ -2267,8 +2267,8 @@
       <c r="D80" t="s">
         <v>29</v>
       </c>
-      <c r="E80" t="e">
-        <v>#N/A</v>
+      <c r="E80" t="s">
+        <v>44</v>
       </c>
       <c r="F80" t="n">
         <v>0.0</v>
@@ -2294,13 +2294,13 @@
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F81" t="n">
         <v>0.0</v>
       </c>
       <c r="G81" t="n">
-        <v>2.0</v>
+        <v>18.0</v>
       </c>
       <c r="H81" t="n">
         <v>0.0</v>
@@ -2311,7 +2311,7 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C82" t="s">
         <v>15</v>
@@ -2320,13 +2320,13 @@
         <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G82" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2346,13 +2346,13 @@
         <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F83" t="n">
         <v>1.0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H83" t="n">
         <v>0.0</v>
@@ -2372,13 +2372,13 @@
         <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F84" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G84" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="H84" t="n">
         <v>0.0</v>
@@ -2398,13 +2398,13 @@
         <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F85" t="n">
         <v>0.0</v>
       </c>
       <c r="G85" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="H85" t="n">
         <v>0.0</v>
@@ -2415,7 +2415,7 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C86" t="s">
         <v>15</v>
@@ -2424,13 +2424,13 @@
         <v>29</v>
       </c>
       <c r="E86" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G86" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="H86" t="n">
         <v>0.0</v>
@@ -2450,10 +2450,10 @@
         <v>29</v>
       </c>
       <c r="E87" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F87" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G87" t="n">
         <v>8.0</v>
@@ -2476,13 +2476,13 @@
         <v>29</v>
       </c>
       <c r="E88" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F88" t="n">
         <v>0.0</v>
       </c>
       <c r="G88" t="n">
-        <v>8.0</v>
+        <v>14.0</v>
       </c>
       <c r="H88" t="n">
         <v>0.0</v>
@@ -2499,16 +2499,16 @@
         <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E89" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G89" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="H89" t="n">
         <v>0.0</v>
@@ -2528,16 +2528,16 @@
         <v>30</v>
       </c>
       <c r="E90" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F90" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="91">
@@ -2554,16 +2554,16 @@
         <v>30</v>
       </c>
       <c r="E91" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F91" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G91" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="H91" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="92">
@@ -2580,16 +2580,16 @@
         <v>30</v>
       </c>
       <c r="E92" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F92" t="n">
         <v>0.0</v>
       </c>
       <c r="G92" t="n">
-        <v>5.0</v>
+        <v>36.0</v>
       </c>
       <c r="H92" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="93">
@@ -2606,16 +2606,16 @@
         <v>30</v>
       </c>
       <c r="E93" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F93" t="n">
         <v>0.0</v>
       </c>
       <c r="G93" t="n">
-        <v>36.0</v>
+        <v>14.0</v>
       </c>
       <c r="H93" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="94">
@@ -2623,13 +2623,13 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C94" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D94" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E94" t="s">
         <v>40</v>
@@ -2638,10 +2638,10 @@
         <v>0.0</v>
       </c>
       <c r="G94" t="n">
-        <v>14.0</v>
+        <v>10.0</v>
       </c>
       <c r="H94" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="95">
@@ -2658,13 +2658,13 @@
         <v>31</v>
       </c>
       <c r="E95" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F95" t="n">
         <v>0.0</v>
       </c>
       <c r="G95" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="H95" t="n">
         <v>0.0</v>
@@ -2675,7 +2675,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C96" t="s">
         <v>16</v>
@@ -2684,13 +2684,13 @@
         <v>31</v>
       </c>
       <c r="E96" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G96" t="n">
-        <v>2.0</v>
+        <v>16.0</v>
       </c>
       <c r="H96" t="n">
         <v>0.0</v>
@@ -2709,14 +2709,14 @@
       <c r="D97" t="s">
         <v>31</v>
       </c>
-      <c r="E97" t="s">
-        <v>40</v>
+      <c r="E97" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F97" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G97" t="n">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -2735,8 +2735,8 @@
       <c r="D98" t="s">
         <v>31</v>
       </c>
-      <c r="E98" t="e">
-        <v>#N/A</v>
+      <c r="E98" t="s">
+        <v>44</v>
       </c>
       <c r="F98" t="n">
         <v>0.0</v>
@@ -2762,13 +2762,13 @@
         <v>31</v>
       </c>
       <c r="E99" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F99" t="n">
         <v>0.0</v>
       </c>
       <c r="G99" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H99" t="n">
         <v>0.0</v>
@@ -2779,7 +2779,7 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C100" t="s">
         <v>16</v>
@@ -2788,13 +2788,13 @@
         <v>31</v>
       </c>
       <c r="E100" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F100" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G100" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2814,10 +2814,10 @@
         <v>31</v>
       </c>
       <c r="E101" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F101" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G101" t="n">
         <v>1.0</v>
@@ -2831,7 +2831,7 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C102" t="s">
         <v>16</v>
@@ -2840,13 +2840,13 @@
         <v>31</v>
       </c>
       <c r="E102" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F102" t="n">
         <v>0.0</v>
       </c>
       <c r="G102" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2866,13 +2866,13 @@
         <v>31</v>
       </c>
       <c r="E103" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F103" t="n">
         <v>0.0</v>
       </c>
       <c r="G103" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="H103" t="n">
         <v>0.0</v>
@@ -2892,13 +2892,13 @@
         <v>31</v>
       </c>
       <c r="E104" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F104" t="n">
         <v>0.0</v>
       </c>
       <c r="G104" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="H104" t="n">
         <v>0.0</v>
@@ -2909,25 +2909,25 @@
         <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C105" t="s">
         <v>16</v>
       </c>
       <c r="D105" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E105" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G105" t="n">
         <v>4.0</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="106">
@@ -2944,16 +2944,16 @@
         <v>32</v>
       </c>
       <c r="E106" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F106" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G106" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H106" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="107">
@@ -2970,13 +2970,13 @@
         <v>32</v>
       </c>
       <c r="E107" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F107" t="n">
         <v>0.0</v>
       </c>
       <c r="G107" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H107" t="n">
         <v>0.0</v>
@@ -2987,7 +2987,7 @@
         <v>8</v>
       </c>
       <c r="B108" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C108" t="s">
         <v>16</v>
@@ -2996,13 +2996,13 @@
         <v>32</v>
       </c>
       <c r="E108" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F108" t="n">
         <v>0.0</v>
       </c>
       <c r="G108" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H108" t="n">
         <v>0.0</v>
@@ -3013,7 +3013,7 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C109" t="s">
         <v>16</v>
@@ -3022,7 +3022,7 @@
         <v>32</v>
       </c>
       <c r="E109" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F109" t="n">
         <v>0.0</v>
@@ -3048,7 +3048,7 @@
         <v>32</v>
       </c>
       <c r="E110" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F110" t="n">
         <v>0.0</v>
@@ -3057,7 +3057,7 @@
         <v>1.0</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="111">
@@ -3065,7 +3065,7 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C111" t="s">
         <v>16</v>
@@ -3073,17 +3073,17 @@
       <c r="D111" t="s">
         <v>32</v>
       </c>
-      <c r="E111" t="s">
-        <v>40</v>
+      <c r="E111" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F111" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G111" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H111" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="112">
@@ -3099,14 +3099,14 @@
       <c r="D112" t="s">
         <v>32</v>
       </c>
-      <c r="E112" t="e">
-        <v>#N/A</v>
+      <c r="E112" t="s">
+        <v>44</v>
       </c>
       <c r="F112" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3126,13 +3126,13 @@
         <v>32</v>
       </c>
       <c r="E113" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F113" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="G113" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
       <c r="H113" t="n">
         <v>0.0</v>
@@ -3152,13 +3152,13 @@
         <v>32</v>
       </c>
       <c r="E114" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F114" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G114" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3169,22 +3169,22 @@
         <v>8</v>
       </c>
       <c r="B115" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C115" t="s">
         <v>16</v>
       </c>
       <c r="D115" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E115" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F115" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G115" t="n">
-        <v>17.0</v>
+        <v>7.0</v>
       </c>
       <c r="H115" t="n">
         <v>0.0</v>
@@ -3204,13 +3204,13 @@
         <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F116" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G116" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H116" t="n">
         <v>0.0</v>
@@ -3230,13 +3230,13 @@
         <v>33</v>
       </c>
       <c r="E117" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F117" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G117" t="n">
-        <v>1.0</v>
+        <v>36.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3256,13 +3256,13 @@
         <v>33</v>
       </c>
       <c r="E118" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F118" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G118" t="n">
-        <v>36.0</v>
+        <v>0.0</v>
       </c>
       <c r="H118" t="n">
         <v>0.0</v>
@@ -3273,7 +3273,7 @@
         <v>8</v>
       </c>
       <c r="B119" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C119" t="s">
         <v>16</v>
@@ -3282,10 +3282,10 @@
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F119" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G119" t="n">
         <v>0.0</v>
@@ -3308,13 +3308,13 @@
         <v>33</v>
       </c>
       <c r="E120" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F120" t="n">
         <v>1.0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H120" t="n">
         <v>0.0</v>
@@ -3334,13 +3334,13 @@
         <v>33</v>
       </c>
       <c r="E121" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F121" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G121" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H121" t="n">
         <v>0.0</v>
@@ -3360,13 +3360,13 @@
         <v>33</v>
       </c>
       <c r="E122" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F122" t="n">
         <v>0.0</v>
       </c>
       <c r="G122" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3377,7 +3377,7 @@
         <v>8</v>
       </c>
       <c r="B123" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C123" t="s">
         <v>16</v>
@@ -3385,17 +3385,17 @@
       <c r="D123" t="s">
         <v>33</v>
       </c>
-      <c r="E123" t="s">
-        <v>42</v>
+      <c r="E123" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G123" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="124">
@@ -3411,17 +3411,17 @@
       <c r="D124" t="s">
         <v>33</v>
       </c>
-      <c r="E124" t="e">
-        <v>#N/A</v>
+      <c r="E124" t="s">
+        <v>44</v>
       </c>
       <c r="F124" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0</v>
+        <v>78.0</v>
       </c>
       <c r="H124" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="125">
@@ -3438,13 +3438,13 @@
         <v>33</v>
       </c>
       <c r="E125" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F125" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="G125" t="n">
-        <v>78.0</v>
+        <v>24.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3464,16 +3464,16 @@
         <v>33</v>
       </c>
       <c r="E126" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F126" t="n">
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
       <c r="G126" t="n">
-        <v>24.0</v>
+        <v>476.0</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="127">
@@ -3490,16 +3490,16 @@
         <v>33</v>
       </c>
       <c r="E127" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F127" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G127" t="n">
-        <v>476.0</v>
+        <v>0.0</v>
       </c>
       <c r="H127" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="128">
@@ -3513,16 +3513,16 @@
         <v>16</v>
       </c>
       <c r="D128" t="s">
-        <v>33</v>
-      </c>
-      <c r="E128" t="s">
-        <v>43</v>
+        <v>34</v>
+      </c>
+      <c r="E128" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F128" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H128" t="n">
         <v>0.0</v>
@@ -3541,14 +3541,14 @@
       <c r="D129" t="s">
         <v>34</v>
       </c>
-      <c r="E129" t="e">
-        <v>#N/A</v>
+      <c r="E129" t="s">
+        <v>44</v>
       </c>
       <c r="F129" t="n">
         <v>1.0</v>
       </c>
       <c r="G129" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -3568,13 +3568,13 @@
         <v>34</v>
       </c>
       <c r="E130" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F130" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H130" t="n">
         <v>0.0</v>
@@ -3594,13 +3594,13 @@
         <v>34</v>
       </c>
       <c r="E131" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F131" t="n">
         <v>2.0</v>
       </c>
       <c r="G131" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
       <c r="H131" t="n">
         <v>0.0</v>
@@ -3617,16 +3617,16 @@
         <v>16</v>
       </c>
       <c r="D132" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E132" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F132" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G132" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -3646,16 +3646,16 @@
         <v>35</v>
       </c>
       <c r="E133" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F133" t="n">
         <v>0.0</v>
       </c>
       <c r="G133" t="n">
-        <v>7.0</v>
+        <v>16.0</v>
       </c>
       <c r="H133" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="134">
@@ -3672,16 +3672,16 @@
         <v>35</v>
       </c>
       <c r="E134" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F134" t="n">
         <v>0.0</v>
       </c>
       <c r="G134" t="n">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
       <c r="H134" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="135">
@@ -3689,22 +3689,22 @@
         <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C135" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D135" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E135" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G135" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3724,13 +3724,13 @@
         <v>36</v>
       </c>
       <c r="E136" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F136" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G136" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="H136" t="n">
         <v>0.0</v>
@@ -3750,13 +3750,13 @@
         <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F137" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3776,13 +3776,13 @@
         <v>36</v>
       </c>
       <c r="E138" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F138" t="n">
         <v>0.0</v>
       </c>
       <c r="G138" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3793,7 +3793,7 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C139" t="s">
         <v>17</v>
@@ -3802,13 +3802,13 @@
         <v>36</v>
       </c>
       <c r="E139" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F139" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G139" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3828,13 +3828,13 @@
         <v>36</v>
       </c>
       <c r="E140" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F140" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G140" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H140" t="n">
         <v>0.0</v>
@@ -3854,13 +3854,13 @@
         <v>36</v>
       </c>
       <c r="E141" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F141" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G141" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G141" t="n">
-        <v>0.0</v>
       </c>
       <c r="H141" t="n">
         <v>0.0</v>
@@ -3880,13 +3880,13 @@
         <v>36</v>
       </c>
       <c r="E142" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F142" t="n">
         <v>0.0</v>
       </c>
       <c r="G142" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3906,13 +3906,13 @@
         <v>36</v>
       </c>
       <c r="E143" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F143" t="n">
         <v>0.0</v>
       </c>
       <c r="G143" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H143" t="n">
         <v>0.0</v>
@@ -3923,7 +3923,7 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C144" t="s">
         <v>17</v>
@@ -3932,13 +3932,13 @@
         <v>36</v>
       </c>
       <c r="E144" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F144" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G144" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3949,7 +3949,7 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
@@ -3957,11 +3957,11 @@
       <c r="D145" t="s">
         <v>36</v>
       </c>
-      <c r="E145" t="s">
-        <v>44</v>
+      <c r="E145" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F145" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G145" t="n">
         <v>0.0</v>
@@ -3983,14 +3983,14 @@
       <c r="D146" t="s">
         <v>36</v>
       </c>
-      <c r="E146" t="e">
-        <v>#N/A</v>
+      <c r="E146" t="s">
+        <v>40</v>
       </c>
       <c r="F146" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4001,22 +4001,22 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E147" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G147" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4036,13 +4036,13 @@
         <v>37</v>
       </c>
       <c r="E148" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F148" t="n">
         <v>1.0</v>
       </c>
       <c r="G148" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4062,13 +4062,13 @@
         <v>37</v>
       </c>
       <c r="E149" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F149" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G149" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4088,13 +4088,13 @@
         <v>37</v>
       </c>
       <c r="E150" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F150" t="n">
         <v>0.0</v>
       </c>
       <c r="G150" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>
@@ -4105,7 +4105,7 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
@@ -4114,13 +4114,13 @@
         <v>37</v>
       </c>
       <c r="E151" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F151" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G151" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4140,13 +4140,13 @@
         <v>37</v>
       </c>
       <c r="E152" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F152" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G152" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4166,13 +4166,13 @@
         <v>37</v>
       </c>
       <c r="E153" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F153" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H153" t="n">
         <v>0.0</v>
@@ -4192,7 +4192,7 @@
         <v>37</v>
       </c>
       <c r="E154" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F154" t="n">
         <v>0.0</v>
@@ -4209,22 +4209,22 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C155" t="s">
         <v>17</v>
       </c>
       <c r="D155" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E155" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F155" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G155" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H155" t="n">
         <v>0.0</v>
@@ -4244,10 +4244,10 @@
         <v>38</v>
       </c>
       <c r="E156" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F156" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G156" t="n">
         <v>0.0</v>
@@ -4270,13 +4270,13 @@
         <v>38</v>
       </c>
       <c r="E157" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F157" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G157" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H157" t="n">
         <v>0.0</v>
@@ -4296,13 +4296,13 @@
         <v>38</v>
       </c>
       <c r="E158" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F158" t="n">
         <v>1.0</v>
       </c>
       <c r="G158" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H158" t="n">
         <v>0.0</v>
@@ -4322,13 +4322,13 @@
         <v>38</v>
       </c>
       <c r="E159" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F159" t="n">
         <v>1.0</v>
       </c>
       <c r="G159" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H159" t="n">
         <v>0.0</v>
@@ -4339,7 +4339,7 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C160" t="s">
         <v>17</v>
@@ -4348,7 +4348,7 @@
         <v>38</v>
       </c>
       <c r="E160" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F160" t="n">
         <v>1.0</v>
@@ -4374,13 +4374,13 @@
         <v>38</v>
       </c>
       <c r="E161" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F161" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H161" t="n">
         <v>0.0</v>
@@ -4391,22 +4391,22 @@
         <v>8</v>
       </c>
       <c r="B162" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C162" t="s">
         <v>17</v>
       </c>
       <c r="D162" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E162" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F162" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G162" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H162" t="n">
         <v>0.0</v>
@@ -4426,13 +4426,13 @@
         <v>39</v>
       </c>
       <c r="E163" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F163" t="n">
         <v>1.0</v>
       </c>
       <c r="G163" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="H163" t="n">
         <v>0.0</v>
@@ -4452,13 +4452,13 @@
         <v>39</v>
       </c>
       <c r="E164" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F164" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G164" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4478,13 +4478,13 @@
         <v>39</v>
       </c>
       <c r="E165" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F165" t="n">
         <v>0.0</v>
       </c>
       <c r="G165" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="H165" t="n">
         <v>0.0</v>
@@ -4495,7 +4495,7 @@
         <v>8</v>
       </c>
       <c r="B166" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C166" t="s">
         <v>17</v>
@@ -4504,13 +4504,13 @@
         <v>39</v>
       </c>
       <c r="E166" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F166" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G166" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="H166" t="n">
         <v>0.0</v>
@@ -4530,10 +4530,10 @@
         <v>39</v>
       </c>
       <c r="E167" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F167" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G167" t="n">
         <v>0.0</v>
@@ -4556,13 +4556,13 @@
         <v>39</v>
       </c>
       <c r="E168" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F168" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G168" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H168" t="n">
         <v>0.0</v>
@@ -4582,13 +4582,13 @@
         <v>39</v>
       </c>
       <c r="E169" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F169" t="n">
         <v>1.0</v>
       </c>
       <c r="G169" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H169" t="n">
         <v>0.0</v>
@@ -4608,13 +4608,13 @@
         <v>39</v>
       </c>
       <c r="E170" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F170" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G170" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H170" t="n">
         <v>0.0</v>
@@ -4634,41 +4634,15 @@
         <v>39</v>
       </c>
       <c r="E171" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F171" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G171" t="n">
         <v>0.0</v>
       </c>
       <c r="H171" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>8</v>
-      </c>
-      <c r="B172" t="s">
-        <v>10</v>
-      </c>
-      <c r="C172" t="s">
-        <v>17</v>
-      </c>
-      <c r="D172" t="s">
-        <v>39</v>
-      </c>
-      <c r="E172" t="s">
-        <v>43</v>
-      </c>
-      <c r="F172" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G172" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H172" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="49">
   <si>
     <t>Area</t>
   </si>
@@ -122,10 +122,16 @@
     <t>VC</t>
   </si>
   <si>
+    <t>FI</t>
+  </si>
+  <si>
     <t>LU</t>
   </si>
   <si>
     <t>MS</t>
+  </si>
+  <si>
+    <t>PI</t>
   </si>
   <si>
     <t>PO</t>
@@ -240,7 +246,7 @@
         <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F2" t="n">
         <v>1.0</v>
@@ -266,7 +272,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -292,7 +298,7 @@
         <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F4" t="n">
         <v>0.0</v>
@@ -318,7 +324,7 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -344,7 +350,7 @@
         <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -370,7 +376,7 @@
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F7" t="n">
         <v>6.0</v>
@@ -396,7 +402,7 @@
         <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
         <v>2.0</v>
@@ -422,7 +428,7 @@
         <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F9" t="n">
         <v>1.0</v>
@@ -448,7 +454,7 @@
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -474,7 +480,7 @@
         <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -500,7 +506,7 @@
         <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F12" t="n">
         <v>1.0</v>
@@ -526,7 +532,7 @@
         <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F13" t="n">
         <v>1.0</v>
@@ -552,13 +558,13 @@
         <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F14" t="n">
         <v>0.0</v>
       </c>
       <c r="G14" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H14" t="n">
         <v>0.0</v>
@@ -578,13 +584,13 @@
         <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
       </c>
       <c r="G15" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="H15" t="n">
         <v>0.0</v>
@@ -604,7 +610,7 @@
         <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F16" t="n">
         <v>2.0</v>
@@ -630,13 +636,13 @@
         <v>19</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H17" t="n">
         <v>0.0</v>
@@ -656,13 +662,13 @@
         <v>19</v>
       </c>
       <c r="E18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F18" t="n">
         <v>0.0</v>
       </c>
       <c r="G18" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H18" t="n">
         <v>0.0</v>
@@ -682,7 +688,7 @@
         <v>19</v>
       </c>
       <c r="E19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F19" t="n">
         <v>0.0</v>
@@ -708,7 +714,7 @@
         <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F20" t="n">
         <v>0.0</v>
@@ -734,7 +740,7 @@
         <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F21" t="n">
         <v>2.0</v>
@@ -760,7 +766,7 @@
         <v>19</v>
       </c>
       <c r="E22" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -786,7 +792,7 @@
         <v>19</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -812,7 +818,7 @@
         <v>20</v>
       </c>
       <c r="E24" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -838,7 +844,7 @@
         <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -864,7 +870,7 @@
         <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>
@@ -890,7 +896,7 @@
         <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F27" t="n">
         <v>1.0</v>
@@ -916,7 +922,7 @@
         <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
@@ -968,7 +974,7 @@
         <v>20</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
@@ -994,7 +1000,7 @@
         <v>21</v>
       </c>
       <c r="E31" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -1020,7 +1026,7 @@
         <v>21</v>
       </c>
       <c r="E32" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F32" t="n">
         <v>0.0</v>
@@ -1046,7 +1052,7 @@
         <v>21</v>
       </c>
       <c r="E33" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F33" t="n">
         <v>0.0</v>
@@ -1072,7 +1078,7 @@
         <v>21</v>
       </c>
       <c r="E34" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F34" t="n">
         <v>2.0</v>
@@ -1098,7 +1104,7 @@
         <v>21</v>
       </c>
       <c r="E35" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F35" t="n">
         <v>2.0</v>
@@ -1124,7 +1130,7 @@
         <v>21</v>
       </c>
       <c r="E36" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F36" t="n">
         <v>0.0</v>
@@ -1150,7 +1156,7 @@
         <v>21</v>
       </c>
       <c r="E37" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F37" t="n">
         <v>0.0</v>
@@ -1176,7 +1182,7 @@
         <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F38" t="n">
         <v>0.0</v>
@@ -1202,7 +1208,7 @@
         <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F39" t="n">
         <v>0.0</v>
@@ -1228,7 +1234,7 @@
         <v>21</v>
       </c>
       <c r="E40" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F40" t="n">
         <v>0.0</v>
@@ -1254,7 +1260,7 @@
         <v>22</v>
       </c>
       <c r="E41" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F41" t="n">
         <v>3.0</v>
@@ -1280,7 +1286,7 @@
         <v>22</v>
       </c>
       <c r="E42" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F42" t="n">
         <v>1.0</v>
@@ -1306,7 +1312,7 @@
         <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F43" t="n">
         <v>0.0</v>
@@ -1332,7 +1338,7 @@
         <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F44" t="n">
         <v>3.0</v>
@@ -1358,7 +1364,7 @@
         <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F45" t="n">
         <v>0.0</v>
@@ -1384,7 +1390,7 @@
         <v>22</v>
       </c>
       <c r="E46" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F46" t="n">
         <v>0.0</v>
@@ -1410,7 +1416,7 @@
         <v>22</v>
       </c>
       <c r="E47" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F47" t="n">
         <v>1.0</v>
@@ -1436,7 +1442,7 @@
         <v>22</v>
       </c>
       <c r="E48" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F48" t="n">
         <v>0.0</v>
@@ -1462,7 +1468,7 @@
         <v>22</v>
       </c>
       <c r="E49" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F49" t="n">
         <v>0.0</v>
@@ -1488,7 +1494,7 @@
         <v>23</v>
       </c>
       <c r="E50" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F50" t="n">
         <v>4.0</v>
@@ -1514,7 +1520,7 @@
         <v>23</v>
       </c>
       <c r="E51" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F51" t="n">
         <v>3.0</v>
@@ -1540,7 +1546,7 @@
         <v>23</v>
       </c>
       <c r="E52" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F52" t="n">
         <v>1.0</v>
@@ -1566,7 +1572,7 @@
         <v>23</v>
       </c>
       <c r="E53" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F53" t="n">
         <v>0.0</v>
@@ -1592,7 +1598,7 @@
         <v>24</v>
       </c>
       <c r="E54" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F54" t="n">
         <v>1.0</v>
@@ -1618,7 +1624,7 @@
         <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F55" t="n">
         <v>2.0</v>
@@ -1644,7 +1650,7 @@
         <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>1.0</v>
@@ -1670,7 +1676,7 @@
         <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F57" t="n">
         <v>3.0</v>
@@ -1696,7 +1702,7 @@
         <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F58" t="n">
         <v>0.0</v>
@@ -1722,7 +1728,7 @@
         <v>25</v>
       </c>
       <c r="E59" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F59" t="n">
         <v>0.0</v>
@@ -1748,7 +1754,7 @@
         <v>25</v>
       </c>
       <c r="E60" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F60" t="n">
         <v>0.0</v>
@@ -1774,7 +1780,7 @@
         <v>25</v>
       </c>
       <c r="E61" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F61" t="n">
         <v>2.0</v>
@@ -1800,7 +1806,7 @@
         <v>25</v>
       </c>
       <c r="E62" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F62" t="n">
         <v>0.0</v>
@@ -1826,7 +1832,7 @@
         <v>25</v>
       </c>
       <c r="E63" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F63" t="n">
         <v>0.0</v>
@@ -1852,7 +1858,7 @@
         <v>25</v>
       </c>
       <c r="E64" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F64" t="n">
         <v>1.0</v>
@@ -1878,7 +1884,7 @@
         <v>25</v>
       </c>
       <c r="E65" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F65" t="n">
         <v>0.0</v>
@@ -1904,7 +1910,7 @@
         <v>25</v>
       </c>
       <c r="E66" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F66" t="n">
         <v>0.0</v>
@@ -1930,7 +1936,7 @@
         <v>26</v>
       </c>
       <c r="E67" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F67" t="n">
         <v>0.0</v>
@@ -1956,7 +1962,7 @@
         <v>26</v>
       </c>
       <c r="E68" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F68" t="n">
         <v>0.0</v>
@@ -1982,7 +1988,7 @@
         <v>26</v>
       </c>
       <c r="E69" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F69" t="n">
         <v>0.0</v>
@@ -2008,7 +2014,7 @@
         <v>27</v>
       </c>
       <c r="E70" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F70" t="n">
         <v>0.0</v>
@@ -2034,7 +2040,7 @@
         <v>27</v>
       </c>
       <c r="E71" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F71" t="n">
         <v>0.0</v>
@@ -2060,7 +2066,7 @@
         <v>27</v>
       </c>
       <c r="E72" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F72" t="n">
         <v>0.0</v>
@@ -2112,7 +2118,7 @@
         <v>28</v>
       </c>
       <c r="E74" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F74" t="n">
         <v>1.0</v>
@@ -2138,7 +2144,7 @@
         <v>28</v>
       </c>
       <c r="E75" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F75" t="n">
         <v>1.0</v>
@@ -2164,7 +2170,7 @@
         <v>28</v>
       </c>
       <c r="E76" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F76" t="n">
         <v>1.0</v>
@@ -2190,7 +2196,7 @@
         <v>28</v>
       </c>
       <c r="E77" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F77" t="n">
         <v>0.0</v>
@@ -2216,7 +2222,7 @@
         <v>29</v>
       </c>
       <c r="E78" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F78" t="n">
         <v>1.0</v>
@@ -2268,7 +2274,7 @@
         <v>29</v>
       </c>
       <c r="E80" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F80" t="n">
         <v>0.0</v>
@@ -2294,7 +2300,7 @@
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F81" t="n">
         <v>0.0</v>
@@ -2320,7 +2326,7 @@
         <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F82" t="n">
         <v>1.0</v>
@@ -2346,7 +2352,7 @@
         <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F83" t="n">
         <v>1.0</v>
@@ -2372,7 +2378,7 @@
         <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F84" t="n">
         <v>0.0</v>
@@ -2398,7 +2404,7 @@
         <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F85" t="n">
         <v>0.0</v>
@@ -2424,7 +2430,7 @@
         <v>29</v>
       </c>
       <c r="E86" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F86" t="n">
         <v>1.0</v>
@@ -2450,7 +2456,7 @@
         <v>29</v>
       </c>
       <c r="E87" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F87" t="n">
         <v>0.0</v>
@@ -2476,7 +2482,7 @@
         <v>29</v>
       </c>
       <c r="E88" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F88" t="n">
         <v>0.0</v>
@@ -2502,7 +2508,7 @@
         <v>30</v>
       </c>
       <c r="E89" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F89" t="n">
         <v>1.0</v>
@@ -2528,7 +2534,7 @@
         <v>30</v>
       </c>
       <c r="E90" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F90" t="n">
         <v>2.0</v>
@@ -2554,7 +2560,7 @@
         <v>30</v>
       </c>
       <c r="E91" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F91" t="n">
         <v>0.0</v>
@@ -2580,7 +2586,7 @@
         <v>30</v>
       </c>
       <c r="E92" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F92" t="n">
         <v>0.0</v>
@@ -2606,7 +2612,7 @@
         <v>30</v>
       </c>
       <c r="E93" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F93" t="n">
         <v>0.0</v>
@@ -2632,7 +2638,7 @@
         <v>31</v>
       </c>
       <c r="E94" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F94" t="n">
         <v>0.0</v>
@@ -2658,7 +2664,7 @@
         <v>31</v>
       </c>
       <c r="E95" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F95" t="n">
         <v>0.0</v>
@@ -2684,7 +2690,7 @@
         <v>31</v>
       </c>
       <c r="E96" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F96" t="n">
         <v>3.0</v>
@@ -2736,7 +2742,7 @@
         <v>31</v>
       </c>
       <c r="E98" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F98" t="n">
         <v>0.0</v>
@@ -2762,7 +2768,7 @@
         <v>31</v>
       </c>
       <c r="E99" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F99" t="n">
         <v>0.0</v>
@@ -2788,7 +2794,7 @@
         <v>31</v>
       </c>
       <c r="E100" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F100" t="n">
         <v>1.0</v>
@@ -2814,7 +2820,7 @@
         <v>31</v>
       </c>
       <c r="E101" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F101" t="n">
         <v>0.0</v>
@@ -2840,7 +2846,7 @@
         <v>31</v>
       </c>
       <c r="E102" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F102" t="n">
         <v>0.0</v>
@@ -2866,7 +2872,7 @@
         <v>31</v>
       </c>
       <c r="E103" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F103" t="n">
         <v>0.0</v>
@@ -2892,7 +2898,7 @@
         <v>31</v>
       </c>
       <c r="E104" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F104" t="n">
         <v>0.0</v>
@@ -2918,7 +2924,7 @@
         <v>32</v>
       </c>
       <c r="E105" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F105" t="n">
         <v>1.0</v>
@@ -2944,7 +2950,7 @@
         <v>32</v>
       </c>
       <c r="E106" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F106" t="n">
         <v>0.0</v>
@@ -2970,7 +2976,7 @@
         <v>32</v>
       </c>
       <c r="E107" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F107" t="n">
         <v>0.0</v>
@@ -2996,7 +3002,7 @@
         <v>32</v>
       </c>
       <c r="E108" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F108" t="n">
         <v>0.0</v>
@@ -3022,7 +3028,7 @@
         <v>32</v>
       </c>
       <c r="E109" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F109" t="n">
         <v>0.0</v>
@@ -3048,7 +3054,7 @@
         <v>32</v>
       </c>
       <c r="E110" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F110" t="n">
         <v>0.0</v>
@@ -3100,7 +3106,7 @@
         <v>32</v>
       </c>
       <c r="E112" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F112" t="n">
         <v>3.0</v>
@@ -3126,7 +3132,7 @@
         <v>32</v>
       </c>
       <c r="E113" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F113" t="n">
         <v>6.0</v>
@@ -3152,7 +3158,7 @@
         <v>32</v>
       </c>
       <c r="E114" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F114" t="n">
         <v>2.0</v>
@@ -3178,7 +3184,7 @@
         <v>33</v>
       </c>
       <c r="E115" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F115" t="n">
         <v>3.0</v>
@@ -3204,7 +3210,7 @@
         <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F116" t="n">
         <v>4.0</v>
@@ -3230,7 +3236,7 @@
         <v>33</v>
       </c>
       <c r="E117" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F117" t="n">
         <v>3.0</v>
@@ -3256,7 +3262,7 @@
         <v>33</v>
       </c>
       <c r="E118" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F118" t="n">
         <v>2.0</v>
@@ -3282,7 +3288,7 @@
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F119" t="n">
         <v>1.0</v>
@@ -3308,7 +3314,7 @@
         <v>33</v>
       </c>
       <c r="E120" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F120" t="n">
         <v>1.0</v>
@@ -3334,7 +3340,7 @@
         <v>33</v>
       </c>
       <c r="E121" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F121" t="n">
         <v>0.0</v>
@@ -3360,7 +3366,7 @@
         <v>33</v>
       </c>
       <c r="E122" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F122" t="n">
         <v>0.0</v>
@@ -3412,7 +3418,7 @@
         <v>33</v>
       </c>
       <c r="E124" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F124" t="n">
         <v>10.0</v>
@@ -3438,7 +3444,7 @@
         <v>33</v>
       </c>
       <c r="E125" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F125" t="n">
         <v>12.0</v>
@@ -3464,7 +3470,7 @@
         <v>33</v>
       </c>
       <c r="E126" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F126" t="n">
         <v>3.0</v>
@@ -3490,7 +3496,7 @@
         <v>33</v>
       </c>
       <c r="E127" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F127" t="n">
         <v>2.0</v>
@@ -3542,7 +3548,7 @@
         <v>34</v>
       </c>
       <c r="E129" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F129" t="n">
         <v>1.0</v>
@@ -3568,7 +3574,7 @@
         <v>34</v>
       </c>
       <c r="E130" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F130" t="n">
         <v>2.0</v>
@@ -3594,7 +3600,7 @@
         <v>34</v>
       </c>
       <c r="E131" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F131" t="n">
         <v>2.0</v>
@@ -3620,7 +3626,7 @@
         <v>35</v>
       </c>
       <c r="E132" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F132" t="n">
         <v>0.0</v>
@@ -3646,7 +3652,7 @@
         <v>35</v>
       </c>
       <c r="E133" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F133" t="n">
         <v>0.0</v>
@@ -3672,7 +3678,7 @@
         <v>35</v>
       </c>
       <c r="E134" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F134" t="n">
         <v>0.0</v>
@@ -3698,13 +3704,13 @@
         <v>36</v>
       </c>
       <c r="E135" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F135" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G135" t="n">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3721,10 +3727,10 @@
         <v>17</v>
       </c>
       <c r="D136" t="s">
-        <v>36</v>
-      </c>
-      <c r="E136" t="s">
-        <v>43</v>
+        <v>37</v>
+      </c>
+      <c r="E136" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F136" t="n">
         <v>1.0</v>
@@ -3747,16 +3753,16 @@
         <v>17</v>
       </c>
       <c r="D137" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E137" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F137" t="n">
         <v>0.0</v>
       </c>
       <c r="G137" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3773,7 +3779,7 @@
         <v>17</v>
       </c>
       <c r="D138" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E138" t="s">
         <v>42</v>
@@ -3782,7 +3788,7 @@
         <v>0.0</v>
       </c>
       <c r="G138" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3793,19 +3799,19 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C139" t="s">
         <v>17</v>
       </c>
       <c r="D139" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E139" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F139" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G139" t="n">
         <v>3.0</v>
@@ -3825,13 +3831,13 @@
         <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>36</v>
-      </c>
-      <c r="E140" t="s">
-        <v>43</v>
+        <v>37</v>
+      </c>
+      <c r="E140" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F140" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G140" t="n">
         <v>0.0</v>
@@ -3851,16 +3857,16 @@
         <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E141" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F141" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G141" t="n">
-        <v>2.0</v>
+        <v>15.0</v>
       </c>
       <c r="H141" t="n">
         <v>0.0</v>
@@ -3877,16 +3883,16 @@
         <v>17</v>
       </c>
       <c r="D142" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E142" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F142" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G142" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3903,10 +3909,10 @@
         <v>17</v>
       </c>
       <c r="D143" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E143" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F143" t="n">
         <v>0.0</v>
@@ -3923,22 +3929,22 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C144" t="s">
         <v>17</v>
       </c>
       <c r="D144" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E144" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F144" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3949,22 +3955,22 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
       </c>
       <c r="D145" t="s">
-        <v>36</v>
-      </c>
-      <c r="E145" t="e">
-        <v>#N/A</v>
+        <v>37</v>
+      </c>
+      <c r="E145" t="s">
+        <v>44</v>
       </c>
       <c r="F145" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H145" t="n">
         <v>0.0</v>
@@ -3975,22 +3981,22 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C146" t="s">
         <v>17</v>
       </c>
       <c r="D146" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E146" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G146" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4007,10 +4013,10 @@
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E147" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F147" t="n">
         <v>1.0</v>
@@ -4033,10 +4039,10 @@
         <v>17</v>
       </c>
       <c r="D148" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E148" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F148" t="n">
         <v>1.0</v>
@@ -4059,10 +4065,10 @@
         <v>17</v>
       </c>
       <c r="D149" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E149" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F149" t="n">
         <v>0.0</v>
@@ -4085,10 +4091,10 @@
         <v>17</v>
       </c>
       <c r="D150" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E150" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F150" t="n">
         <v>0.0</v>
@@ -4111,10 +4117,10 @@
         <v>17</v>
       </c>
       <c r="D151" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E151" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F151" t="n">
         <v>2.0</v>
@@ -4137,10 +4143,10 @@
         <v>17</v>
       </c>
       <c r="D152" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E152" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F152" t="n">
         <v>1.0</v>
@@ -4163,10 +4169,10 @@
         <v>17</v>
       </c>
       <c r="D153" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E153" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F153" t="n">
         <v>0.0</v>
@@ -4189,10 +4195,10 @@
         <v>17</v>
       </c>
       <c r="D154" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E154" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F154" t="n">
         <v>0.0</v>
@@ -4215,10 +4221,10 @@
         <v>17</v>
       </c>
       <c r="D155" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E155" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F155" t="n">
         <v>1.0</v>
@@ -4241,16 +4247,16 @@
         <v>17</v>
       </c>
       <c r="D156" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E156" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F156" t="n">
         <v>3.0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H156" t="n">
         <v>0.0</v>
@@ -4267,10 +4273,10 @@
         <v>17</v>
       </c>
       <c r="D157" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E157" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F157" t="n">
         <v>1.0</v>
@@ -4293,13 +4299,13 @@
         <v>17</v>
       </c>
       <c r="D158" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E158" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F158" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G158" t="n">
         <v>1.0</v>
@@ -4319,16 +4325,16 @@
         <v>17</v>
       </c>
       <c r="D159" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E159" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F159" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H159" t="n">
         <v>0.0</v>
@@ -4339,16 +4345,16 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C160" t="s">
         <v>17</v>
       </c>
       <c r="D160" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E160" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F160" t="n">
         <v>1.0</v>
@@ -4365,22 +4371,22 @@
         <v>8</v>
       </c>
       <c r="B161" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C161" t="s">
         <v>17</v>
       </c>
       <c r="D161" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E161" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F161" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G161" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H161" t="n">
         <v>0.0</v>
@@ -4397,16 +4403,16 @@
         <v>17</v>
       </c>
       <c r="D162" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E162" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F162" t="n">
         <v>1.0</v>
       </c>
       <c r="G162" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="H162" t="n">
         <v>0.0</v>
@@ -4423,16 +4429,16 @@
         <v>17</v>
       </c>
       <c r="D163" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E163" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F163" t="n">
         <v>1.0</v>
       </c>
       <c r="G163" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="H163" t="n">
         <v>0.0</v>
@@ -4449,16 +4455,16 @@
         <v>17</v>
       </c>
       <c r="D164" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E164" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F164" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G164" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4469,22 +4475,22 @@
         <v>8</v>
       </c>
       <c r="B165" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C165" t="s">
         <v>17</v>
       </c>
       <c r="D165" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E165" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F165" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G165" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="H165" t="n">
         <v>0.0</v>
@@ -4495,22 +4501,22 @@
         <v>8</v>
       </c>
       <c r="B166" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C166" t="s">
         <v>17</v>
       </c>
       <c r="D166" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E166" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F166" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G166" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H166" t="n">
         <v>0.0</v>
@@ -4521,22 +4527,22 @@
         <v>8</v>
       </c>
       <c r="B167" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C167" t="s">
         <v>17</v>
       </c>
       <c r="D167" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E167" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F167" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G167" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G167" t="n">
-        <v>0.0</v>
       </c>
       <c r="H167" t="n">
         <v>0.0</v>
@@ -4547,22 +4553,22 @@
         <v>8</v>
       </c>
       <c r="B168" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C168" t="s">
         <v>17</v>
       </c>
       <c r="D168" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E168" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F168" t="n">
         <v>1.0</v>
       </c>
       <c r="G168" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H168" t="n">
         <v>0.0</v>
@@ -4573,22 +4579,22 @@
         <v>8</v>
       </c>
       <c r="B169" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C169" t="s">
         <v>17</v>
       </c>
       <c r="D169" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E169" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F169" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G169" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H169" t="n">
         <v>0.0</v>
@@ -4599,22 +4605,22 @@
         <v>8</v>
       </c>
       <c r="B170" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C170" t="s">
         <v>17</v>
       </c>
       <c r="D170" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E170" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F170" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H170" t="n">
         <v>0.0</v>
@@ -4625,24 +4631,180 @@
         <v>8</v>
       </c>
       <c r="B171" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C171" t="s">
         <v>17</v>
       </c>
       <c r="D171" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E171" t="s">
         <v>43</v>
       </c>
       <c r="F171" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G171" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H171" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>8</v>
+      </c>
+      <c r="B172" t="s">
+        <v>10</v>
+      </c>
+      <c r="C172" t="s">
+        <v>17</v>
+      </c>
+      <c r="D172" t="s">
+        <v>41</v>
+      </c>
+      <c r="E172" t="s">
+        <v>48</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>8</v>
+      </c>
+      <c r="B173" t="s">
+        <v>10</v>
+      </c>
+      <c r="C173" t="s">
+        <v>17</v>
+      </c>
+      <c r="D173" t="s">
+        <v>41</v>
+      </c>
+      <c r="E173" t="s">
+        <v>47</v>
+      </c>
+      <c r="F173" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>8</v>
+      </c>
+      <c r="B174" t="s">
+        <v>10</v>
+      </c>
+      <c r="C174" t="s">
+        <v>17</v>
+      </c>
+      <c r="D174" t="s">
+        <v>41</v>
+      </c>
+      <c r="E174" t="s">
+        <v>46</v>
+      </c>
+      <c r="F174" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G174" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>8</v>
+      </c>
+      <c r="B175" t="s">
+        <v>10</v>
+      </c>
+      <c r="C175" t="s">
+        <v>17</v>
+      </c>
+      <c r="D175" t="s">
+        <v>41</v>
+      </c>
+      <c r="E175" t="s">
+        <v>43</v>
+      </c>
+      <c r="F175" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G175" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>8</v>
+      </c>
+      <c r="B176" t="s">
+        <v>10</v>
+      </c>
+      <c r="C176" t="s">
+        <v>17</v>
+      </c>
+      <c r="D176" t="s">
+        <v>41</v>
+      </c>
+      <c r="E176" t="s">
+        <v>44</v>
+      </c>
+      <c r="F176" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>8</v>
+      </c>
+      <c r="B177" t="s">
+        <v>10</v>
+      </c>
+      <c r="C177" t="s">
+        <v>17</v>
+      </c>
+      <c r="D177" t="s">
+        <v>41</v>
+      </c>
+      <c r="E177" t="s">
+        <v>45</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H177" t="n">
         <v>0.0</v>
       </c>
     </row>
